--- a/TTABLEAU DES PRIX AVEC REF.xlsx
+++ b/TTABLEAU DES PRIX AVEC REF.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melou\blazing-dynasty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749EAF14-F73D-4D92-BF80-58087E2AC82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA56D4DA-CE41-4563-8EA1-AE95D11A1CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14280" yWindow="0" windowWidth="14625" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$374</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$374</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1501" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="1129">
   <si>
     <t>Art</t>
   </si>
@@ -3409,6 +3409,12 @@
   </si>
   <si>
     <t>SET 010702 + 010703 + 010705</t>
+  </si>
+  <si>
+    <t>Rupture</t>
+  </si>
+  <si>
+    <t>Oui</t>
   </si>
 </sst>
 </file>
@@ -3802,20 +3808,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L381"/>
+  <dimension ref="A1:M381"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="45" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="5" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="45" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3832,19 +3838,22 @@
         <v>1108</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -3862,12 +3871,13 @@
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="2"/>
+      <c r="I2" s="11" t="s">
         <v>1089</v>
       </c>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -3885,12 +3895,13 @@
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="2"/>
+      <c r="I3" s="11" t="s">
         <v>1090</v>
       </c>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -3908,12 +3919,13 @@
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="2"/>
+      <c r="I4" s="11" t="s">
         <v>1091</v>
       </c>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -3931,12 +3943,13 @@
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="2"/>
+      <c r="I5" s="11" t="s">
         <v>1092</v>
       </c>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -3954,12 +3967,13 @@
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="2"/>
+      <c r="I6" s="11" t="s">
         <v>1093</v>
       </c>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -3977,12 +3991,13 @@
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="2"/>
+      <c r="I7" s="11" t="s">
         <v>1094</v>
       </c>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
@@ -4000,12 +4015,13 @@
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="2"/>
+      <c r="I8" s="11" t="s">
         <v>1095</v>
       </c>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -4023,12 +4039,13 @@
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="2"/>
+      <c r="I9" s="11" t="s">
         <v>1096</v>
       </c>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
@@ -4046,12 +4063,13 @@
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="2"/>
+      <c r="I10" s="11" t="s">
         <v>1097</v>
       </c>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
@@ -4069,12 +4087,13 @@
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="2"/>
+      <c r="I11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
@@ -4092,12 +4111,13 @@
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="2"/>
+      <c r="I12" s="11" t="s">
         <v>1098</v>
       </c>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>33</v>
       </c>
@@ -4115,12 +4135,13 @@
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="2"/>
+      <c r="I13" s="11" t="s">
         <v>1099</v>
       </c>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>35</v>
       </c>
@@ -4138,12 +4159,13 @@
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="2"/>
+      <c r="I14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>38</v>
       </c>
@@ -4161,12 +4183,13 @@
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="2"/>
+      <c r="I15" s="11" t="s">
         <v>1100</v>
       </c>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>40</v>
       </c>
@@ -4184,12 +4207,13 @@
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="2"/>
+      <c r="I16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>43</v>
       </c>
@@ -4207,12 +4231,13 @@
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="3" t="s">
+      <c r="H17" s="2"/>
+      <c r="I17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>46</v>
       </c>
@@ -4230,12 +4255,13 @@
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="2"/>
+      <c r="I18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>49</v>
       </c>
@@ -4253,12 +4279,13 @@
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="2"/>
+      <c r="I19" s="3" t="s">
         <v>1101</v>
       </c>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
@@ -4276,12 +4303,13 @@
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-      <c r="H20" s="3" t="s">
+      <c r="H20" s="2"/>
+      <c r="I20" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>54</v>
       </c>
@@ -4299,12 +4327,13 @@
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="2"/>
+      <c r="I21" s="11" t="s">
         <v>1102</v>
       </c>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4322,12 +4351,13 @@
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="3" t="s">
+      <c r="H22" s="2"/>
+      <c r="I22" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>59</v>
       </c>
@@ -4345,12 +4375,13 @@
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="3" t="s">
+      <c r="H23" s="2"/>
+      <c r="I23" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>62</v>
       </c>
@@ -4368,12 +4399,13 @@
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="3" t="s">
+      <c r="H24" s="2"/>
+      <c r="I24" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>65</v>
       </c>
@@ -4391,12 +4423,13 @@
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-      <c r="H25" s="3" t="s">
+      <c r="H25" s="2"/>
+      <c r="I25" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>68</v>
       </c>
@@ -4414,12 +4447,13 @@
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-      <c r="H26" s="3" t="s">
+      <c r="H26" s="2"/>
+      <c r="I26" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>71</v>
       </c>
@@ -4437,12 +4471,13 @@
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="2"/>
+      <c r="I27" s="11" t="s">
         <v>1104</v>
       </c>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>73</v>
       </c>
@@ -4460,12 +4495,13 @@
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-      <c r="H28" s="3" t="s">
+      <c r="H28" s="2"/>
+      <c r="I28" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>76</v>
       </c>
@@ -4483,12 +4519,13 @@
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
-      <c r="H29" s="3" t="s">
+      <c r="H29" s="2"/>
+      <c r="I29" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J29" s="2"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>79</v>
       </c>
@@ -4506,12 +4543,13 @@
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="2"/>
+      <c r="I30" s="11" t="s">
         <v>1103</v>
       </c>
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J30" s="2"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>81</v>
       </c>
@@ -4529,12 +4567,13 @@
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
-      <c r="H31" s="3" t="s">
+      <c r="H31" s="2"/>
+      <c r="I31" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J31" s="2"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>84</v>
       </c>
@@ -4552,12 +4591,13 @@
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="3" t="s">
+      <c r="H32" s="2"/>
+      <c r="I32" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I32" s="2"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>87</v>
       </c>
@@ -4575,12 +4615,13 @@
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="3" t="s">
+      <c r="H33" s="2"/>
+      <c r="I33" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>90</v>
       </c>
@@ -4598,12 +4639,13 @@
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
-      <c r="H34" s="3" t="s">
+      <c r="H34" s="2"/>
+      <c r="I34" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I34" s="2"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>93</v>
       </c>
@@ -4621,12 +4663,13 @@
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
-      <c r="H35" s="3" t="s">
+      <c r="H35" s="2"/>
+      <c r="I35" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I35" s="2"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>96</v>
       </c>
@@ -4644,12 +4687,13 @@
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
-      <c r="H36" s="3" t="s">
+      <c r="H36" s="2"/>
+      <c r="I36" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="I36" s="2"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>99</v>
       </c>
@@ -4667,12 +4711,13 @@
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
-      <c r="H37" s="3" t="s">
+      <c r="H37" s="2"/>
+      <c r="I37" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I37" s="2"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J37" s="2"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>102</v>
       </c>
@@ -4690,12 +4735,13 @@
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="2"/>
+      <c r="I38" s="11" t="s">
         <v>1105</v>
       </c>
-      <c r="I38" s="2"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J38" s="2"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>104</v>
       </c>
@@ -4713,12 +4759,13 @@
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-      <c r="H39" s="11" t="s">
+      <c r="H39" s="2"/>
+      <c r="I39" s="11" t="s">
         <v>1106</v>
       </c>
-      <c r="I39" s="2"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>106</v>
       </c>
@@ -4736,12 +4783,13 @@
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="11" t="s">
+      <c r="H40" s="2"/>
+      <c r="I40" s="11" t="s">
         <v>1107</v>
       </c>
-      <c r="I40" s="2"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J40" s="2"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>108</v>
       </c>
@@ -4759,12 +4807,13 @@
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
-      <c r="H41" s="3" t="s">
+      <c r="H41" s="2"/>
+      <c r="I41" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="I41" s="2"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J41" s="2"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>111</v>
       </c>
@@ -4782,12 +4831,13 @@
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="3" t="s">
+      <c r="H42" s="2"/>
+      <c r="I42" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="I42" s="2"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J42" s="2"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>114</v>
       </c>
@@ -4805,12 +4855,13 @@
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="3" t="s">
+      <c r="H43" s="2"/>
+      <c r="I43" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="I43" s="2"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J43" s="2"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>117</v>
       </c>
@@ -4828,12 +4879,13 @@
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="3" t="s">
+      <c r="H44" s="2"/>
+      <c r="I44" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I44" s="2"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J44" s="2"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>120</v>
       </c>
@@ -4851,12 +4903,13 @@
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="3" t="s">
+      <c r="H45" s="2"/>
+      <c r="I45" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="I45" s="2"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J45" s="2"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>123</v>
       </c>
@@ -4874,12 +4927,13 @@
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="3" t="s">
+      <c r="H46" s="2"/>
+      <c r="I46" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="I46" s="2"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J46" s="2"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>126</v>
       </c>
@@ -4897,12 +4951,13 @@
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
-      <c r="H47" s="3" t="s">
+      <c r="H47" s="2"/>
+      <c r="I47" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I47" s="2"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J47" s="2"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>129</v>
       </c>
@@ -4920,12 +4975,13 @@
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="3" t="s">
+      <c r="H48" s="2"/>
+      <c r="I48" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="I48" s="2"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J48" s="2"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>132</v>
       </c>
@@ -4941,14 +4997,17 @@
       <c r="E49" s="2">
         <v>5.25</v>
       </c>
-      <c r="F49" s="2"/>
+      <c r="F49" s="2" t="s">
+        <v>1128</v>
+      </c>
       <c r="G49" s="2"/>
-      <c r="H49" s="3" t="s">
+      <c r="H49" s="2"/>
+      <c r="I49" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="I49" s="2"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J49" s="2"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>135</v>
       </c>
@@ -4966,12 +5025,13 @@
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="3" t="s">
+      <c r="H50" s="2"/>
+      <c r="I50" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="I50" s="2"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J50" s="2"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>138</v>
       </c>
@@ -4989,12 +5049,13 @@
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-      <c r="H51" s="3" t="s">
+      <c r="H51" s="2"/>
+      <c r="I51" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="I51" s="2"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J51" s="2"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>141</v>
       </c>
@@ -5012,12 +5073,13 @@
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="3" t="s">
+      <c r="H52" s="2"/>
+      <c r="I52" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="I52" s="2"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J52" s="2"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>144</v>
       </c>
@@ -5035,12 +5097,13 @@
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="3" t="s">
+      <c r="H53" s="2"/>
+      <c r="I53" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="I53" s="2"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J53" s="2"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>147</v>
       </c>
@@ -5058,12 +5121,13 @@
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="3" t="s">
+      <c r="H54" s="2"/>
+      <c r="I54" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="I54" s="2"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J54" s="2"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>150</v>
       </c>
@@ -5081,12 +5145,13 @@
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-      <c r="H55" s="3" t="s">
+      <c r="H55" s="2"/>
+      <c r="I55" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="I55" s="2"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J55" s="2"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>153</v>
       </c>
@@ -5104,12 +5169,13 @@
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="3" t="s">
+      <c r="H56" s="2"/>
+      <c r="I56" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="I56" s="2"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J56" s="2"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>156</v>
       </c>
@@ -5127,12 +5193,13 @@
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="3" t="s">
+      <c r="H57" s="2"/>
+      <c r="I57" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I57" s="2"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J57" s="2"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>159</v>
       </c>
@@ -5150,12 +5217,13 @@
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-      <c r="H58" s="3" t="s">
+      <c r="H58" s="2"/>
+      <c r="I58" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I58" s="2"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J58" s="2"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>161</v>
       </c>
@@ -5173,12 +5241,13 @@
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-      <c r="H59" s="3" t="s">
+      <c r="H59" s="2"/>
+      <c r="I59" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="I59" s="2"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J59" s="2"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>164</v>
       </c>
@@ -5196,12 +5265,13 @@
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="H60" s="3" t="s">
+      <c r="H60" s="2"/>
+      <c r="I60" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="I60" s="2"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J60" s="2"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>167</v>
       </c>
@@ -5219,12 +5289,13 @@
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
-      <c r="H61" s="3" t="s">
+      <c r="H61" s="2"/>
+      <c r="I61" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="I61" s="2"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J61" s="2"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>170</v>
       </c>
@@ -5242,12 +5313,13 @@
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="3" t="s">
+      <c r="H62" s="2"/>
+      <c r="I62" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="I62" s="2"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J62" s="2"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>173</v>
       </c>
@@ -5265,12 +5337,13 @@
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
-      <c r="H63" s="3" t="s">
+      <c r="H63" s="2"/>
+      <c r="I63" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="I63" s="2"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J63" s="2"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>176</v>
       </c>
@@ -5288,12 +5361,13 @@
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="3" t="s">
+      <c r="H64" s="2"/>
+      <c r="I64" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="I64" s="2"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J64" s="2"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>179</v>
       </c>
@@ -5311,12 +5385,13 @@
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
-      <c r="H65" s="3" t="s">
+      <c r="H65" s="2"/>
+      <c r="I65" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="I65" s="2"/>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J65" s="2"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>182</v>
       </c>
@@ -5334,12 +5409,13 @@
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="3" t="s">
+      <c r="H66" s="2"/>
+      <c r="I66" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="I66" s="2"/>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J66" s="2"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>185</v>
       </c>
@@ -5357,12 +5433,13 @@
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="3" t="s">
+      <c r="H67" s="2"/>
+      <c r="I67" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="I67" s="2"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J67" s="2"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>188</v>
       </c>
@@ -5380,12 +5457,13 @@
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="3" t="s">
+      <c r="H68" s="2"/>
+      <c r="I68" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="I68" s="2"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J68" s="2"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>191</v>
       </c>
@@ -5403,12 +5481,13 @@
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
-      <c r="H69" s="3" t="s">
+      <c r="H69" s="2"/>
+      <c r="I69" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I69" s="2"/>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J69" s="2"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>194</v>
       </c>
@@ -5426,12 +5505,13 @@
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="3" t="s">
+      <c r="H70" s="2"/>
+      <c r="I70" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="I70" s="2"/>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J70" s="2"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>197</v>
       </c>
@@ -5449,12 +5529,13 @@
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
-      <c r="H71" s="3" t="s">
+      <c r="H71" s="2"/>
+      <c r="I71" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="I71" s="2"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J71" s="2"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>200</v>
       </c>
@@ -5472,12 +5553,13 @@
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
-      <c r="H72" s="3" t="s">
+      <c r="H72" s="2"/>
+      <c r="I72" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="I72" s="2"/>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J72" s="2"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>203</v>
       </c>
@@ -5495,12 +5577,13 @@
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
-      <c r="H73" s="3" t="s">
+      <c r="H73" s="2"/>
+      <c r="I73" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="I73" s="2"/>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J73" s="2"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>206</v>
       </c>
@@ -5518,12 +5601,13 @@
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
-      <c r="H74" s="3" t="s">
+      <c r="H74" s="2"/>
+      <c r="I74" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="I74" s="2"/>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J74" s="2"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
         <v>210</v>
       </c>
@@ -5541,14 +5625,15 @@
       </c>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
-      <c r="H75" s="7" t="s">
+      <c r="H75" s="6"/>
+      <c r="I75" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="I75" s="8"/>
-      <c r="J75" s="9"/>
+      <c r="J75" s="8"/>
       <c r="K75" s="9"/>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L75" s="9"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>213</v>
       </c>
@@ -5566,12 +5651,13 @@
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
-      <c r="H76" s="3" t="s">
+      <c r="H76" s="2"/>
+      <c r="I76" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="I76" s="2"/>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J76" s="2"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>216</v>
       </c>
@@ -5589,12 +5675,13 @@
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
-      <c r="H77" s="3" t="s">
+      <c r="H77" s="2"/>
+      <c r="I77" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="I77" s="2"/>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J77" s="2"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>219</v>
       </c>
@@ -5612,12 +5699,13 @@
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
-      <c r="H78" s="3" t="s">
+      <c r="H78" s="2"/>
+      <c r="I78" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="I78" s="2"/>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J78" s="2"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>251104</v>
       </c>
@@ -5635,13 +5723,14 @@
       </c>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
-      <c r="H79" s="7" t="s">
+      <c r="H79" s="6"/>
+      <c r="I79" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="I79" s="8"/>
-      <c r="J79" s="9"/>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J79" s="8"/>
+      <c r="K79" s="9"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>224</v>
       </c>
@@ -5659,12 +5748,13 @@
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
-      <c r="H80" s="3" t="s">
+      <c r="H80" s="2"/>
+      <c r="I80" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="I80" s="2"/>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J80" s="2"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>228</v>
       </c>
@@ -5682,12 +5772,13 @@
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
-      <c r="H81" s="3" t="s">
+      <c r="H81" s="2"/>
+      <c r="I81" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="I81" s="2"/>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J81" s="2"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>231</v>
       </c>
@@ -5705,12 +5796,13 @@
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
-      <c r="H82" s="3" t="s">
+      <c r="H82" s="2"/>
+      <c r="I82" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="I82" s="2"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J82" s="2"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
         <v>234</v>
       </c>
@@ -5728,15 +5820,16 @@
       </c>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
-      <c r="H83" s="7" t="s">
+      <c r="H83" s="6"/>
+      <c r="I83" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="I83" s="8"/>
-      <c r="J83" s="9"/>
+      <c r="J83" s="8"/>
       <c r="K83" s="9"/>
       <c r="L83" s="9"/>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M83" s="9"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>237</v>
       </c>
@@ -5754,12 +5847,13 @@
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
-      <c r="H84" s="3" t="s">
+      <c r="H84" s="2"/>
+      <c r="I84" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="I84" s="2"/>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J84" s="2"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
         <v>240</v>
       </c>
@@ -5777,14 +5871,15 @@
       </c>
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
-      <c r="H85" s="7" t="s">
+      <c r="H85" s="6"/>
+      <c r="I85" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="I85" s="8"/>
-      <c r="J85" s="9"/>
+      <c r="J85" s="8"/>
       <c r="K85" s="9"/>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L85" s="9"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>243</v>
       </c>
@@ -5802,12 +5897,13 @@
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
-      <c r="H86" s="3" t="s">
+      <c r="H86" s="2"/>
+      <c r="I86" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="I86" s="2"/>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J86" s="2"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>246</v>
       </c>
@@ -5825,12 +5921,13 @@
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
-      <c r="H87" s="3" t="s">
+      <c r="H87" s="2"/>
+      <c r="I87" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="I87" s="2"/>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J87" s="2"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>249</v>
       </c>
@@ -5848,14 +5945,15 @@
       </c>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
-      <c r="H88" s="7" t="s">
+      <c r="H88" s="6"/>
+      <c r="I88" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="I88" s="8"/>
-      <c r="J88" s="9"/>
+      <c r="J88" s="8"/>
       <c r="K88" s="9"/>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L88" s="9"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>252</v>
       </c>
@@ -5873,12 +5971,13 @@
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
-      <c r="H89" s="3" t="s">
+      <c r="H89" s="2"/>
+      <c r="I89" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="I89" s="2"/>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J89" s="2"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>256</v>
       </c>
@@ -5896,12 +5995,13 @@
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
-      <c r="H90" s="3" t="s">
+      <c r="H90" s="2"/>
+      <c r="I90" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="I90" s="2"/>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J90" s="2"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>259</v>
       </c>
@@ -5919,12 +6019,13 @@
       </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
-      <c r="H91" s="3" t="s">
+      <c r="H91" s="2"/>
+      <c r="I91" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="I91" s="2"/>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J91" s="2"/>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>262</v>
       </c>
@@ -5942,12 +6043,13 @@
       </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
-      <c r="H92" s="3" t="s">
+      <c r="H92" s="2"/>
+      <c r="I92" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="I92" s="2"/>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J92" s="2"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>265</v>
       </c>
@@ -5965,12 +6067,13 @@
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
-      <c r="H93" s="3" t="s">
+      <c r="H93" s="2"/>
+      <c r="I93" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="I93" s="2"/>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J93" s="2"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>268</v>
       </c>
@@ -5988,12 +6091,13 @@
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
-      <c r="H94" s="3" t="s">
+      <c r="H94" s="2"/>
+      <c r="I94" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="I94" s="2"/>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J94" s="2"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>271</v>
       </c>
@@ -6011,12 +6115,13 @@
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
-      <c r="H95" s="3" t="s">
+      <c r="H95" s="2"/>
+      <c r="I95" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="I95" s="2"/>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J95" s="2"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>274</v>
       </c>
@@ -6034,12 +6139,13 @@
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
-      <c r="H96" s="3" t="s">
+      <c r="H96" s="2"/>
+      <c r="I96" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="I96" s="2"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J96" s="2"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>277</v>
       </c>
@@ -6057,12 +6163,13 @@
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="3" t="s">
+      <c r="H97" s="2"/>
+      <c r="I97" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="I97" s="2"/>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J97" s="2"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>280</v>
       </c>
@@ -6080,12 +6187,13 @@
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="3" t="s">
+      <c r="H98" s="2"/>
+      <c r="I98" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="I98" s="2"/>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J98" s="2"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>283</v>
       </c>
@@ -6103,12 +6211,13 @@
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
-      <c r="H99" s="3" t="s">
+      <c r="H99" s="2"/>
+      <c r="I99" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="I99" s="2"/>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J99" s="2"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>286</v>
       </c>
@@ -6126,12 +6235,13 @@
       </c>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
-      <c r="H100" s="3" t="s">
+      <c r="H100" s="2"/>
+      <c r="I100" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="I100" s="2"/>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J100" s="2"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>289</v>
       </c>
@@ -6149,12 +6259,13 @@
       </c>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
-      <c r="H101" s="3" t="s">
+      <c r="H101" s="2"/>
+      <c r="I101" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="I101" s="2"/>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J101" s="2"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>292</v>
       </c>
@@ -6172,12 +6283,13 @@
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
-      <c r="H102" s="3" t="s">
+      <c r="H102" s="2"/>
+      <c r="I102" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="I102" s="2"/>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J102" s="2"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>295</v>
       </c>
@@ -6195,12 +6307,13 @@
       </c>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
-      <c r="H103" s="3" t="s">
+      <c r="H103" s="2"/>
+      <c r="I103" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="I103" s="2"/>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J103" s="2"/>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>298</v>
       </c>
@@ -6218,12 +6331,13 @@
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
-      <c r="H104" s="3" t="s">
+      <c r="H104" s="2"/>
+      <c r="I104" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="I104" s="2"/>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J104" s="2"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>301</v>
       </c>
@@ -6241,12 +6355,13 @@
       </c>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
-      <c r="H105" s="3" t="s">
+      <c r="H105" s="2"/>
+      <c r="I105" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="I105" s="2"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J105" s="2"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>304</v>
       </c>
@@ -6264,12 +6379,13 @@
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
-      <c r="H106" s="3" t="s">
+      <c r="H106" s="2"/>
+      <c r="I106" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="I106" s="2"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J106" s="2"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>307</v>
       </c>
@@ -6287,12 +6403,13 @@
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
-      <c r="H107" s="3" t="s">
+      <c r="H107" s="2"/>
+      <c r="I107" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="I107" s="2"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J107" s="2"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>310</v>
       </c>
@@ -6310,12 +6427,13 @@
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
-      <c r="H108" s="3" t="s">
+      <c r="H108" s="2"/>
+      <c r="I108" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="I108" s="2"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J108" s="2"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>313</v>
       </c>
@@ -6333,12 +6451,13 @@
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
-      <c r="H109" s="3" t="s">
+      <c r="H109" s="2"/>
+      <c r="I109" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="I109" s="2"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J109" s="2"/>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>316</v>
       </c>
@@ -6356,12 +6475,13 @@
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
-      <c r="H110" s="3" t="s">
+      <c r="H110" s="2"/>
+      <c r="I110" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="I110" s="2"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J110" s="2"/>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>319</v>
       </c>
@@ -6379,12 +6499,13 @@
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
-      <c r="H111" s="3" t="s">
+      <c r="H111" s="2"/>
+      <c r="I111" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="I111" s="2"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J111" s="2"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>322</v>
       </c>
@@ -6402,12 +6523,13 @@
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
-      <c r="H112" s="3" t="s">
+      <c r="H112" s="2"/>
+      <c r="I112" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="I112" s="2"/>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J112" s="2"/>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>325</v>
       </c>
@@ -6425,12 +6547,13 @@
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
-      <c r="H113" s="3" t="s">
+      <c r="H113" s="2"/>
+      <c r="I113" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="I113" s="2"/>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J113" s="2"/>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>328</v>
       </c>
@@ -6448,12 +6571,13 @@
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
-      <c r="H114" s="3" t="s">
+      <c r="H114" s="2"/>
+      <c r="I114" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="I114" s="2"/>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J114" s="2"/>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>331</v>
       </c>
@@ -6471,12 +6595,13 @@
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
-      <c r="H115" s="3" t="s">
+      <c r="H115" s="2"/>
+      <c r="I115" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="I115" s="2"/>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J115" s="2"/>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>334</v>
       </c>
@@ -6494,12 +6619,13 @@
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
-      <c r="H116" s="3" t="s">
+      <c r="H116" s="2"/>
+      <c r="I116" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="I116" s="2"/>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J116" s="2"/>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>337</v>
       </c>
@@ -6517,12 +6643,13 @@
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
-      <c r="H117" s="3" t="s">
+      <c r="H117" s="2"/>
+      <c r="I117" s="3" t="s">
         <v>1110</v>
       </c>
-      <c r="I117" s="2"/>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J117" s="2"/>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>338</v>
       </c>
@@ -6540,12 +6667,13 @@
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
-      <c r="H118" s="3" t="s">
+      <c r="H118" s="2"/>
+      <c r="I118" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="I118" s="2"/>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J118" s="2"/>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>341</v>
       </c>
@@ -6563,12 +6691,13 @@
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
-      <c r="H119" s="3" t="s">
+      <c r="H119" s="2"/>
+      <c r="I119" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="I119" s="2"/>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J119" s="2"/>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>344</v>
       </c>
@@ -6586,12 +6715,13 @@
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
-      <c r="H120" s="3" t="s">
+      <c r="H120" s="2"/>
+      <c r="I120" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="I120" s="2"/>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J120" s="2"/>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>347</v>
       </c>
@@ -6609,12 +6739,13 @@
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
-      <c r="H121" s="3" t="s">
+      <c r="H121" s="2"/>
+      <c r="I121" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="I121" s="2"/>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J121" s="2"/>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>350</v>
       </c>
@@ -6632,12 +6763,13 @@
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
-      <c r="H122" s="3" t="s">
+      <c r="H122" s="2"/>
+      <c r="I122" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="I122" s="2"/>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J122" s="2"/>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>353</v>
       </c>
@@ -6655,12 +6787,13 @@
       </c>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
-      <c r="H123" s="3" t="s">
+      <c r="H123" s="2"/>
+      <c r="I123" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="I123" s="2"/>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J123" s="2"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>356</v>
       </c>
@@ -6678,12 +6811,13 @@
       </c>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
-      <c r="H124" s="3" t="s">
+      <c r="H124" s="2"/>
+      <c r="I124" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="I124" s="2"/>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J124" s="2"/>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>359</v>
       </c>
@@ -6701,12 +6835,13 @@
       </c>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
-      <c r="H125" s="3" t="s">
+      <c r="H125" s="2"/>
+      <c r="I125" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="I125" s="2"/>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J125" s="2"/>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>362</v>
       </c>
@@ -6724,12 +6859,13 @@
       </c>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
-      <c r="H126" s="3" t="s">
+      <c r="H126" s="2"/>
+      <c r="I126" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="I126" s="2"/>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J126" s="2"/>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>365</v>
       </c>
@@ -6747,12 +6883,13 @@
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
-      <c r="H127" s="3" t="s">
+      <c r="H127" s="2"/>
+      <c r="I127" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="I127" s="2"/>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J127" s="2"/>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>368</v>
       </c>
@@ -6770,12 +6907,13 @@
       </c>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
-      <c r="H128" s="3" t="s">
+      <c r="H128" s="2"/>
+      <c r="I128" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="I128" s="2"/>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J128" s="2"/>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>371</v>
       </c>
@@ -6793,12 +6931,13 @@
       </c>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
-      <c r="H129" s="3" t="s">
+      <c r="H129" s="2"/>
+      <c r="I129" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="I129" s="2"/>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J129" s="2"/>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>374</v>
       </c>
@@ -6816,12 +6955,13 @@
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
-      <c r="H130" s="3" t="s">
+      <c r="H130" s="2"/>
+      <c r="I130" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="I130" s="2"/>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J130" s="2"/>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>377</v>
       </c>
@@ -6839,12 +6979,13 @@
       </c>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
-      <c r="H131" s="3" t="s">
+      <c r="H131" s="2"/>
+      <c r="I131" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="I131" s="2"/>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J131" s="2"/>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>380</v>
       </c>
@@ -6862,12 +7003,13 @@
       </c>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
-      <c r="H132" s="3" t="s">
+      <c r="H132" s="2"/>
+      <c r="I132" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="I132" s="2"/>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J132" s="2"/>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>383</v>
       </c>
@@ -6885,12 +7027,13 @@
       </c>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
-      <c r="H133" s="3" t="s">
+      <c r="H133" s="2"/>
+      <c r="I133" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="I133" s="2"/>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J133" s="2"/>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>386</v>
       </c>
@@ -6908,12 +7051,13 @@
       </c>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
-      <c r="H134" s="3" t="s">
+      <c r="H134" s="2"/>
+      <c r="I134" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="I134" s="2"/>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J134" s="2"/>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>389</v>
       </c>
@@ -6931,12 +7075,13 @@
       </c>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
-      <c r="H135" s="3" t="s">
+      <c r="H135" s="2"/>
+      <c r="I135" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="I135" s="2"/>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J135" s="2"/>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>392</v>
       </c>
@@ -6954,12 +7099,13 @@
       </c>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
-      <c r="H136" s="3" t="s">
+      <c r="H136" s="2"/>
+      <c r="I136" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="I136" s="2"/>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J136" s="2"/>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>395</v>
       </c>
@@ -6977,12 +7123,13 @@
       </c>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
-      <c r="H137" s="3" t="s">
+      <c r="H137" s="2"/>
+      <c r="I137" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="I137" s="2"/>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J137" s="2"/>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>398</v>
       </c>
@@ -7000,12 +7147,13 @@
       </c>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
-      <c r="H138" s="3" t="s">
+      <c r="H138" s="2"/>
+      <c r="I138" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="I138" s="2"/>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J138" s="2"/>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>401</v>
       </c>
@@ -7023,12 +7171,13 @@
       </c>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
-      <c r="H139" s="3" t="s">
+      <c r="H139" s="2"/>
+      <c r="I139" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="I139" s="2"/>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J139" s="2"/>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>404</v>
       </c>
@@ -7046,12 +7195,13 @@
       </c>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
-      <c r="H140" s="3" t="s">
+      <c r="H140" s="2"/>
+      <c r="I140" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="I140" s="2"/>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J140" s="2"/>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>407</v>
       </c>
@@ -7069,12 +7219,13 @@
       </c>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
-      <c r="H141" s="3" t="s">
+      <c r="H141" s="2"/>
+      <c r="I141" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="I141" s="2"/>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J141" s="2"/>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>410</v>
       </c>
@@ -7092,12 +7243,13 @@
       </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
-      <c r="H142" s="3" t="s">
+      <c r="H142" s="2"/>
+      <c r="I142" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="I142" s="2"/>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J142" s="2"/>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>413</v>
       </c>
@@ -7115,12 +7267,13 @@
       </c>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
-      <c r="H143" s="3" t="s">
+      <c r="H143" s="2"/>
+      <c r="I143" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="I143" s="2"/>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J143" s="2"/>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>416</v>
       </c>
@@ -7138,12 +7291,13 @@
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
-      <c r="H144" s="3" t="s">
+      <c r="H144" s="2"/>
+      <c r="I144" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="I144" s="2"/>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J144" s="2"/>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>419</v>
       </c>
@@ -7161,12 +7315,13 @@
       </c>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
-      <c r="H145" s="3" t="s">
+      <c r="H145" s="2"/>
+      <c r="I145" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="I145" s="2"/>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J145" s="2"/>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>422</v>
       </c>
@@ -7184,12 +7339,13 @@
       </c>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
-      <c r="H146" s="3" t="s">
+      <c r="H146" s="2"/>
+      <c r="I146" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="I146" s="2"/>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J146" s="2"/>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>425</v>
       </c>
@@ -7207,12 +7363,13 @@
       </c>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
-      <c r="H147" s="3" t="s">
+      <c r="H147" s="2"/>
+      <c r="I147" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="I147" s="2"/>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J147" s="2"/>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>429</v>
       </c>
@@ -7230,12 +7387,13 @@
       </c>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
-      <c r="H148" s="3" t="s">
+      <c r="H148" s="2"/>
+      <c r="I148" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="I148" s="2"/>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J148" s="2"/>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>433</v>
       </c>
@@ -7253,12 +7411,13 @@
       </c>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
-      <c r="H149" s="3" t="s">
+      <c r="H149" s="2"/>
+      <c r="I149" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="I149" s="2"/>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J149" s="2"/>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>436</v>
       </c>
@@ -7276,12 +7435,13 @@
       </c>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
-      <c r="H150" s="3" t="s">
+      <c r="H150" s="2"/>
+      <c r="I150" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="I150" s="2"/>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J150" s="2"/>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>439</v>
       </c>
@@ -7299,12 +7459,13 @@
       </c>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
-      <c r="H151" s="3" t="s">
+      <c r="H151" s="2"/>
+      <c r="I151" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="I151" s="2"/>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J151" s="2"/>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>442</v>
       </c>
@@ -7322,12 +7483,13 @@
       </c>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
-      <c r="H152" s="3" t="s">
+      <c r="H152" s="2"/>
+      <c r="I152" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="I152" s="2"/>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J152" s="2"/>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>445</v>
       </c>
@@ -7345,12 +7507,13 @@
       </c>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
-      <c r="H153" s="3" t="s">
+      <c r="H153" s="2"/>
+      <c r="I153" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="I153" s="2"/>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J153" s="2"/>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>448</v>
       </c>
@@ -7368,12 +7531,13 @@
       </c>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
-      <c r="H154" s="3" t="s">
+      <c r="H154" s="2"/>
+      <c r="I154" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="I154" s="2"/>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J154" s="2"/>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>451</v>
       </c>
@@ -7391,12 +7555,13 @@
       </c>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
-      <c r="H155" s="3" t="s">
+      <c r="H155" s="2"/>
+      <c r="I155" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="I155" s="2"/>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J155" s="2"/>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>454</v>
       </c>
@@ -7414,12 +7579,13 @@
       </c>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
-      <c r="H156" s="3" t="s">
+      <c r="H156" s="2"/>
+      <c r="I156" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="I156" s="2"/>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J156" s="2"/>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>457</v>
       </c>
@@ -7437,12 +7603,13 @@
       </c>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
-      <c r="H157" s="3" t="s">
+      <c r="H157" s="2"/>
+      <c r="I157" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="I157" s="2"/>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J157" s="2"/>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>460</v>
       </c>
@@ -7460,12 +7627,13 @@
       </c>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
-      <c r="H158" s="3" t="s">
+      <c r="H158" s="2"/>
+      <c r="I158" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="I158" s="2"/>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J158" s="2"/>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>463</v>
       </c>
@@ -7483,12 +7651,13 @@
       </c>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
-      <c r="H159" s="3" t="s">
+      <c r="H159" s="2"/>
+      <c r="I159" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="I159" s="2"/>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J159" s="2"/>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>466</v>
       </c>
@@ -7506,12 +7675,13 @@
       </c>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
-      <c r="H160" s="3" t="s">
+      <c r="H160" s="2"/>
+      <c r="I160" s="3" t="s">
         <v>1112</v>
       </c>
-      <c r="I160" s="2"/>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J160" s="2"/>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>467</v>
       </c>
@@ -7529,12 +7699,13 @@
       </c>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
-      <c r="H161" s="3" t="s">
+      <c r="H161" s="2"/>
+      <c r="I161" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="I161" s="2"/>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J161" s="2"/>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>470</v>
       </c>
@@ -7552,12 +7723,13 @@
       </c>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
-      <c r="H162" s="3" t="s">
+      <c r="H162" s="2"/>
+      <c r="I162" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="I162" s="2"/>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J162" s="2"/>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>473</v>
       </c>
@@ -7575,12 +7747,13 @@
       </c>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
-      <c r="H163" s="3" t="s">
+      <c r="H163" s="2"/>
+      <c r="I163" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="I163" s="2"/>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J163" s="2"/>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>476</v>
       </c>
@@ -7598,12 +7771,13 @@
       </c>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
-      <c r="H164" s="3" t="s">
+      <c r="H164" s="2"/>
+      <c r="I164" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="I164" s="2"/>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J164" s="2"/>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>479</v>
       </c>
@@ -7621,12 +7795,13 @@
       </c>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
-      <c r="H165" s="3" t="s">
+      <c r="H165" s="2"/>
+      <c r="I165" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="I165" s="2"/>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J165" s="2"/>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>482</v>
       </c>
@@ -7644,12 +7819,13 @@
       </c>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
-      <c r="H166" s="3" t="s">
+      <c r="H166" s="2"/>
+      <c r="I166" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="I166" s="2"/>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J166" s="2"/>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>485</v>
       </c>
@@ -7667,12 +7843,13 @@
       </c>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
-      <c r="H167" s="3" t="s">
+      <c r="H167" s="2"/>
+      <c r="I167" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="I167" s="2"/>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J167" s="2"/>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>488</v>
       </c>
@@ -7690,12 +7867,13 @@
       </c>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
-      <c r="H168" s="3" t="s">
+      <c r="H168" s="2"/>
+      <c r="I168" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="I168" s="2"/>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J168" s="2"/>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>491</v>
       </c>
@@ -7713,12 +7891,13 @@
       </c>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
-      <c r="H169" s="3" t="s">
+      <c r="H169" s="2"/>
+      <c r="I169" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="I169" s="2"/>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J169" s="2"/>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>494</v>
       </c>
@@ -7736,12 +7915,13 @@
       </c>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
-      <c r="H170" s="3" t="s">
+      <c r="H170" s="2"/>
+      <c r="I170" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="I170" s="2"/>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J170" s="2"/>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>497</v>
       </c>
@@ -7759,12 +7939,13 @@
       </c>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
-      <c r="H171" s="3" t="s">
+      <c r="H171" s="2"/>
+      <c r="I171" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="I171" s="2"/>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J171" s="2"/>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>500</v>
       </c>
@@ -7782,12 +7963,13 @@
       </c>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
-      <c r="H172" s="3" t="s">
+      <c r="H172" s="2"/>
+      <c r="I172" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="I172" s="2"/>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J172" s="2"/>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>503</v>
       </c>
@@ -7805,12 +7987,13 @@
       </c>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
-      <c r="H173" s="3" t="s">
+      <c r="H173" s="2"/>
+      <c r="I173" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="I173" s="2"/>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J173" s="2"/>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>506</v>
       </c>
@@ -7828,12 +8011,13 @@
       </c>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
-      <c r="H174" s="3" t="s">
+      <c r="H174" s="2"/>
+      <c r="I174" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="I174" s="2"/>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J174" s="2"/>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>509</v>
       </c>
@@ -7851,12 +8035,13 @@
       </c>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
-      <c r="H175" s="3" t="s">
+      <c r="H175" s="2"/>
+      <c r="I175" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="I175" s="2"/>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J175" s="2"/>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>512</v>
       </c>
@@ -7874,12 +8059,13 @@
       </c>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
-      <c r="H176" s="3" t="s">
+      <c r="H176" s="2"/>
+      <c r="I176" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="I176" s="2"/>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J176" s="2"/>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>515</v>
       </c>
@@ -7897,12 +8083,13 @@
       </c>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
-      <c r="H177" s="3" t="s">
+      <c r="H177" s="2"/>
+      <c r="I177" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="I177" s="2"/>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J177" s="2"/>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>518</v>
       </c>
@@ -7920,12 +8107,13 @@
       </c>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
-      <c r="H178" s="3" t="s">
+      <c r="H178" s="2"/>
+      <c r="I178" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="I178" s="2"/>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J178" s="2"/>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>521</v>
       </c>
@@ -7941,14 +8129,17 @@
       <c r="E179" s="2">
         <v>4.13</v>
       </c>
-      <c r="F179" s="2"/>
+      <c r="F179" s="2" t="s">
+        <v>1128</v>
+      </c>
       <c r="G179" s="2"/>
-      <c r="H179" s="3" t="s">
+      <c r="H179" s="2"/>
+      <c r="I179" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="I179" s="2"/>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J179" s="2"/>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>524</v>
       </c>
@@ -7966,12 +8157,13 @@
       </c>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
-      <c r="H180" s="3" t="s">
+      <c r="H180" s="2"/>
+      <c r="I180" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="I180" s="2"/>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J180" s="2"/>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>527</v>
       </c>
@@ -7989,12 +8181,13 @@
       </c>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
-      <c r="H181" s="3" t="s">
+      <c r="H181" s="2"/>
+      <c r="I181" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="I181" s="2"/>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J181" s="2"/>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>530</v>
       </c>
@@ -8012,12 +8205,13 @@
       </c>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
-      <c r="H182" s="3" t="s">
+      <c r="H182" s="2"/>
+      <c r="I182" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="I182" s="2"/>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J182" s="2"/>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>533</v>
       </c>
@@ -8035,12 +8229,13 @@
       </c>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
-      <c r="H183" s="3" t="s">
+      <c r="H183" s="2"/>
+      <c r="I183" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="I183" s="2"/>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J183" s="2"/>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>536</v>
       </c>
@@ -8058,12 +8253,13 @@
       </c>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
-      <c r="H184" s="3" t="s">
+      <c r="H184" s="2"/>
+      <c r="I184" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="I184" s="2"/>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J184" s="2"/>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>539</v>
       </c>
@@ -8081,12 +8277,13 @@
       </c>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
-      <c r="H185" s="3" t="s">
+      <c r="H185" s="2"/>
+      <c r="I185" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="I185" s="2"/>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J185" s="2"/>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>542</v>
       </c>
@@ -8104,12 +8301,13 @@
       </c>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
-      <c r="H186" s="3" t="s">
+      <c r="H186" s="2"/>
+      <c r="I186" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="I186" s="2"/>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J186" s="2"/>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>545</v>
       </c>
@@ -8127,12 +8325,13 @@
       </c>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
-      <c r="H187" s="3" t="s">
+      <c r="H187" s="2"/>
+      <c r="I187" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="I187" s="2"/>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J187" s="2"/>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>548</v>
       </c>
@@ -8150,12 +8349,13 @@
       </c>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
-      <c r="H188" s="3" t="s">
+      <c r="H188" s="2"/>
+      <c r="I188" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="I188" s="2"/>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J188" s="2"/>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>551</v>
       </c>
@@ -8173,12 +8373,13 @@
       </c>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
-      <c r="H189" s="3" t="s">
+      <c r="H189" s="2"/>
+      <c r="I189" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="I189" s="2"/>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J189" s="2"/>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>554</v>
       </c>
@@ -8196,12 +8397,13 @@
       </c>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
-      <c r="H190" s="3" t="s">
+      <c r="H190" s="2"/>
+      <c r="I190" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="I190" s="2"/>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J190" s="2"/>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>557</v>
       </c>
@@ -8219,12 +8421,13 @@
       </c>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
-      <c r="H191" s="3" t="s">
+      <c r="H191" s="2"/>
+      <c r="I191" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="I191" s="2"/>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J191" s="2"/>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>560</v>
       </c>
@@ -8242,12 +8445,13 @@
       </c>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
-      <c r="H192" s="3" t="s">
+      <c r="H192" s="2"/>
+      <c r="I192" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="I192" s="2"/>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J192" s="2"/>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>563</v>
       </c>
@@ -8265,12 +8469,13 @@
       </c>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
-      <c r="H193" s="3" t="s">
+      <c r="H193" s="2"/>
+      <c r="I193" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="I193" s="2"/>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J193" s="2"/>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>566</v>
       </c>
@@ -8288,12 +8493,13 @@
       </c>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
-      <c r="H194" s="3" t="s">
+      <c r="H194" s="2"/>
+      <c r="I194" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="I194" s="2"/>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J194" s="2"/>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>569</v>
       </c>
@@ -8311,12 +8517,13 @@
       </c>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
-      <c r="H195" s="3" t="s">
+      <c r="H195" s="2"/>
+      <c r="I195" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="I195" s="2"/>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J195" s="2"/>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>572</v>
       </c>
@@ -8334,12 +8541,13 @@
       </c>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
-      <c r="H196" s="3" t="s">
+      <c r="H196" s="2"/>
+      <c r="I196" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="I196" s="2"/>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J196" s="2"/>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>575</v>
       </c>
@@ -8357,12 +8565,13 @@
       </c>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
-      <c r="H197" s="3" t="s">
+      <c r="H197" s="2"/>
+      <c r="I197" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="I197" s="2"/>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J197" s="2"/>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>578</v>
       </c>
@@ -8380,12 +8589,13 @@
       </c>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
-      <c r="H198" s="3" t="s">
+      <c r="H198" s="2"/>
+      <c r="I198" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="I198" s="2"/>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J198" s="2"/>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>581</v>
       </c>
@@ -8403,12 +8613,13 @@
       </c>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
-      <c r="H199" s="3" t="s">
+      <c r="H199" s="2"/>
+      <c r="I199" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="I199" s="2"/>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J199" s="2"/>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>584</v>
       </c>
@@ -8426,12 +8637,13 @@
       </c>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
-      <c r="H200" s="3" t="s">
+      <c r="H200" s="2"/>
+      <c r="I200" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="I200" s="2"/>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J200" s="2"/>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>587</v>
       </c>
@@ -8449,12 +8661,13 @@
       </c>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
-      <c r="H201" s="3" t="s">
+      <c r="H201" s="2"/>
+      <c r="I201" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="I201" s="2"/>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J201" s="2"/>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>590</v>
       </c>
@@ -8472,12 +8685,13 @@
       </c>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
-      <c r="H202" s="3" t="s">
+      <c r="H202" s="2"/>
+      <c r="I202" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="I202" s="2"/>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J202" s="2"/>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>593</v>
       </c>
@@ -8495,12 +8709,13 @@
       </c>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
-      <c r="H203" s="3" t="s">
+      <c r="H203" s="2"/>
+      <c r="I203" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="I203" s="2"/>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J203" s="2"/>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>596</v>
       </c>
@@ -8518,12 +8733,13 @@
       </c>
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
-      <c r="H204" s="3" t="s">
+      <c r="H204" s="2"/>
+      <c r="I204" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="I204" s="2"/>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J204" s="2"/>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" s="6" t="s">
         <v>599</v>
       </c>
@@ -8541,13 +8757,14 @@
       </c>
       <c r="F205" s="6"/>
       <c r="G205" s="6"/>
-      <c r="H205" s="7" t="s">
+      <c r="H205" s="6"/>
+      <c r="I205" s="7" t="s">
         <v>601</v>
       </c>
-      <c r="I205" s="8"/>
-      <c r="J205" s="9"/>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J205" s="8"/>
+      <c r="K205" s="9"/>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" s="5">
         <v>70109</v>
       </c>
@@ -8565,13 +8782,14 @@
       </c>
       <c r="F206" s="6"/>
       <c r="G206" s="6"/>
-      <c r="H206" s="7" t="s">
+      <c r="H206" s="6"/>
+      <c r="I206" s="7" t="s">
         <v>603</v>
       </c>
-      <c r="I206" s="8"/>
-      <c r="J206" s="9"/>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J206" s="8"/>
+      <c r="K206" s="9"/>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>604</v>
       </c>
@@ -8589,12 +8807,13 @@
       </c>
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
-      <c r="H207" s="3" t="s">
+      <c r="H207" s="2"/>
+      <c r="I207" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="I207" s="2"/>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J207" s="2"/>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>607</v>
       </c>
@@ -8612,12 +8831,13 @@
       </c>
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
-      <c r="H208" s="3" t="s">
+      <c r="H208" s="2"/>
+      <c r="I208" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="I208" s="2"/>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J208" s="2"/>
+    </row>
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>610</v>
       </c>
@@ -8635,12 +8855,13 @@
       </c>
       <c r="F209" s="2"/>
       <c r="G209" s="2"/>
-      <c r="H209" s="3" t="s">
+      <c r="H209" s="2"/>
+      <c r="I209" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="I209" s="2"/>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J209" s="2"/>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>613</v>
       </c>
@@ -8658,12 +8879,13 @@
       </c>
       <c r="F210" s="2"/>
       <c r="G210" s="2"/>
-      <c r="H210" s="3" t="s">
+      <c r="H210" s="2"/>
+      <c r="I210" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="I210" s="2"/>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J210" s="2"/>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>616</v>
       </c>
@@ -8681,12 +8903,13 @@
       </c>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
-      <c r="H211" s="3" t="s">
+      <c r="H211" s="2"/>
+      <c r="I211" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="I211" s="2"/>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J211" s="2"/>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>619</v>
       </c>
@@ -8704,12 +8927,13 @@
       </c>
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
-      <c r="H212" s="3" t="s">
+      <c r="H212" s="2"/>
+      <c r="I212" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="I212" s="2"/>
-    </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J212" s="2"/>
+    </row>
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>622</v>
       </c>
@@ -8727,12 +8951,13 @@
       </c>
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
-      <c r="H213" s="3" t="s">
+      <c r="H213" s="2"/>
+      <c r="I213" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="I213" s="2"/>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J213" s="2"/>
+    </row>
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>625</v>
       </c>
@@ -8750,12 +8975,13 @@
       </c>
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
-      <c r="H214" s="3" t="s">
+      <c r="H214" s="2"/>
+      <c r="I214" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="I214" s="2"/>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J214" s="2"/>
+    </row>
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>628</v>
       </c>
@@ -8773,12 +8999,13 @@
       </c>
       <c r="F215" s="2"/>
       <c r="G215" s="2"/>
-      <c r="H215" s="3" t="s">
+      <c r="H215" s="2"/>
+      <c r="I215" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="I215" s="2"/>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J215" s="2"/>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>631</v>
       </c>
@@ -8796,12 +9023,13 @@
       </c>
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
-      <c r="H216" s="3" t="s">
+      <c r="H216" s="2"/>
+      <c r="I216" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="I216" s="2"/>
-    </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J216" s="2"/>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>635</v>
       </c>
@@ -8819,12 +9047,13 @@
       </c>
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
-      <c r="H217" s="3" t="s">
+      <c r="H217" s="2"/>
+      <c r="I217" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="I217" s="2"/>
-    </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J217" s="2"/>
+    </row>
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>638</v>
       </c>
@@ -8842,12 +9071,13 @@
       </c>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
-      <c r="H218" s="3" t="s">
+      <c r="H218" s="2"/>
+      <c r="I218" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="I218" s="2"/>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J218" s="2"/>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>641</v>
       </c>
@@ -8865,12 +9095,13 @@
       </c>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
-      <c r="H219" s="3" t="s">
+      <c r="H219" s="2"/>
+      <c r="I219" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="I219" s="2"/>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J219" s="2"/>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>644</v>
       </c>
@@ -8888,12 +9119,13 @@
       </c>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
-      <c r="H220" s="3" t="s">
+      <c r="H220" s="2"/>
+      <c r="I220" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="I220" s="2"/>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J220" s="2"/>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>647</v>
       </c>
@@ -8911,12 +9143,13 @@
       </c>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
-      <c r="H221" s="3" t="s">
+      <c r="H221" s="2"/>
+      <c r="I221" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="I221" s="2"/>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J221" s="2"/>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>650</v>
       </c>
@@ -8934,12 +9167,13 @@
       </c>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
-      <c r="H222" s="3" t="s">
+      <c r="H222" s="2"/>
+      <c r="I222" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="I222" s="2"/>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J222" s="2"/>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>653</v>
       </c>
@@ -8957,12 +9191,13 @@
       </c>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
-      <c r="H223" s="3" t="s">
+      <c r="H223" s="2"/>
+      <c r="I223" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="I223" s="2"/>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J223" s="2"/>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>656</v>
       </c>
@@ -8980,12 +9215,13 @@
       </c>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
-      <c r="H224" s="3" t="s">
+      <c r="H224" s="2"/>
+      <c r="I224" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="I224" s="2"/>
-    </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J224" s="2"/>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>659</v>
       </c>
@@ -9003,12 +9239,13 @@
       </c>
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
-      <c r="H225" s="3" t="s">
+      <c r="H225" s="2"/>
+      <c r="I225" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="I225" s="2"/>
-    </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J225" s="2"/>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>662</v>
       </c>
@@ -9026,12 +9263,13 @@
       </c>
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
-      <c r="H226" s="3" t="s">
+      <c r="H226" s="2"/>
+      <c r="I226" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="I226" s="2"/>
-    </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J226" s="2"/>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>665</v>
       </c>
@@ -9049,12 +9287,13 @@
       </c>
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
-      <c r="H227" s="3" t="s">
+      <c r="H227" s="2"/>
+      <c r="I227" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="I227" s="2"/>
-    </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J227" s="2"/>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>668</v>
       </c>
@@ -9072,12 +9311,13 @@
       </c>
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
-      <c r="H228" s="3" t="s">
+      <c r="H228" s="2"/>
+      <c r="I228" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="I228" s="2"/>
-    </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J228" s="2"/>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>671</v>
       </c>
@@ -9095,12 +9335,13 @@
       </c>
       <c r="F229" s="2"/>
       <c r="G229" s="2"/>
-      <c r="H229" s="3" t="s">
+      <c r="H229" s="2"/>
+      <c r="I229" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="I229" s="2"/>
-    </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J229" s="2"/>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>674</v>
       </c>
@@ -9118,12 +9359,13 @@
       </c>
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
-      <c r="H230" s="3" t="s">
+      <c r="H230" s="2"/>
+      <c r="I230" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="I230" s="2"/>
-    </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J230" s="2"/>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>677</v>
       </c>
@@ -9141,12 +9383,13 @@
       </c>
       <c r="F231" s="2"/>
       <c r="G231" s="2"/>
-      <c r="H231" s="3" t="s">
+      <c r="H231" s="2"/>
+      <c r="I231" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="I231" s="2"/>
-    </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J231" s="2"/>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A232" s="5">
         <v>30802</v>
       </c>
@@ -9164,15 +9407,16 @@
       </c>
       <c r="F232" s="6"/>
       <c r="G232" s="6"/>
-      <c r="H232" s="7" t="s">
+      <c r="H232" s="6"/>
+      <c r="I232" s="7" t="s">
         <v>681</v>
       </c>
-      <c r="I232" s="8"/>
-      <c r="J232" s="9"/>
+      <c r="J232" s="8"/>
       <c r="K232" s="9"/>
       <c r="L232" s="9"/>
-    </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M232" s="9"/>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>682</v>
       </c>
@@ -9190,12 +9434,13 @@
       </c>
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
-      <c r="H233" s="3" t="s">
+      <c r="H233" s="2"/>
+      <c r="I233" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="I233" s="2"/>
-    </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J233" s="2"/>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>685</v>
       </c>
@@ -9213,12 +9458,13 @@
       </c>
       <c r="F234" s="2"/>
       <c r="G234" s="2"/>
-      <c r="H234" s="3" t="s">
+      <c r="H234" s="2"/>
+      <c r="I234" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="I234" s="2"/>
-    </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J234" s="2"/>
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>688</v>
       </c>
@@ -9236,12 +9482,13 @@
       </c>
       <c r="F235" s="2"/>
       <c r="G235" s="2"/>
-      <c r="H235" s="3" t="s">
+      <c r="H235" s="2"/>
+      <c r="I235" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="I235" s="2"/>
-    </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J235" s="2"/>
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>691</v>
       </c>
@@ -9259,12 +9506,13 @@
       </c>
       <c r="F236" s="2"/>
       <c r="G236" s="2"/>
-      <c r="H236" s="3" t="s">
+      <c r="H236" s="2"/>
+      <c r="I236" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="I236" s="2"/>
-    </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J236" s="2"/>
+    </row>
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>694</v>
       </c>
@@ -9282,12 +9530,13 @@
       </c>
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
-      <c r="H237" s="3" t="s">
+      <c r="H237" s="2"/>
+      <c r="I237" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="I237" s="2"/>
-    </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J237" s="2"/>
+    </row>
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>697</v>
       </c>
@@ -9305,12 +9554,13 @@
       </c>
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
-      <c r="H238" s="3" t="s">
+      <c r="H238" s="2"/>
+      <c r="I238" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="I238" s="2"/>
-    </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J238" s="2"/>
+    </row>
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>700</v>
       </c>
@@ -9328,12 +9578,13 @@
       </c>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
-      <c r="H239" s="3" t="s">
+      <c r="H239" s="2"/>
+      <c r="I239" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="I239" s="2"/>
-    </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J239" s="2"/>
+    </row>
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>703</v>
       </c>
@@ -9351,12 +9602,13 @@
       </c>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
-      <c r="H240" s="3" t="s">
+      <c r="H240" s="2"/>
+      <c r="I240" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="I240" s="2"/>
-    </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J240" s="2"/>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>706</v>
       </c>
@@ -9374,12 +9626,13 @@
       </c>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
-      <c r="H241" s="3" t="s">
+      <c r="H241" s="2"/>
+      <c r="I241" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="I241" s="2"/>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J241" s="2"/>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>709</v>
       </c>
@@ -9397,12 +9650,13 @@
       </c>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
-      <c r="H242" s="3" t="s">
+      <c r="H242" s="2"/>
+      <c r="I242" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="I242" s="2"/>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J242" s="2"/>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>712</v>
       </c>
@@ -9420,12 +9674,13 @@
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
-      <c r="H243" s="3" t="s">
+      <c r="H243" s="2"/>
+      <c r="I243" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="I243" s="2"/>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J243" s="2"/>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>715</v>
       </c>
@@ -9443,12 +9698,13 @@
       </c>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
-      <c r="H244" s="3" t="s">
+      <c r="H244" s="2"/>
+      <c r="I244" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="I244" s="2"/>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J244" s="2"/>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>718</v>
       </c>
@@ -9466,12 +9722,13 @@
       </c>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
-      <c r="H245" s="3" t="s">
+      <c r="H245" s="2"/>
+      <c r="I245" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="I245" s="2"/>
-    </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J245" s="2"/>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>721</v>
       </c>
@@ -9489,12 +9746,13 @@
       </c>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
-      <c r="H246" s="3" t="s">
+      <c r="H246" s="2"/>
+      <c r="I246" s="3" t="s">
         <v>723</v>
       </c>
-      <c r="I246" s="2"/>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J246" s="2"/>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>724</v>
       </c>
@@ -9512,12 +9770,13 @@
       </c>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
-      <c r="H247" s="3" t="s">
+      <c r="H247" s="2"/>
+      <c r="I247" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="I247" s="2"/>
-    </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J247" s="2"/>
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>727</v>
       </c>
@@ -9535,12 +9794,13 @@
       </c>
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
-      <c r="H248" s="3" t="s">
+      <c r="H248" s="2"/>
+      <c r="I248" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="I248" s="2"/>
-    </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J248" s="2"/>
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>730</v>
       </c>
@@ -9558,12 +9818,13 @@
       </c>
       <c r="F249" s="2"/>
       <c r="G249" s="2"/>
-      <c r="H249" s="3" t="s">
+      <c r="H249" s="2"/>
+      <c r="I249" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="I249" s="2"/>
-    </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J249" s="2"/>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>733</v>
       </c>
@@ -9581,12 +9842,13 @@
       </c>
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
-      <c r="H250" s="3" t="s">
+      <c r="H250" s="2"/>
+      <c r="I250" s="3" t="s">
         <v>735</v>
       </c>
-      <c r="I250" s="2"/>
-    </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J250" s="2"/>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>736</v>
       </c>
@@ -9604,12 +9866,13 @@
       </c>
       <c r="F251" s="2"/>
       <c r="G251" s="2"/>
-      <c r="H251" s="3" t="s">
+      <c r="H251" s="2"/>
+      <c r="I251" s="3" t="s">
         <v>738</v>
       </c>
-      <c r="I251" s="2"/>
-    </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J251" s="2"/>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>739</v>
       </c>
@@ -9627,12 +9890,13 @@
       </c>
       <c r="F252" s="2"/>
       <c r="G252" s="2"/>
-      <c r="H252" s="3" t="s">
+      <c r="H252" s="2"/>
+      <c r="I252" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="I252" s="2"/>
-    </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J252" s="2"/>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>742</v>
       </c>
@@ -9650,12 +9914,13 @@
       </c>
       <c r="F253" s="2"/>
       <c r="G253" s="2"/>
-      <c r="H253" s="3" t="s">
+      <c r="H253" s="2"/>
+      <c r="I253" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="I253" s="2"/>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J253" s="2"/>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>745</v>
       </c>
@@ -9673,12 +9938,13 @@
       </c>
       <c r="F254" s="2"/>
       <c r="G254" s="2"/>
-      <c r="H254" s="3" t="s">
+      <c r="H254" s="2"/>
+      <c r="I254" s="3" t="s">
         <v>747</v>
       </c>
-      <c r="I254" s="2"/>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J254" s="2"/>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>748</v>
       </c>
@@ -9694,14 +9960,17 @@
       <c r="E255" s="2">
         <v>6.23</v>
       </c>
-      <c r="F255" s="2"/>
+      <c r="F255" s="2" t="s">
+        <v>1128</v>
+      </c>
       <c r="G255" s="2"/>
-      <c r="H255" s="3" t="s">
+      <c r="H255" s="2"/>
+      <c r="I255" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="I255" s="2"/>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J255" s="2"/>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>751</v>
       </c>
@@ -9719,12 +9988,13 @@
       </c>
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
-      <c r="H256" s="3" t="s">
+      <c r="H256" s="2"/>
+      <c r="I256" s="3" t="s">
         <v>753</v>
       </c>
-      <c r="I256" s="2"/>
-    </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J256" s="2"/>
+    </row>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>754</v>
       </c>
@@ -9742,12 +10012,13 @@
       </c>
       <c r="F257" s="2"/>
       <c r="G257" s="2"/>
-      <c r="H257" s="3" t="s">
+      <c r="H257" s="2"/>
+      <c r="I257" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="I257" s="2"/>
-    </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J257" s="2"/>
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>755</v>
       </c>
@@ -9765,12 +10036,13 @@
       </c>
       <c r="F258" s="2"/>
       <c r="G258" s="2"/>
-      <c r="H258" s="3" t="s">
+      <c r="H258" s="2"/>
+      <c r="I258" s="3" t="s">
         <v>758</v>
       </c>
-      <c r="I258" s="2"/>
-    </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J258" s="2"/>
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>759</v>
       </c>
@@ -9788,12 +10060,13 @@
       </c>
       <c r="F259" s="2"/>
       <c r="G259" s="2"/>
-      <c r="H259" s="3" t="s">
+      <c r="H259" s="2"/>
+      <c r="I259" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="I259" s="2"/>
-    </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J259" s="2"/>
+    </row>
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>762</v>
       </c>
@@ -9811,12 +10084,13 @@
       </c>
       <c r="F260" s="2"/>
       <c r="G260" s="2"/>
-      <c r="H260" s="3" t="s">
+      <c r="H260" s="2"/>
+      <c r="I260" s="3" t="s">
         <v>764</v>
       </c>
-      <c r="I260" s="2"/>
-    </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J260" s="2"/>
+    </row>
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>765</v>
       </c>
@@ -9834,12 +10108,13 @@
       </c>
       <c r="F261" s="2"/>
       <c r="G261" s="2"/>
-      <c r="H261" s="3" t="s">
+      <c r="H261" s="2"/>
+      <c r="I261" s="3" t="s">
         <v>767</v>
       </c>
-      <c r="I261" s="2"/>
-    </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J261" s="2"/>
+    </row>
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>768</v>
       </c>
@@ -9857,12 +10132,13 @@
       </c>
       <c r="F262" s="2"/>
       <c r="G262" s="2"/>
-      <c r="H262" s="3" t="s">
+      <c r="H262" s="2"/>
+      <c r="I262" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="I262" s="2"/>
-    </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J262" s="2"/>
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>771</v>
       </c>
@@ -9880,12 +10156,13 @@
       </c>
       <c r="F263" s="2"/>
       <c r="G263" s="2"/>
-      <c r="H263" s="3" t="s">
+      <c r="H263" s="2"/>
+      <c r="I263" s="3" t="s">
         <v>773</v>
       </c>
-      <c r="I263" s="2"/>
-    </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J263" s="2"/>
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>774</v>
       </c>
@@ -9903,12 +10180,13 @@
       </c>
       <c r="F264" s="2"/>
       <c r="G264" s="2"/>
-      <c r="H264" s="3" t="s">
+      <c r="H264" s="2"/>
+      <c r="I264" s="3" t="s">
         <v>776</v>
       </c>
-      <c r="I264" s="2"/>
-    </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J264" s="2"/>
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>777</v>
       </c>
@@ -9926,12 +10204,13 @@
       </c>
       <c r="F265" s="2"/>
       <c r="G265" s="2"/>
-      <c r="H265" s="3" t="s">
+      <c r="H265" s="2"/>
+      <c r="I265" s="3" t="s">
         <v>779</v>
       </c>
-      <c r="I265" s="2"/>
-    </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J265" s="2"/>
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266" s="5">
         <v>80305</v>
       </c>
@@ -9949,13 +10228,14 @@
       </c>
       <c r="F266" s="6"/>
       <c r="G266" s="6"/>
-      <c r="H266" s="7" t="s">
+      <c r="H266" s="6"/>
+      <c r="I266" s="7" t="s">
         <v>781</v>
       </c>
-      <c r="I266" s="8"/>
-      <c r="J266" s="9"/>
-    </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J266" s="8"/>
+      <c r="K266" s="9"/>
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>782</v>
       </c>
@@ -9973,12 +10253,13 @@
       </c>
       <c r="F267" s="2"/>
       <c r="G267" s="2"/>
-      <c r="H267" s="3" t="s">
+      <c r="H267" s="2"/>
+      <c r="I267" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="I267" s="2"/>
-    </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J267" s="2"/>
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>786</v>
       </c>
@@ -9996,12 +10277,13 @@
       </c>
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
-      <c r="H268" s="3" t="s">
+      <c r="H268" s="2"/>
+      <c r="I268" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="I268" s="2"/>
-    </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J268" s="2"/>
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>789</v>
       </c>
@@ -10019,12 +10301,13 @@
       </c>
       <c r="F269" s="2"/>
       <c r="G269" s="2"/>
-      <c r="H269" s="3" t="s">
+      <c r="H269" s="2"/>
+      <c r="I269" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="I269" s="2"/>
-    </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J269" s="2"/>
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>792</v>
       </c>
@@ -10042,12 +10325,13 @@
       </c>
       <c r="F270" s="2"/>
       <c r="G270" s="2"/>
-      <c r="H270" s="3" t="s">
+      <c r="H270" s="2"/>
+      <c r="I270" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="I270" s="2"/>
-    </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J270" s="2"/>
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>795</v>
       </c>
@@ -10065,12 +10349,13 @@
       </c>
       <c r="F271" s="2"/>
       <c r="G271" s="2"/>
-      <c r="H271" s="3" t="s">
+      <c r="H271" s="2"/>
+      <c r="I271" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="I271" s="2"/>
-    </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J271" s="2"/>
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>798</v>
       </c>
@@ -10088,12 +10373,13 @@
       </c>
       <c r="F272" s="2"/>
       <c r="G272" s="2"/>
-      <c r="H272" s="3" t="s">
+      <c r="H272" s="2"/>
+      <c r="I272" s="3" t="s">
         <v>800</v>
       </c>
-      <c r="I272" s="2"/>
-    </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J272" s="2"/>
+    </row>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>801</v>
       </c>
@@ -10111,12 +10397,13 @@
       </c>
       <c r="F273" s="2"/>
       <c r="G273" s="2"/>
-      <c r="H273" s="3" t="s">
+      <c r="H273" s="2"/>
+      <c r="I273" s="3" t="s">
         <v>803</v>
       </c>
-      <c r="I273" s="2"/>
-    </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J273" s="2"/>
+    </row>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>804</v>
       </c>
@@ -10134,12 +10421,13 @@
       </c>
       <c r="F274" s="2"/>
       <c r="G274" s="2"/>
-      <c r="H274" s="3" t="s">
+      <c r="H274" s="2"/>
+      <c r="I274" s="3" t="s">
         <v>806</v>
       </c>
-      <c r="I274" s="2"/>
-    </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J274" s="2"/>
+    </row>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>807</v>
       </c>
@@ -10157,12 +10445,13 @@
       </c>
       <c r="F275" s="2"/>
       <c r="G275" s="2"/>
-      <c r="H275" s="3" t="s">
+      <c r="H275" s="2"/>
+      <c r="I275" s="3" t="s">
         <v>809</v>
       </c>
-      <c r="I275" s="2"/>
-    </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J275" s="2"/>
+    </row>
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>810</v>
       </c>
@@ -10180,12 +10469,13 @@
       </c>
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
-      <c r="H276" s="3" t="s">
+      <c r="H276" s="2"/>
+      <c r="I276" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="I276" s="2"/>
-    </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J276" s="2"/>
+    </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>813</v>
       </c>
@@ -10203,12 +10493,13 @@
       </c>
       <c r="F277" s="2"/>
       <c r="G277" s="2"/>
-      <c r="H277" s="3" t="s">
+      <c r="H277" s="2"/>
+      <c r="I277" s="3" t="s">
         <v>815</v>
       </c>
-      <c r="I277" s="2"/>
-    </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J277" s="2"/>
+    </row>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>816</v>
       </c>
@@ -10226,12 +10517,13 @@
       </c>
       <c r="F278" s="2"/>
       <c r="G278" s="2"/>
-      <c r="H278" s="3" t="s">
+      <c r="H278" s="2"/>
+      <c r="I278" s="3" t="s">
         <v>818</v>
       </c>
-      <c r="I278" s="2"/>
-    </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J278" s="2"/>
+    </row>
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>819</v>
       </c>
@@ -10249,12 +10541,13 @@
       </c>
       <c r="F279" s="2"/>
       <c r="G279" s="2"/>
-      <c r="H279" s="3" t="s">
+      <c r="H279" s="2"/>
+      <c r="I279" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="I279" s="2"/>
-    </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J279" s="2"/>
+    </row>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>822</v>
       </c>
@@ -10272,12 +10565,13 @@
       </c>
       <c r="F280" s="2"/>
       <c r="G280" s="2"/>
-      <c r="H280" s="3" t="s">
+      <c r="H280" s="2"/>
+      <c r="I280" s="3" t="s">
         <v>824</v>
       </c>
-      <c r="I280" s="2"/>
-    </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J280" s="2"/>
+    </row>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>825</v>
       </c>
@@ -10295,12 +10589,13 @@
       </c>
       <c r="F281" s="2"/>
       <c r="G281" s="2"/>
-      <c r="H281" s="3" t="s">
+      <c r="H281" s="2"/>
+      <c r="I281" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="I281" s="2"/>
-    </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J281" s="2"/>
+    </row>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>828</v>
       </c>
@@ -10318,12 +10613,13 @@
       </c>
       <c r="F282" s="2"/>
       <c r="G282" s="2"/>
-      <c r="H282" s="3" t="s">
+      <c r="H282" s="2"/>
+      <c r="I282" s="3" t="s">
         <v>830</v>
       </c>
-      <c r="I282" s="2"/>
-    </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J282" s="2"/>
+    </row>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>831</v>
       </c>
@@ -10341,12 +10637,13 @@
       </c>
       <c r="F283" s="2"/>
       <c r="G283" s="2"/>
-      <c r="H283" s="3" t="s">
+      <c r="H283" s="2"/>
+      <c r="I283" s="3" t="s">
         <v>833</v>
       </c>
-      <c r="I283" s="2"/>
-    </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J283" s="2"/>
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>834</v>
       </c>
@@ -10364,12 +10661,13 @@
       </c>
       <c r="F284" s="2"/>
       <c r="G284" s="2"/>
-      <c r="H284" s="3" t="s">
+      <c r="H284" s="2"/>
+      <c r="I284" s="3" t="s">
         <v>836</v>
       </c>
-      <c r="I284" s="2"/>
-    </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J284" s="2"/>
+    </row>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>837</v>
       </c>
@@ -10387,12 +10685,13 @@
       </c>
       <c r="F285" s="2"/>
       <c r="G285" s="2"/>
-      <c r="H285" s="3" t="s">
+      <c r="H285" s="2"/>
+      <c r="I285" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="I285" s="2"/>
-    </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J285" s="2"/>
+    </row>
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>840</v>
       </c>
@@ -10410,12 +10709,13 @@
       </c>
       <c r="F286" s="2"/>
       <c r="G286" s="2"/>
-      <c r="H286" s="3" t="s">
+      <c r="H286" s="2"/>
+      <c r="I286" s="3" t="s">
         <v>842</v>
       </c>
-      <c r="I286" s="2"/>
-    </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J286" s="2"/>
+    </row>
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>843</v>
       </c>
@@ -10433,12 +10733,13 @@
       </c>
       <c r="F287" s="2"/>
       <c r="G287" s="2"/>
-      <c r="H287" s="3" t="s">
+      <c r="H287" s="2"/>
+      <c r="I287" s="3" t="s">
         <v>845</v>
       </c>
-      <c r="I287" s="2"/>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J287" s="2"/>
+    </row>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>846</v>
       </c>
@@ -10456,12 +10757,13 @@
       </c>
       <c r="F288" s="2"/>
       <c r="G288" s="2"/>
-      <c r="H288" s="3" t="s">
+      <c r="H288" s="2"/>
+      <c r="I288" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="I288" s="2"/>
-    </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J288" s="2"/>
+    </row>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>849</v>
       </c>
@@ -10479,12 +10781,13 @@
       </c>
       <c r="F289" s="2"/>
       <c r="G289" s="2"/>
-      <c r="H289" s="3" t="s">
+      <c r="H289" s="2"/>
+      <c r="I289" s="3" t="s">
         <v>851</v>
       </c>
-      <c r="I289" s="2"/>
-    </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J289" s="2"/>
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>852</v>
       </c>
@@ -10502,12 +10805,13 @@
       </c>
       <c r="F290" s="2"/>
       <c r="G290" s="2"/>
-      <c r="H290" s="3" t="s">
+      <c r="H290" s="2"/>
+      <c r="I290" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="I290" s="2"/>
-    </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J290" s="2"/>
+    </row>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>855</v>
       </c>
@@ -10525,12 +10829,13 @@
       </c>
       <c r="F291" s="2"/>
       <c r="G291" s="2"/>
-      <c r="H291" s="3" t="s">
+      <c r="H291" s="2"/>
+      <c r="I291" s="3" t="s">
         <v>857</v>
       </c>
-      <c r="I291" s="2"/>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J291" s="2"/>
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>858</v>
       </c>
@@ -10548,12 +10853,13 @@
       </c>
       <c r="F292" s="2"/>
       <c r="G292" s="2"/>
-      <c r="H292" s="3" t="s">
+      <c r="H292" s="2"/>
+      <c r="I292" s="3" t="s">
         <v>860</v>
       </c>
-      <c r="I292" s="2"/>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J292" s="2"/>
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>861</v>
       </c>
@@ -10571,12 +10877,13 @@
       </c>
       <c r="F293" s="2"/>
       <c r="G293" s="2"/>
-      <c r="H293" s="3" t="s">
+      <c r="H293" s="2"/>
+      <c r="I293" s="3" t="s">
         <v>863</v>
       </c>
-      <c r="I293" s="2"/>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J293" s="2"/>
+    </row>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>864</v>
       </c>
@@ -10594,12 +10901,13 @@
       </c>
       <c r="F294" s="2"/>
       <c r="G294" s="2"/>
-      <c r="H294" s="3" t="s">
+      <c r="H294" s="2"/>
+      <c r="I294" s="3" t="s">
         <v>866</v>
       </c>
-      <c r="I294" s="2"/>
-    </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J294" s="2"/>
+    </row>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>867</v>
       </c>
@@ -10617,12 +10925,13 @@
       </c>
       <c r="F295" s="2"/>
       <c r="G295" s="2"/>
-      <c r="H295" s="3" t="s">
+      <c r="H295" s="2"/>
+      <c r="I295" s="3" t="s">
         <v>869</v>
       </c>
-      <c r="I295" s="2"/>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J295" s="2"/>
+    </row>
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>870</v>
       </c>
@@ -10640,12 +10949,13 @@
       </c>
       <c r="F296" s="2"/>
       <c r="G296" s="2"/>
-      <c r="H296" s="3" t="s">
+      <c r="H296" s="2"/>
+      <c r="I296" s="3" t="s">
         <v>872</v>
       </c>
-      <c r="I296" s="2"/>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J296" s="2"/>
+    </row>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>873</v>
       </c>
@@ -10663,12 +10973,13 @@
       </c>
       <c r="F297" s="2"/>
       <c r="G297" s="2"/>
-      <c r="H297" s="3" t="s">
+      <c r="H297" s="2"/>
+      <c r="I297" s="3" t="s">
         <v>875</v>
       </c>
-      <c r="I297" s="2"/>
-    </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J297" s="2"/>
+    </row>
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>876</v>
       </c>
@@ -10686,12 +10997,13 @@
       </c>
       <c r="F298" s="2"/>
       <c r="G298" s="2"/>
-      <c r="H298" s="3" t="s">
+      <c r="H298" s="2"/>
+      <c r="I298" s="3" t="s">
         <v>878</v>
       </c>
-      <c r="I298" s="2"/>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J298" s="2"/>
+    </row>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>879</v>
       </c>
@@ -10709,12 +11021,13 @@
       </c>
       <c r="F299" s="2"/>
       <c r="G299" s="2"/>
-      <c r="H299" s="3" t="s">
+      <c r="H299" s="2"/>
+      <c r="I299" s="3" t="s">
         <v>881</v>
       </c>
-      <c r="I299" s="2"/>
-    </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J299" s="2"/>
+    </row>
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>882</v>
       </c>
@@ -10732,12 +11045,13 @@
       </c>
       <c r="F300" s="2"/>
       <c r="G300" s="2"/>
-      <c r="H300" s="3" t="s">
+      <c r="H300" s="2"/>
+      <c r="I300" s="3" t="s">
         <v>884</v>
       </c>
-      <c r="I300" s="2"/>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J300" s="2"/>
+    </row>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>885</v>
       </c>
@@ -10755,12 +11069,13 @@
       </c>
       <c r="F301" s="2"/>
       <c r="G301" s="2"/>
-      <c r="H301" s="3" t="s">
+      <c r="H301" s="2"/>
+      <c r="I301" s="3" t="s">
         <v>887</v>
       </c>
-      <c r="I301" s="2"/>
-    </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J301" s="2"/>
+    </row>
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>888</v>
       </c>
@@ -10778,12 +11093,13 @@
       </c>
       <c r="F302" s="2"/>
       <c r="G302" s="2"/>
-      <c r="H302" s="3" t="s">
+      <c r="H302" s="2"/>
+      <c r="I302" s="3" t="s">
         <v>890</v>
       </c>
-      <c r="I302" s="2"/>
-    </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J302" s="2"/>
+    </row>
+    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>891</v>
       </c>
@@ -10799,14 +11115,17 @@
       <c r="E303" s="2">
         <v>4.83</v>
       </c>
-      <c r="F303" s="2"/>
+      <c r="F303" s="2" t="s">
+        <v>1128</v>
+      </c>
       <c r="G303" s="2"/>
-      <c r="H303" s="3" t="s">
+      <c r="H303" s="2"/>
+      <c r="I303" s="3" t="s">
         <v>893</v>
       </c>
-      <c r="I303" s="2"/>
-    </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J303" s="2"/>
+    </row>
+    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>894</v>
       </c>
@@ -10824,12 +11143,13 @@
       </c>
       <c r="F304" s="2"/>
       <c r="G304" s="2"/>
-      <c r="H304" s="3" t="s">
+      <c r="H304" s="2"/>
+      <c r="I304" s="3" t="s">
         <v>896</v>
       </c>
-      <c r="I304" s="2"/>
-    </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J304" s="2"/>
+    </row>
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>897</v>
       </c>
@@ -10847,12 +11167,13 @@
       </c>
       <c r="F305" s="2"/>
       <c r="G305" s="2"/>
-      <c r="H305" s="3" t="s">
+      <c r="H305" s="2"/>
+      <c r="I305" s="3" t="s">
         <v>899</v>
       </c>
-      <c r="I305" s="2"/>
-    </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J305" s="2"/>
+    </row>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>900</v>
       </c>
@@ -10870,12 +11191,13 @@
       </c>
       <c r="F306" s="2"/>
       <c r="G306" s="2"/>
-      <c r="H306" s="3" t="s">
+      <c r="H306" s="2"/>
+      <c r="I306" s="3" t="s">
         <v>902</v>
       </c>
-      <c r="I306" s="2"/>
-    </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J306" s="2"/>
+    </row>
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>903</v>
       </c>
@@ -10893,12 +11215,13 @@
       </c>
       <c r="F307" s="2"/>
       <c r="G307" s="2"/>
-      <c r="H307" s="3" t="s">
+      <c r="H307" s="2"/>
+      <c r="I307" s="3" t="s">
         <v>905</v>
       </c>
-      <c r="I307" s="2"/>
-    </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J307" s="2"/>
+    </row>
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>906</v>
       </c>
@@ -10916,12 +11239,13 @@
       </c>
       <c r="F308" s="2"/>
       <c r="G308" s="2"/>
-      <c r="H308" s="3" t="s">
+      <c r="H308" s="2"/>
+      <c r="I308" s="3" t="s">
         <v>908</v>
       </c>
-      <c r="I308" s="2"/>
-    </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J308" s="2"/>
+    </row>
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>909</v>
       </c>
@@ -10939,12 +11263,13 @@
       </c>
       <c r="F309" s="2"/>
       <c r="G309" s="2"/>
-      <c r="H309" s="3" t="s">
+      <c r="H309" s="2"/>
+      <c r="I309" s="3" t="s">
         <v>911</v>
       </c>
-      <c r="I309" s="2"/>
-    </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J309" s="2"/>
+    </row>
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>912</v>
       </c>
@@ -10962,12 +11287,13 @@
       </c>
       <c r="F310" s="2"/>
       <c r="G310" s="2"/>
-      <c r="H310" s="3" t="s">
+      <c r="H310" s="2"/>
+      <c r="I310" s="3" t="s">
         <v>914</v>
       </c>
-      <c r="I310" s="2"/>
-    </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J310" s="2"/>
+    </row>
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>915</v>
       </c>
@@ -10985,12 +11311,13 @@
       </c>
       <c r="F311" s="2"/>
       <c r="G311" s="2"/>
-      <c r="H311" s="3" t="s">
+      <c r="H311" s="2"/>
+      <c r="I311" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="I311" s="2"/>
-    </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J311" s="2"/>
+    </row>
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>917</v>
       </c>
@@ -11008,14 +11335,19 @@
       </c>
       <c r="F312" s="2"/>
       <c r="G312" s="2"/>
-      <c r="H312" s="3" t="s">
+      <c r="H312" s="2"/>
+      <c r="I312" s="3" t="s">
         <v>919</v>
       </c>
-      <c r="I312" s="2"/>
-    </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A313" s="2"/>
-      <c r="B313" s="2"/>
+      <c r="J312" s="2"/>
+    </row>
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A313" s="13">
+        <v>40505</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>756</v>
+      </c>
       <c r="C313" s="2" t="s">
         <v>1113</v>
       </c>
@@ -11027,12 +11359,13 @@
       </c>
       <c r="F313" s="2"/>
       <c r="G313" s="2"/>
-      <c r="H313" s="3" t="s">
+      <c r="H313" s="2"/>
+      <c r="I313" s="3" t="s">
         <v>1114</v>
       </c>
-      <c r="I313" s="2"/>
-    </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J313" s="2"/>
+    </row>
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>920</v>
       </c>
@@ -11050,12 +11383,13 @@
       </c>
       <c r="F314" s="2"/>
       <c r="G314" s="2"/>
-      <c r="H314" s="3" t="s">
+      <c r="H314" s="2"/>
+      <c r="I314" s="3" t="s">
         <v>922</v>
       </c>
-      <c r="I314" s="2"/>
-    </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J314" s="2"/>
+    </row>
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>923</v>
       </c>
@@ -11073,12 +11407,13 @@
       </c>
       <c r="F315" s="2"/>
       <c r="G315" s="2"/>
-      <c r="H315" s="3" t="s">
+      <c r="H315" s="2"/>
+      <c r="I315" s="3" t="s">
         <v>925</v>
       </c>
-      <c r="I315" s="2"/>
-    </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J315" s="2"/>
+    </row>
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>926</v>
       </c>
@@ -11096,12 +11431,13 @@
       </c>
       <c r="F316" s="2"/>
       <c r="G316" s="2"/>
-      <c r="H316" s="3" t="s">
+      <c r="H316" s="2"/>
+      <c r="I316" s="3" t="s">
         <v>928</v>
       </c>
-      <c r="I316" s="2"/>
-    </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J316" s="2"/>
+    </row>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>929</v>
       </c>
@@ -11119,12 +11455,13 @@
       </c>
       <c r="F317" s="2"/>
       <c r="G317" s="2"/>
-      <c r="H317" s="3" t="s">
+      <c r="H317" s="2"/>
+      <c r="I317" s="3" t="s">
         <v>931</v>
       </c>
-      <c r="I317" s="2"/>
-    </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J317" s="2"/>
+    </row>
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>932</v>
       </c>
@@ -11142,12 +11479,13 @@
       </c>
       <c r="F318" s="2"/>
       <c r="G318" s="2"/>
-      <c r="H318" s="3" t="s">
+      <c r="H318" s="2"/>
+      <c r="I318" s="3" t="s">
         <v>934</v>
       </c>
-      <c r="I318" s="2"/>
-    </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J318" s="2"/>
+    </row>
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>935</v>
       </c>
@@ -11165,12 +11503,13 @@
       </c>
       <c r="F319" s="2"/>
       <c r="G319" s="2"/>
-      <c r="H319" s="3" t="s">
+      <c r="H319" s="2"/>
+      <c r="I319" s="3" t="s">
         <v>937</v>
       </c>
-      <c r="I319" s="2"/>
-    </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J319" s="2"/>
+    </row>
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>938</v>
       </c>
@@ -11188,12 +11527,13 @@
       </c>
       <c r="F320" s="2"/>
       <c r="G320" s="2"/>
-      <c r="H320" s="3" t="s">
+      <c r="H320" s="2"/>
+      <c r="I320" s="3" t="s">
         <v>940</v>
       </c>
-      <c r="I320" s="2"/>
-    </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J320" s="2"/>
+    </row>
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>941</v>
       </c>
@@ -11211,12 +11551,13 @@
       </c>
       <c r="F321" s="2"/>
       <c r="G321" s="2"/>
-      <c r="H321" s="3" t="s">
+      <c r="H321" s="2"/>
+      <c r="I321" s="3" t="s">
         <v>943</v>
       </c>
-      <c r="I321" s="2"/>
-    </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J321" s="2"/>
+    </row>
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>944</v>
       </c>
@@ -11234,12 +11575,13 @@
       </c>
       <c r="F322" s="2"/>
       <c r="G322" s="2"/>
-      <c r="H322" s="3" t="s">
+      <c r="H322" s="2"/>
+      <c r="I322" s="3" t="s">
         <v>946</v>
       </c>
-      <c r="I322" s="2"/>
-    </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J322" s="2"/>
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>947</v>
       </c>
@@ -11257,12 +11599,13 @@
       </c>
       <c r="F323" s="2"/>
       <c r="G323" s="2"/>
-      <c r="H323" s="3" t="s">
+      <c r="H323" s="2"/>
+      <c r="I323" s="3" t="s">
         <v>949</v>
       </c>
-      <c r="I323" s="2"/>
-    </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J323" s="2"/>
+    </row>
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>950</v>
       </c>
@@ -11280,12 +11623,13 @@
       </c>
       <c r="F324" s="2"/>
       <c r="G324" s="2"/>
-      <c r="H324" s="3" t="s">
+      <c r="H324" s="2"/>
+      <c r="I324" s="3" t="s">
         <v>952</v>
       </c>
-      <c r="I324" s="2"/>
-    </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J324" s="2"/>
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>953</v>
       </c>
@@ -11303,12 +11647,13 @@
       </c>
       <c r="F325" s="2"/>
       <c r="G325" s="2"/>
-      <c r="H325" s="3" t="s">
+      <c r="H325" s="2"/>
+      <c r="I325" s="3" t="s">
         <v>955</v>
       </c>
-      <c r="I325" s="2"/>
-    </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J325" s="2"/>
+    </row>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>956</v>
       </c>
@@ -11326,12 +11671,13 @@
       </c>
       <c r="F326" s="2"/>
       <c r="G326" s="2"/>
-      <c r="H326" s="3" t="s">
+      <c r="H326" s="2"/>
+      <c r="I326" s="3" t="s">
         <v>958</v>
       </c>
-      <c r="I326" s="2"/>
-    </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J326" s="2"/>
+    </row>
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>959</v>
       </c>
@@ -11349,12 +11695,13 @@
       </c>
       <c r="F327" s="2"/>
       <c r="G327" s="2"/>
-      <c r="H327" s="3" t="s">
+      <c r="H327" s="2"/>
+      <c r="I327" s="3" t="s">
         <v>961</v>
       </c>
-      <c r="I327" s="2"/>
-    </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J327" s="2"/>
+    </row>
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>962</v>
       </c>
@@ -11372,12 +11719,13 @@
       </c>
       <c r="F328" s="2"/>
       <c r="G328" s="2"/>
-      <c r="H328" s="3" t="s">
+      <c r="H328" s="2"/>
+      <c r="I328" s="3" t="s">
         <v>964</v>
       </c>
-      <c r="I328" s="2"/>
-    </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J328" s="2"/>
+    </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>965</v>
       </c>
@@ -11395,12 +11743,13 @@
       </c>
       <c r="F329" s="2"/>
       <c r="G329" s="2"/>
-      <c r="H329" s="3" t="s">
+      <c r="H329" s="2"/>
+      <c r="I329" s="3" t="s">
         <v>967</v>
       </c>
-      <c r="I329" s="2"/>
-    </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J329" s="2"/>
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>968</v>
       </c>
@@ -11416,14 +11765,17 @@
       <c r="E330" s="2">
         <v>11.83</v>
       </c>
-      <c r="F330" s="2"/>
+      <c r="F330" s="2" t="s">
+        <v>1128</v>
+      </c>
       <c r="G330" s="2"/>
-      <c r="H330" s="3" t="s">
+      <c r="H330" s="2"/>
+      <c r="I330" s="3" t="s">
         <v>970</v>
       </c>
-      <c r="I330" s="2"/>
-    </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J330" s="2"/>
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>971</v>
       </c>
@@ -11441,12 +11793,13 @@
       </c>
       <c r="F331" s="2"/>
       <c r="G331" s="2"/>
-      <c r="H331" s="3" t="s">
+      <c r="H331" s="2"/>
+      <c r="I331" s="3" t="s">
         <v>973</v>
       </c>
-      <c r="I331" s="2"/>
-    </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J331" s="2"/>
+    </row>
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332" s="5">
         <v>100236</v>
       </c>
@@ -11464,13 +11817,14 @@
       </c>
       <c r="F332" s="6"/>
       <c r="G332" s="6"/>
-      <c r="H332" s="7" t="s">
+      <c r="H332" s="6"/>
+      <c r="I332" s="7" t="s">
         <v>975</v>
       </c>
-      <c r="I332" s="8"/>
-      <c r="J332" s="9"/>
-    </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J332" s="8"/>
+      <c r="K332" s="9"/>
+    </row>
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>976</v>
       </c>
@@ -11488,12 +11842,13 @@
       </c>
       <c r="F333" s="2"/>
       <c r="G333" s="2"/>
-      <c r="H333" s="3" t="s">
+      <c r="H333" s="2"/>
+      <c r="I333" s="3" t="s">
         <v>978</v>
       </c>
-      <c r="I333" s="2"/>
-    </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J333" s="2"/>
+    </row>
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>979</v>
       </c>
@@ -11511,12 +11866,13 @@
       </c>
       <c r="F334" s="2"/>
       <c r="G334" s="2"/>
-      <c r="H334" s="3" t="s">
+      <c r="H334" s="2"/>
+      <c r="I334" s="3" t="s">
         <v>981</v>
       </c>
-      <c r="I334" s="2"/>
-    </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J334" s="2"/>
+    </row>
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>982</v>
       </c>
@@ -11534,12 +11890,13 @@
       </c>
       <c r="F335" s="2"/>
       <c r="G335" s="2"/>
-      <c r="H335" s="3" t="s">
+      <c r="H335" s="2"/>
+      <c r="I335" s="3" t="s">
         <v>984</v>
       </c>
-      <c r="I335" s="2"/>
-    </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J335" s="2"/>
+    </row>
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>985</v>
       </c>
@@ -11557,12 +11914,13 @@
       </c>
       <c r="F336" s="2"/>
       <c r="G336" s="2"/>
-      <c r="H336" s="3" t="s">
+      <c r="H336" s="2"/>
+      <c r="I336" s="3" t="s">
         <v>987</v>
       </c>
-      <c r="I336" s="2"/>
-    </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J336" s="2"/>
+    </row>
+    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>988</v>
       </c>
@@ -11580,12 +11938,13 @@
       </c>
       <c r="F337" s="2"/>
       <c r="G337" s="2"/>
-      <c r="H337" s="3" t="s">
+      <c r="H337" s="2"/>
+      <c r="I337" s="3" t="s">
         <v>990</v>
       </c>
-      <c r="I337" s="2"/>
-    </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J337" s="2"/>
+    </row>
+    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>991</v>
       </c>
@@ -11603,12 +11962,13 @@
       </c>
       <c r="F338" s="2"/>
       <c r="G338" s="2"/>
-      <c r="H338" s="3" t="s">
+      <c r="H338" s="2"/>
+      <c r="I338" s="3" t="s">
         <v>993</v>
       </c>
-      <c r="I338" s="2"/>
-    </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J338" s="2"/>
+    </row>
+    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>994</v>
       </c>
@@ -11626,12 +11986,13 @@
       </c>
       <c r="F339" s="2"/>
       <c r="G339" s="2"/>
-      <c r="H339" s="3" t="s">
+      <c r="H339" s="2"/>
+      <c r="I339" s="3" t="s">
         <v>995</v>
       </c>
-      <c r="I339" s="2"/>
-    </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J339" s="2"/>
+    </row>
+    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>996</v>
       </c>
@@ -11649,12 +12010,13 @@
       </c>
       <c r="F340" s="2"/>
       <c r="G340" s="2"/>
-      <c r="H340" s="3" t="s">
+      <c r="H340" s="2"/>
+      <c r="I340" s="3" t="s">
         <v>998</v>
       </c>
-      <c r="I340" s="2"/>
-    </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J340" s="2"/>
+    </row>
+    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>999</v>
       </c>
@@ -11672,12 +12034,13 @@
       </c>
       <c r="F341" s="2"/>
       <c r="G341" s="2"/>
-      <c r="H341" s="3" t="s">
+      <c r="H341" s="2"/>
+      <c r="I341" s="3" t="s">
         <v>1001</v>
       </c>
-      <c r="I341" s="2"/>
-    </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J341" s="2"/>
+    </row>
+    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>1002</v>
       </c>
@@ -11695,12 +12058,13 @@
       </c>
       <c r="F342" s="2"/>
       <c r="G342" s="2"/>
-      <c r="H342" s="3" t="s">
+      <c r="H342" s="2"/>
+      <c r="I342" s="3" t="s">
         <v>1004</v>
       </c>
-      <c r="I342" s="2"/>
-    </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J342" s="2"/>
+    </row>
+    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>1005</v>
       </c>
@@ -11718,12 +12082,13 @@
       </c>
       <c r="F343" s="2"/>
       <c r="G343" s="2"/>
-      <c r="H343" s="3" t="s">
+      <c r="H343" s="2"/>
+      <c r="I343" s="3" t="s">
         <v>1007</v>
       </c>
-      <c r="I343" s="2"/>
-    </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J343" s="2"/>
+    </row>
+    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344" s="5">
         <v>100224</v>
       </c>
@@ -11741,13 +12106,14 @@
       </c>
       <c r="F344" s="6"/>
       <c r="G344" s="6"/>
-      <c r="H344" s="7" t="s">
+      <c r="H344" s="6"/>
+      <c r="I344" s="7" t="s">
         <v>1009</v>
       </c>
-      <c r="I344" s="8"/>
-      <c r="J344" s="9"/>
-    </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J344" s="8"/>
+      <c r="K344" s="9"/>
+    </row>
+    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>1010</v>
       </c>
@@ -11765,12 +12131,13 @@
       </c>
       <c r="F345" s="2"/>
       <c r="G345" s="2"/>
-      <c r="H345" s="3" t="s">
+      <c r="H345" s="2"/>
+      <c r="I345" s="3" t="s">
         <v>1012</v>
       </c>
-      <c r="I345" s="2"/>
-    </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J345" s="2"/>
+    </row>
+    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>1013</v>
       </c>
@@ -11788,12 +12155,13 @@
       </c>
       <c r="F346" s="2"/>
       <c r="G346" s="2"/>
-      <c r="H346" s="3" t="s">
+      <c r="H346" s="2"/>
+      <c r="I346" s="3" t="s">
         <v>1015</v>
       </c>
-      <c r="I346" s="2"/>
-    </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J346" s="2"/>
+    </row>
+    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>1016</v>
       </c>
@@ -11811,12 +12179,13 @@
       </c>
       <c r="F347" s="2"/>
       <c r="G347" s="2"/>
-      <c r="H347" s="3" t="s">
+      <c r="H347" s="2"/>
+      <c r="I347" s="3" t="s">
         <v>1018</v>
       </c>
-      <c r="I347" s="2"/>
-    </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J347" s="2"/>
+    </row>
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>1019</v>
       </c>
@@ -11834,12 +12203,13 @@
       </c>
       <c r="F348" s="2"/>
       <c r="G348" s="2"/>
-      <c r="H348" s="3" t="s">
+      <c r="H348" s="2"/>
+      <c r="I348" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="I348" s="2"/>
-    </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J348" s="2"/>
+    </row>
+    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>1021</v>
       </c>
@@ -11857,12 +12227,13 @@
       </c>
       <c r="F349" s="2"/>
       <c r="G349" s="2"/>
-      <c r="H349" s="3" t="s">
+      <c r="H349" s="2"/>
+      <c r="I349" s="3" t="s">
         <v>1023</v>
       </c>
-      <c r="I349" s="2"/>
-    </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J349" s="2"/>
+    </row>
+    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>1024</v>
       </c>
@@ -11880,12 +12251,13 @@
       </c>
       <c r="F350" s="2"/>
       <c r="G350" s="2"/>
-      <c r="H350" s="3" t="s">
+      <c r="H350" s="2"/>
+      <c r="I350" s="3" t="s">
         <v>1026</v>
       </c>
-      <c r="I350" s="2"/>
-    </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J350" s="2"/>
+    </row>
+    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>1027</v>
       </c>
@@ -11903,12 +12275,13 @@
       </c>
       <c r="F351" s="2"/>
       <c r="G351" s="2"/>
-      <c r="H351" s="3" t="s">
+      <c r="H351" s="2"/>
+      <c r="I351" s="3" t="s">
         <v>1029</v>
       </c>
-      <c r="I351" s="2"/>
-    </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J351" s="2"/>
+    </row>
+    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A352" s="13">
         <v>100218</v>
       </c>
@@ -11926,10 +12299,11 @@
       </c>
       <c r="F352" s="2"/>
       <c r="G352" s="2"/>
-      <c r="H352" s="3"/>
-      <c r="I352" s="2"/>
-    </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H352" s="2"/>
+      <c r="I352" s="3"/>
+      <c r="J352" s="2"/>
+    </row>
+    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>1030</v>
       </c>
@@ -11947,12 +12321,13 @@
       </c>
       <c r="F353" s="2"/>
       <c r="G353" s="2"/>
-      <c r="H353" s="3" t="s">
+      <c r="H353" s="2"/>
+      <c r="I353" s="3" t="s">
         <v>1032</v>
       </c>
-      <c r="I353" s="2"/>
-    </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J353" s="2"/>
+    </row>
+    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>1033</v>
       </c>
@@ -11970,12 +12345,13 @@
       </c>
       <c r="F354" s="2"/>
       <c r="G354" s="2"/>
-      <c r="H354" s="3" t="s">
+      <c r="H354" s="2"/>
+      <c r="I354" s="3" t="s">
         <v>1035</v>
       </c>
-      <c r="I354" s="2"/>
-    </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J354" s="2"/>
+    </row>
+    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>1036</v>
       </c>
@@ -11993,12 +12369,13 @@
       </c>
       <c r="F355" s="2"/>
       <c r="G355" s="2"/>
-      <c r="H355" s="3" t="s">
+      <c r="H355" s="2"/>
+      <c r="I355" s="3" t="s">
         <v>1038</v>
       </c>
-      <c r="I355" s="2"/>
-    </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J355" s="2"/>
+    </row>
+    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>1039</v>
       </c>
@@ -12016,12 +12393,13 @@
       </c>
       <c r="F356" s="2"/>
       <c r="G356" s="2"/>
-      <c r="H356" s="3" t="s">
+      <c r="H356" s="2"/>
+      <c r="I356" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="I356" s="2"/>
-    </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J356" s="2"/>
+    </row>
+    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>1042</v>
       </c>
@@ -12039,12 +12417,13 @@
       </c>
       <c r="F357" s="2"/>
       <c r="G357" s="2"/>
-      <c r="H357" s="3" t="s">
+      <c r="H357" s="2"/>
+      <c r="I357" s="3" t="s">
         <v>1044</v>
       </c>
-      <c r="I357" s="2"/>
-    </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J357" s="2"/>
+    </row>
+    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>1045</v>
       </c>
@@ -12062,12 +12441,13 @@
       </c>
       <c r="F358" s="2"/>
       <c r="G358" s="2"/>
-      <c r="H358" s="3" t="s">
+      <c r="H358" s="2"/>
+      <c r="I358" s="3" t="s">
         <v>1047</v>
       </c>
-      <c r="I358" s="2"/>
-    </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J358" s="2"/>
+    </row>
+    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A359" s="13">
         <v>100206</v>
       </c>
@@ -12085,10 +12465,11 @@
       </c>
       <c r="F359" s="2"/>
       <c r="G359" s="2"/>
-      <c r="H359" s="3"/>
-      <c r="I359" s="2"/>
-    </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H359" s="2"/>
+      <c r="I359" s="3"/>
+      <c r="J359" s="2"/>
+    </row>
+    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A360" s="13">
         <v>100220</v>
       </c>
@@ -12106,10 +12487,11 @@
       </c>
       <c r="F360" s="2"/>
       <c r="G360" s="2"/>
-      <c r="H360" s="3"/>
-      <c r="I360" s="2"/>
-    </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H360" s="2"/>
+      <c r="I360" s="3"/>
+      <c r="J360" s="2"/>
+    </row>
+    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>1048</v>
       </c>
@@ -12127,12 +12509,13 @@
       </c>
       <c r="F361" s="2"/>
       <c r="G361" s="2"/>
-      <c r="H361" s="3" t="s">
+      <c r="H361" s="2"/>
+      <c r="I361" s="3" t="s">
         <v>1050</v>
       </c>
-      <c r="I361" s="2"/>
-    </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J361" s="2"/>
+    </row>
+    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>1051</v>
       </c>
@@ -12150,12 +12533,13 @@
       </c>
       <c r="F362" s="2"/>
       <c r="G362" s="2"/>
-      <c r="H362" s="3" t="s">
+      <c r="H362" s="2"/>
+      <c r="I362" s="3" t="s">
         <v>1053</v>
       </c>
-      <c r="I362" s="2"/>
-    </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J362" s="2"/>
+    </row>
+    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>1054</v>
       </c>
@@ -12173,12 +12557,13 @@
       </c>
       <c r="F363" s="2"/>
       <c r="G363" s="2"/>
-      <c r="H363" s="3" t="s">
+      <c r="H363" s="2"/>
+      <c r="I363" s="3" t="s">
         <v>1056</v>
       </c>
-      <c r="I363" s="2"/>
-    </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J363" s="2"/>
+    </row>
+    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>1057</v>
       </c>
@@ -12196,12 +12581,13 @@
       </c>
       <c r="F364" s="2"/>
       <c r="G364" s="2"/>
-      <c r="H364" s="3" t="s">
+      <c r="H364" s="2"/>
+      <c r="I364" s="3" t="s">
         <v>1059</v>
       </c>
-      <c r="I364" s="2"/>
-    </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J364" s="2"/>
+    </row>
+    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>1060</v>
       </c>
@@ -12219,12 +12605,13 @@
       </c>
       <c r="F365" s="2"/>
       <c r="G365" s="2"/>
-      <c r="H365" s="3" t="s">
+      <c r="H365" s="2"/>
+      <c r="I365" s="3" t="s">
         <v>1062</v>
       </c>
-      <c r="I365" s="2"/>
-    </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J365" s="2"/>
+    </row>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>1063</v>
       </c>
@@ -12242,12 +12629,13 @@
       </c>
       <c r="F366" s="2"/>
       <c r="G366" s="2"/>
-      <c r="H366" s="3" t="s">
+      <c r="H366" s="2"/>
+      <c r="I366" s="3" t="s">
         <v>1065</v>
       </c>
-      <c r="I366" s="2"/>
-    </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J366" s="2"/>
+    </row>
+    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>1066</v>
       </c>
@@ -12265,12 +12653,13 @@
       </c>
       <c r="F367" s="2"/>
       <c r="G367" s="2"/>
-      <c r="H367" s="3" t="s">
+      <c r="H367" s="2"/>
+      <c r="I367" s="3" t="s">
         <v>1068</v>
       </c>
-      <c r="I367" s="2"/>
-    </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J367" s="2"/>
+    </row>
+    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>1069</v>
       </c>
@@ -12283,15 +12672,18 @@
       <c r="D368" s="2">
         <v>2.5</v>
       </c>
-      <c r="E368" s="2"/>
+      <c r="E368" s="2">
+        <v>2.5</v>
+      </c>
       <c r="F368" s="2"/>
       <c r="G368" s="2"/>
-      <c r="H368" s="3" t="s">
+      <c r="H368" s="2"/>
+      <c r="I368" s="3" t="s">
         <v>1071</v>
       </c>
-      <c r="I368" s="2"/>
-    </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J368" s="2"/>
+    </row>
+    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>1072</v>
       </c>
@@ -12304,15 +12696,18 @@
       <c r="D369" s="2">
         <v>0.3</v>
       </c>
-      <c r="E369" s="2"/>
+      <c r="E369" s="2">
+        <v>0.3</v>
+      </c>
       <c r="F369" s="2"/>
       <c r="G369" s="2"/>
-      <c r="H369" s="3" t="s">
+      <c r="H369" s="2"/>
+      <c r="I369" s="3" t="s">
         <v>1074</v>
       </c>
-      <c r="I369" s="2"/>
-    </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J369" s="2"/>
+    </row>
+    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>1075</v>
       </c>
@@ -12325,15 +12720,18 @@
       <c r="D370" s="2">
         <v>0.3</v>
       </c>
-      <c r="E370" s="2"/>
+      <c r="E370" s="2">
+        <v>0.3</v>
+      </c>
       <c r="F370" s="2"/>
       <c r="G370" s="2"/>
-      <c r="H370" s="3" t="s">
+      <c r="H370" s="2"/>
+      <c r="I370" s="3" t="s">
         <v>1077</v>
       </c>
-      <c r="I370" s="2"/>
-    </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J370" s="2"/>
+    </row>
+    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>1078</v>
       </c>
@@ -12346,15 +12744,18 @@
       <c r="D371" s="2">
         <v>0.3</v>
       </c>
-      <c r="E371" s="2"/>
+      <c r="E371" s="2">
+        <v>0.3</v>
+      </c>
       <c r="F371" s="2"/>
       <c r="G371" s="2"/>
-      <c r="H371" s="3" t="s">
+      <c r="H371" s="2"/>
+      <c r="I371" s="3" t="s">
         <v>1080</v>
       </c>
-      <c r="I371" s="2"/>
-    </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J371" s="2"/>
+    </row>
+    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>1081</v>
       </c>
@@ -12367,15 +12768,18 @@
       <c r="D372" s="2">
         <v>1</v>
       </c>
-      <c r="E372" s="2"/>
+      <c r="E372" s="2">
+        <v>1</v>
+      </c>
       <c r="F372" s="2"/>
       <c r="G372" s="2"/>
-      <c r="H372" s="3" t="s">
+      <c r="H372" s="2"/>
+      <c r="I372" s="3" t="s">
         <v>1083</v>
       </c>
-      <c r="I372" s="2"/>
-    </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J372" s="2"/>
+    </row>
+    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>1084</v>
       </c>
@@ -12388,15 +12792,18 @@
       <c r="D373" s="2">
         <v>1</v>
       </c>
-      <c r="E373" s="2"/>
+      <c r="E373" s="2">
+        <v>1</v>
+      </c>
       <c r="F373" s="2"/>
       <c r="G373" s="2"/>
-      <c r="H373" s="3" t="s">
+      <c r="H373" s="2"/>
+      <c r="I373" s="3" t="s">
         <v>1083</v>
       </c>
-      <c r="I373" s="2"/>
-    </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J373" s="2"/>
+    </row>
+    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>1086</v>
       </c>
@@ -12409,15 +12816,18 @@
       <c r="D374" s="2">
         <v>3.3</v>
       </c>
-      <c r="E374" s="2"/>
+      <c r="E374" s="2">
+        <v>3.3</v>
+      </c>
       <c r="F374" s="2"/>
       <c r="G374" s="2"/>
-      <c r="H374" s="3" t="s">
+      <c r="H374" s="2"/>
+      <c r="I374" s="3" t="s">
         <v>1088</v>
       </c>
-      <c r="I374" s="2"/>
-    </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J374" s="2"/>
+    </row>
+    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A375" s="14">
         <v>210546</v>
       </c>
@@ -12434,7 +12844,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A376" s="14">
         <v>210535</v>
       </c>
@@ -12451,7 +12861,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A377" s="14">
         <v>260611</v>
       </c>
@@ -12468,7 +12878,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A378" s="14">
         <v>210536</v>
       </c>
@@ -12485,7 +12895,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A379" s="14">
         <v>210537</v>
       </c>
@@ -12502,7 +12912,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A380" s="14">
         <v>210545</v>
       </c>
@@ -12519,7 +12929,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A381" s="14">
         <v>210526</v>
       </c>
@@ -12537,374 +12947,374 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I374" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J374" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="H4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="H5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="H6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="H7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="H8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="H9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="H10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="H11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="H12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="H13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="H14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="H15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="H16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="H17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="H18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="H20" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="H21" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="H22" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="H23" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="H24" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="H25" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="H26" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="H27" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="H28" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="H29" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="H30" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="H31" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="H32" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="H33" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="H34" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="H35" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="H36" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="H37" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="H38" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="H39" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="H40" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="H41" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="H42" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="H43" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="H44" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="H45" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="H46" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="H47" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="H48" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="H49" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="H50" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="H51" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="H52" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="H53" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="H54" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="H55" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="H56" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="H57" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="H58" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="H59" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="H60" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="H61" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="H62" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="H63" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="H64" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="H65" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="H66" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="H67" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="H68" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="H69" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="H70" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="H71" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="H72" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="H73" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="H74" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="H75" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="H76" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="H77" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="H78" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="H79" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="H80" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="H81" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="H82" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="H83" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="H84" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="H85" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="H86" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="H87" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="H88" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="H89" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="H90" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="H91" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="H92" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="H93" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="H94" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="H95" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="H96" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="H97" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="H98" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="H99" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="H100" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="H101" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="H102" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="H103" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="H104" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="H105" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="H106" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="H107" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="H108" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="H109" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="H110" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="H111" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="H112" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="H113" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="H114" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="H115" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="H116" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="H118" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="H119" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="H120" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="H121" r:id="rId118" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="H122" r:id="rId119" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="H123" r:id="rId120" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="H124" r:id="rId121" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="H125" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="H126" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="H127" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="H128" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="H129" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
-    <hyperlink ref="H130" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="H131" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
-    <hyperlink ref="H132" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="H133" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
-    <hyperlink ref="H134" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
-    <hyperlink ref="H135" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="H136" r:id="rId133" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="H137" r:id="rId134" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="H138" r:id="rId135" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="H139" r:id="rId136" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="H140" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="H141" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="H142" r:id="rId139" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="H143" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="H144" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="H145" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="H146" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="H147" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="H148" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="H149" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="H150" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="H151" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="H152" r:id="rId149" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="H153" r:id="rId150" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="H154" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="H155" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="H156" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="H157" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="H158" r:id="rId155" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="H159" r:id="rId156" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="H161" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="H162" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="H163" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="H164" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="H165" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
-    <hyperlink ref="H166" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="H167" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="H168" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="H169" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="H170" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="H171" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="H172" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="H173" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="H174" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="H175" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="H176" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="H177" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="H178" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="H179" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="H180" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="H181" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="H182" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="H183" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="H184" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="H185" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="H186" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="H187" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="H188" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="H189" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="H190" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="H191" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="H192" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="H193" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="H194" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="H195" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="H196" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="H197" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="H198" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
-    <hyperlink ref="H199" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="H200" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="H201" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="H202" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="H203" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="H204" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="H205" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="H206" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="H207" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="H208" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="H209" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="H210" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="H211" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
-    <hyperlink ref="H212" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="H213" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="H214" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="H215" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="H216" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="H217" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="H218" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="H219" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="H220" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="H221" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="H222" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="H223" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="H224" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="H225" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="H226" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="H227" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="H228" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="H229" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="H230" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="H231" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="H232" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="H233" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="H234" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="H235" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="H236" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="H237" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="H238" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="H239" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="H240" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="H241" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="H242" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="H243" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="H244" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="H245" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="H246" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="H247" r:id="rId243" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="H248" r:id="rId244" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="H249" r:id="rId245" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="H250" r:id="rId246" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="H251" r:id="rId247" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="H252" r:id="rId248" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="H253" r:id="rId249" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="H254" r:id="rId250" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="H255" r:id="rId251" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="H256" r:id="rId252" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="H257" r:id="rId253" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="H258" r:id="rId254" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="H259" r:id="rId255" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="H260" r:id="rId256" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="H261" r:id="rId257" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="H262" r:id="rId258" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="H263" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="H264" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="H265" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="H266" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="H267" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="H268" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="H269" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="H270" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="H271" r:id="rId267" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="H272" r:id="rId268" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="H273" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="H274" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="H275" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="H276" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="H277" r:id="rId273" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="H278" r:id="rId274" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="H279" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="H280" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="H281" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="H282" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="H283" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="H284" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="H285" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="H286" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="H287" r:id="rId283" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="H288" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="H289" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="H290" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="H291" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="H292" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="H293" r:id="rId289" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="H294" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="H295" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="H296" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="H297" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="H298" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="H299" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="H300" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="H301" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="H302" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="H303" r:id="rId299" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="H304" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="H305" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="H306" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="H307" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="H308" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="H309" r:id="rId305" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="H310" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="H311" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="H312" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="H314" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="H315" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="H316" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="H317" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="H318" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="H319" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="H320" r:id="rId315" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="H321" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="H322" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="H323" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="H324" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="H325" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="H326" r:id="rId321" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="H327" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="H328" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="H329" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="H330" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="H331" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="H332" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="H333" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="H334" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="H335" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="H336" r:id="rId331" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="H337" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="H338" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="H339" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="H340" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="H341" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="H342" r:id="rId337" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="H343" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="H344" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="H345" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="H346" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="H347" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="H348" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="H349" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="H350" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="H351" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="H353" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="H354" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="H355" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="H356" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="H357" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="H358" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="H361" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="H362" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="H363" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="H364" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="H365" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="H366" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="H367" r:id="rId359" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="H368" r:id="rId360" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="H369" r:id="rId361" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="H370" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="H371" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="H372" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="H373" r:id="rId365" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="H374" r:id="rId366" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="I4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="I5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="I6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="I7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="I8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="I9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="I10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="I11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="I12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="I13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="I14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="I15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="I16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="I17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="I18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="I20" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="I21" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="I22" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="I23" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="I24" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="I25" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="I26" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="I27" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="I28" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="I29" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="I30" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="I31" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="I32" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="I33" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="I34" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="I35" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="I36" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="I37" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="I38" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="I39" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="I40" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="I41" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="I42" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="I43" r:id="rId41" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="I44" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="I45" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="I46" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="I47" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="I48" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="I49" r:id="rId47" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="I50" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="I51" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="I52" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="I53" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="I54" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="I55" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="I56" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="I57" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="I58" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="I59" r:id="rId57" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="I60" r:id="rId58" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="I61" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="I62" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="I63" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="I64" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="I65" r:id="rId63" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="I66" r:id="rId64" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="I67" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="I68" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="I69" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="I70" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="I71" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="I72" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="I73" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="I74" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="I75" r:id="rId73" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="I76" r:id="rId74" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="I77" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="I78" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="I79" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="I80" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="I81" r:id="rId79" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="I82" r:id="rId80" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="I83" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="I84" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="I85" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="I86" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="I87" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="I88" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="I89" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="I90" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="I91" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="I92" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="I93" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="I94" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="I95" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="I96" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="I97" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="I98" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="I99" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="I100" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="I101" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
+    <hyperlink ref="I102" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
+    <hyperlink ref="I103" r:id="rId101" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
+    <hyperlink ref="I104" r:id="rId102" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
+    <hyperlink ref="I105" r:id="rId103" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
+    <hyperlink ref="I106" r:id="rId104" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
+    <hyperlink ref="I107" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
+    <hyperlink ref="I108" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
+    <hyperlink ref="I109" r:id="rId107" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
+    <hyperlink ref="I110" r:id="rId108" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
+    <hyperlink ref="I111" r:id="rId109" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
+    <hyperlink ref="I112" r:id="rId110" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
+    <hyperlink ref="I113" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
+    <hyperlink ref="I114" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
+    <hyperlink ref="I115" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
+    <hyperlink ref="I116" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
+    <hyperlink ref="I118" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
+    <hyperlink ref="I119" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
+    <hyperlink ref="I120" r:id="rId117" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
+    <hyperlink ref="I121" r:id="rId118" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
+    <hyperlink ref="I122" r:id="rId119" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
+    <hyperlink ref="I123" r:id="rId120" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
+    <hyperlink ref="I124" r:id="rId121" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="I125" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
+    <hyperlink ref="I126" r:id="rId123" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="I127" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="I128" r:id="rId125" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="I129" r:id="rId126" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
+    <hyperlink ref="I130" r:id="rId127" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
+    <hyperlink ref="I131" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="I132" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
+    <hyperlink ref="I133" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000086000000}"/>
+    <hyperlink ref="I134" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000088000000}"/>
+    <hyperlink ref="I135" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="I136" r:id="rId133" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="I137" r:id="rId134" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="I138" r:id="rId135" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="I139" r:id="rId136" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="I140" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="I141" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="I142" r:id="rId139" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="I143" r:id="rId140" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="I144" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="I145" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="I146" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="I147" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="I148" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="I149" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="I150" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="I151" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="I152" r:id="rId149" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="I153" r:id="rId150" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="I154" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="I155" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="I156" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="I157" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="I158" r:id="rId155" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="I159" r:id="rId156" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="I161" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="I162" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="I163" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="I164" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="I165" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A7000000}"/>
+    <hyperlink ref="I166" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="I167" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="I168" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="I169" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="I170" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="I171" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="I172" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="I173" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="I174" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="I175" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="I176" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="I177" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="I178" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="I179" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="I180" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="I181" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="I182" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="I183" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="I184" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="I185" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="I186" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="I187" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="I188" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="I189" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="I190" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="I191" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="I192" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="I193" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="I194" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="I195" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="I196" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="I197" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="I198" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000CC000000}"/>
+    <hyperlink ref="I199" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="I200" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="I201" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="I202" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="I203" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="I204" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="I205" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="I206" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="I207" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="I208" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="I209" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="I210" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="I211" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="I212" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
+    <hyperlink ref="I213" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="I214" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="I215" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="I216" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="I217" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="I218" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="I219" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="I220" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="I221" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="I222" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="I223" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="I224" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="I225" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="I226" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="I227" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="I228" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="I229" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="I230" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="I231" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="I232" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="I233" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="I234" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="I235" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="I236" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="I237" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="I238" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="I239" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="I240" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="I241" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="I242" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="I243" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="I244" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="I245" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="I246" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="I247" r:id="rId243" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="I248" r:id="rId244" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="I249" r:id="rId245" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="I250" r:id="rId246" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="I251" r:id="rId247" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="I252" r:id="rId248" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="I253" r:id="rId249" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="I254" r:id="rId250" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="I255" r:id="rId251" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="I256" r:id="rId252" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="I257" r:id="rId253" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="I258" r:id="rId254" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="I259" r:id="rId255" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="I260" r:id="rId256" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="I261" r:id="rId257" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="I262" r:id="rId258" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="I263" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="I264" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="I265" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="I266" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="I267" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="I268" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="I269" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="I270" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="I271" r:id="rId267" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="I272" r:id="rId268" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="I273" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="I274" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="I275" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="I276" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="I277" r:id="rId273" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="I278" r:id="rId274" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="I279" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="I280" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="I281" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="I282" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="I283" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="I284" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="I285" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="I286" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="I287" r:id="rId283" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="I288" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="I289" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="I290" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="I291" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="I292" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="I293" r:id="rId289" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="I294" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="I295" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="I296" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="I297" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="I298" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="I299" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="I300" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="I301" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="I302" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="I303" r:id="rId299" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="I304" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="I305" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="I306" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="I307" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="I308" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="I309" r:id="rId305" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="I310" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="I311" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="I312" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="I314" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="I315" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="I316" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="I317" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="I318" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="I319" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="I320" r:id="rId315" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="I321" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="I322" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="I323" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="I324" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="I325" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="I326" r:id="rId321" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="I327" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="I328" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="I329" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="I330" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="I331" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="I332" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="I333" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="I334" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="I335" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="I336" r:id="rId331" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="I337" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="I338" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="I339" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="I340" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="I341" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="I342" r:id="rId337" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="I343" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="I344" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="I345" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="I346" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="I347" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="I348" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="I349" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="I350" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="I351" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="I353" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="I354" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="I355" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="I356" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="I357" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="I358" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="I361" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="I362" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="I363" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="I364" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="I365" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="I366" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="I367" r:id="rId359" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="I368" r:id="rId360" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="I369" r:id="rId361" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="I370" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="I371" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="I372" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
+    <hyperlink ref="I373" r:id="rId365" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="I374" r:id="rId366" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/TTABLEAU DES PRIX AVEC REF.xlsx
+++ b/TTABLEAU DES PRIX AVEC REF.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melou\blazing-dynasty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA56D4DA-CE41-4563-8EA1-AE95D11A1CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2009645-D2C3-4308-BAEF-3446A65BE841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15135" yWindow="255" windowWidth="13665" windowHeight="14925" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$374</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$372</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="1129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="1121">
   <si>
     <t>Art</t>
   </si>
@@ -2385,9 +2385,6 @@
     <t>Aroma Home. Désodorisant d'ambiance Cerise de la Barbade</t>
   </si>
   <si>
-    <t>https://www.mihi.care/storage/mini/24/01/yZAmw0lFpU1cbdVBlnn0QIcHdxwb0wnKPfhCaUth.png</t>
-  </si>
-  <si>
     <t>80129</t>
   </si>
   <si>
@@ -3273,30 +3270,6 @@
     <t>https://www.mihi.care/storage/mini/25/11/KrgNnwl59KAKvBzT6Tr11GiKnZ6ANA1WvrLpRzCL.png</t>
   </si>
   <si>
-    <t>90428</t>
-  </si>
-  <si>
-    <t>Gift Bag&amp;Box. Sac cadeau en papier rouge 140*80*200</t>
-  </si>
-  <si>
-    <t>https://www.mihi.care/storage/mini/26/02/xyZnFVWf46MUDKTjBb59HOl8WSPl3Eh7z2HzEefx.png</t>
-  </si>
-  <si>
-    <t>90429</t>
-  </si>
-  <si>
-    <t>Gift Bag&amp;Box. Sac cadeau en papier blanc 140*80*200</t>
-  </si>
-  <si>
-    <t>90430</t>
-  </si>
-  <si>
-    <t>Gift Bag&amp;Box. Magnetic Gift Box Golden 175*175*60</t>
-  </si>
-  <si>
-    <t>https://www.mihi.care/storage/mini/25/11/U06am40NjN3jKiIwZ25COrmvpS4QiyH7DUx29wDu.png</t>
-  </si>
-  <si>
     <t>https://www.mihi.care/storage/mini/26/04/Wc1nrgD0u8QtyKONHBgFODwJ1mdk8zGJUzxXLAoH.png</t>
   </si>
   <si>
@@ -3384,44 +3357,47 @@
     <t>Vitamins spiruline 500 mg</t>
   </si>
   <si>
-    <t>SETS</t>
-  </si>
-  <si>
-    <t>SET Sparkling Home Formula (080110 + 080106 + 080136 + 080140 + 080129 + 080133)</t>
-  </si>
-  <si>
-    <t>SET 020623 + 020624</t>
-  </si>
-  <si>
-    <t>KIDS KIDS SET</t>
-  </si>
-  <si>
-    <t>SET 060402 + 060403</t>
-  </si>
-  <si>
-    <t>SET 050603 + 050102 Make up</t>
-  </si>
-  <si>
-    <t>sets</t>
-  </si>
-  <si>
-    <t>SET 051213 + 051111</t>
-  </si>
-  <si>
-    <t>SET 010702 + 010703 + 010705</t>
-  </si>
-  <si>
     <t>Rupture</t>
   </si>
   <si>
     <t>Oui</t>
+  </si>
+  <si>
+    <t>nutrition</t>
+  </si>
+  <si>
+    <t>smart meal noix de coco et melnage de noix</t>
+  </si>
+  <si>
+    <t>https://www.mihi.care/storage/26/08/1XQ7M5QZu3DGoo276toQbRtRNsILNiuIwQC0dE3Q.png</t>
+  </si>
+  <si>
+    <t>Smart Meal. MÉLANGE À DOUBLE NOIX</t>
+  </si>
+  <si>
+    <t>https://www.mihi.care/storage/26/08/XDX2uKi3dHRhWSaVRAi2oA3wP0c5bR79f6mCv4VP.png</t>
+  </si>
+  <si>
+    <t>Smart Meal. LA PUISSANCE DES PROTÉINES D'ARACHIDE</t>
+  </si>
+  <si>
+    <t>https://www.mihi.care/storage/26/08/F1xTpJP05keVSz5SeUXAJxbGHUio6wqsAjYDqkPE.png</t>
+  </si>
+  <si>
+    <t>Clean Home. Grout &amp; Tile Cleaner Expert</t>
+  </si>
+  <si>
+    <t>https://www.mihi.care/storage/26/07/p4a8QE9Pvzt3cjDYaL0tDmDXYCoQlnvYYjkHJ93J.png</t>
+  </si>
+  <si>
+    <t>https://www.mihi.care/storage/26/08/7GUlemeYM4xjOMEdN8AQJLiLAIlAdVnFzYHc262U.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3466,6 +3442,11 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF212529"/>
+      <name val="Jost"/>
     </font>
   </fonts>
   <fills count="6">
@@ -3516,7 +3497,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3542,6 +3523,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3808,8 +3792,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M381"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M375"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
@@ -3821,7 +3805,7 @@
     <col min="10" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3835,10 +3819,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1108</v>
+        <v>1099</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1127</v>
+        <v>1109</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -3853,7 +3837,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -3873,11 +3857,11 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="11" t="s">
-        <v>1089</v>
+        <v>1080</v>
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -3897,11 +3881,11 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="11" t="s">
-        <v>1090</v>
+        <v>1081</v>
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -3921,11 +3905,11 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="11" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -3945,11 +3929,11 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="11" t="s">
-        <v>1092</v>
+        <v>1083</v>
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -3969,11 +3953,11 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="11" t="s">
-        <v>1093</v>
+        <v>1084</v>
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -3993,11 +3977,11 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="11" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
@@ -4017,11 +4001,11 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="11" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -4041,11 +4025,11 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="11" t="s">
-        <v>1096</v>
+        <v>1087</v>
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
@@ -4065,11 +4049,11 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="11" t="s">
-        <v>1097</v>
+        <v>1088</v>
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
@@ -4093,7 +4077,7 @@
       </c>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
@@ -4113,11 +4097,11 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="11" t="s">
-        <v>1098</v>
+        <v>1089</v>
       </c>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
         <v>33</v>
       </c>
@@ -4137,11 +4121,11 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="11" t="s">
-        <v>1099</v>
+        <v>1090</v>
       </c>
       <c r="J13" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
         <v>35</v>
       </c>
@@ -4165,7 +4149,7 @@
       </c>
       <c r="J14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
         <v>38</v>
       </c>
@@ -4185,11 +4169,11 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="11" t="s">
-        <v>1100</v>
+        <v>1091</v>
       </c>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
         <v>40</v>
       </c>
@@ -4213,7 +4197,7 @@
       </c>
       <c r="J16" s="2"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
         <v>43</v>
       </c>
@@ -4237,7 +4221,7 @@
       </c>
       <c r="J17" s="2"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
         <v>46</v>
       </c>
@@ -4261,7 +4245,7 @@
       </c>
       <c r="J18" s="2"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
         <v>49</v>
       </c>
@@ -4281,11 +4265,11 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="3" t="s">
-        <v>1101</v>
+        <v>1092</v>
       </c>
       <c r="J19" s="2"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
@@ -4309,7 +4293,7 @@
       </c>
       <c r="J20" s="2"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
         <v>54</v>
       </c>
@@ -4329,11 +4313,11 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="11" t="s">
-        <v>1102</v>
+        <v>1093</v>
       </c>
       <c r="J21" s="2"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4357,7 +4341,7 @@
       </c>
       <c r="J22" s="2"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
         <v>59</v>
       </c>
@@ -4381,7 +4365,7 @@
       </c>
       <c r="J23" s="2"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
         <v>62</v>
       </c>
@@ -4405,7 +4389,7 @@
       </c>
       <c r="J24" s="2"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
         <v>65</v>
       </c>
@@ -4429,7 +4413,7 @@
       </c>
       <c r="J25" s="2"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
         <v>68</v>
       </c>
@@ -4453,7 +4437,7 @@
       </c>
       <c r="J26" s="2"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
         <v>71</v>
       </c>
@@ -4473,11 +4457,11 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="11" t="s">
-        <v>1104</v>
+        <v>1095</v>
       </c>
       <c r="J27" s="2"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
         <v>73</v>
       </c>
@@ -4501,7 +4485,7 @@
       </c>
       <c r="J28" s="2"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
         <v>76</v>
       </c>
@@ -4525,7 +4509,7 @@
       </c>
       <c r="J29" s="2"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
         <v>79</v>
       </c>
@@ -4545,11 +4529,11 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="11" t="s">
-        <v>1103</v>
+        <v>1094</v>
       </c>
       <c r="J30" s="2"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
         <v>81</v>
       </c>
@@ -4573,7 +4557,7 @@
       </c>
       <c r="J31" s="2"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
         <v>84</v>
       </c>
@@ -4597,7 +4581,7 @@
       </c>
       <c r="J32" s="2"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10">
       <c r="A33" s="2" t="s">
         <v>87</v>
       </c>
@@ -4621,7 +4605,7 @@
       </c>
       <c r="J33" s="2"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10">
       <c r="A34" s="2" t="s">
         <v>90</v>
       </c>
@@ -4645,7 +4629,7 @@
       </c>
       <c r="J34" s="2"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10">
       <c r="A35" s="2" t="s">
         <v>93</v>
       </c>
@@ -4669,7 +4653,7 @@
       </c>
       <c r="J35" s="2"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10">
       <c r="A36" s="2" t="s">
         <v>96</v>
       </c>
@@ -4693,7 +4677,7 @@
       </c>
       <c r="J36" s="2"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10">
       <c r="A37" s="2" t="s">
         <v>99</v>
       </c>
@@ -4717,7 +4701,7 @@
       </c>
       <c r="J37" s="2"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10">
       <c r="A38" s="2" t="s">
         <v>102</v>
       </c>
@@ -4737,11 +4721,11 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="11" t="s">
-        <v>1105</v>
+        <v>1096</v>
       </c>
       <c r="J38" s="2"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10">
       <c r="A39" s="2" t="s">
         <v>104</v>
       </c>
@@ -4761,11 +4745,11 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="11" t="s">
-        <v>1106</v>
+        <v>1097</v>
       </c>
       <c r="J39" s="2"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10">
       <c r="A40" s="2" t="s">
         <v>106</v>
       </c>
@@ -4785,11 +4769,11 @@
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="11" t="s">
-        <v>1107</v>
+        <v>1098</v>
       </c>
       <c r="J40" s="2"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10">
       <c r="A41" s="2" t="s">
         <v>108</v>
       </c>
@@ -4813,7 +4797,7 @@
       </c>
       <c r="J41" s="2"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10">
       <c r="A42" s="2" t="s">
         <v>111</v>
       </c>
@@ -4837,7 +4821,7 @@
       </c>
       <c r="J42" s="2"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10">
       <c r="A43" s="2" t="s">
         <v>114</v>
       </c>
@@ -4861,7 +4845,7 @@
       </c>
       <c r="J43" s="2"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10">
       <c r="A44" s="2" t="s">
         <v>117</v>
       </c>
@@ -4885,7 +4869,7 @@
       </c>
       <c r="J44" s="2"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10">
       <c r="A45" s="2" t="s">
         <v>120</v>
       </c>
@@ -4909,7 +4893,7 @@
       </c>
       <c r="J45" s="2"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10">
       <c r="A46" s="2" t="s">
         <v>123</v>
       </c>
@@ -4933,7 +4917,7 @@
       </c>
       <c r="J46" s="2"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10">
       <c r="A47" s="2" t="s">
         <v>126</v>
       </c>
@@ -4957,7 +4941,7 @@
       </c>
       <c r="J47" s="2"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10">
       <c r="A48" s="2" t="s">
         <v>129</v>
       </c>
@@ -4981,7 +4965,7 @@
       </c>
       <c r="J48" s="2"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10">
       <c r="A49" s="2" t="s">
         <v>132</v>
       </c>
@@ -4998,7 +4982,7 @@
         <v>5.25</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>1128</v>
+        <v>1110</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -5007,7 +4991,7 @@
       </c>
       <c r="J49" s="2"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10">
       <c r="A50" s="2" t="s">
         <v>135</v>
       </c>
@@ -5031,7 +5015,7 @@
       </c>
       <c r="J50" s="2"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10">
       <c r="A51" s="2" t="s">
         <v>138</v>
       </c>
@@ -5055,7 +5039,7 @@
       </c>
       <c r="J51" s="2"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10">
       <c r="A52" s="2" t="s">
         <v>141</v>
       </c>
@@ -5079,7 +5063,7 @@
       </c>
       <c r="J52" s="2"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10">
       <c r="A53" s="2" t="s">
         <v>144</v>
       </c>
@@ -5103,7 +5087,7 @@
       </c>
       <c r="J53" s="2"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10">
       <c r="A54" s="2" t="s">
         <v>147</v>
       </c>
@@ -5127,7 +5111,7 @@
       </c>
       <c r="J54" s="2"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10">
       <c r="A55" s="2" t="s">
         <v>150</v>
       </c>
@@ -5151,7 +5135,7 @@
       </c>
       <c r="J55" s="2"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10">
       <c r="A56" s="2" t="s">
         <v>153</v>
       </c>
@@ -5175,7 +5159,7 @@
       </c>
       <c r="J56" s="2"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10">
       <c r="A57" s="2" t="s">
         <v>156</v>
       </c>
@@ -5199,7 +5183,7 @@
       </c>
       <c r="J57" s="2"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10">
       <c r="A58" s="2" t="s">
         <v>159</v>
       </c>
@@ -5223,7 +5207,7 @@
       </c>
       <c r="J58" s="2"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10">
       <c r="A59" s="2" t="s">
         <v>161</v>
       </c>
@@ -5247,7 +5231,7 @@
       </c>
       <c r="J59" s="2"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10">
       <c r="A60" s="2" t="s">
         <v>164</v>
       </c>
@@ -5271,7 +5255,7 @@
       </c>
       <c r="J60" s="2"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10">
       <c r="A61" s="2" t="s">
         <v>167</v>
       </c>
@@ -5295,7 +5279,7 @@
       </c>
       <c r="J61" s="2"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10">
       <c r="A62" s="2" t="s">
         <v>170</v>
       </c>
@@ -5319,7 +5303,7 @@
       </c>
       <c r="J62" s="2"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10">
       <c r="A63" s="2" t="s">
         <v>173</v>
       </c>
@@ -5343,7 +5327,7 @@
       </c>
       <c r="J63" s="2"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10">
       <c r="A64" s="2" t="s">
         <v>176</v>
       </c>
@@ -5367,7 +5351,7 @@
       </c>
       <c r="J64" s="2"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12">
       <c r="A65" s="2" t="s">
         <v>179</v>
       </c>
@@ -5391,7 +5375,7 @@
       </c>
       <c r="J65" s="2"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12">
       <c r="A66" s="2" t="s">
         <v>182</v>
       </c>
@@ -5415,7 +5399,7 @@
       </c>
       <c r="J66" s="2"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12">
       <c r="A67" s="2" t="s">
         <v>185</v>
       </c>
@@ -5439,7 +5423,7 @@
       </c>
       <c r="J67" s="2"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12">
       <c r="A68" s="2" t="s">
         <v>188</v>
       </c>
@@ -5463,7 +5447,7 @@
       </c>
       <c r="J68" s="2"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12">
       <c r="A69" s="2" t="s">
         <v>191</v>
       </c>
@@ -5487,7 +5471,7 @@
       </c>
       <c r="J69" s="2"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12">
       <c r="A70" s="2" t="s">
         <v>194</v>
       </c>
@@ -5511,7 +5495,7 @@
       </c>
       <c r="J70" s="2"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12">
       <c r="A71" s="2" t="s">
         <v>197</v>
       </c>
@@ -5535,7 +5519,7 @@
       </c>
       <c r="J71" s="2"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12">
       <c r="A72" s="2" t="s">
         <v>200</v>
       </c>
@@ -5559,7 +5543,7 @@
       </c>
       <c r="J72" s="2"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12">
       <c r="A73" s="2" t="s">
         <v>203</v>
       </c>
@@ -5583,7 +5567,7 @@
       </c>
       <c r="J73" s="2"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12">
       <c r="A74" s="2" t="s">
         <v>206</v>
       </c>
@@ -5607,7 +5591,7 @@
       </c>
       <c r="J74" s="2"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12">
       <c r="A75" s="6" t="s">
         <v>210</v>
       </c>
@@ -5633,7 +5617,7 @@
       <c r="K75" s="9"/>
       <c r="L75" s="9"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12">
       <c r="A76" s="2" t="s">
         <v>213</v>
       </c>
@@ -5657,7 +5641,7 @@
       </c>
       <c r="J76" s="2"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12">
       <c r="A77" s="2" t="s">
         <v>216</v>
       </c>
@@ -5681,7 +5665,7 @@
       </c>
       <c r="J77" s="2"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12">
       <c r="A78" s="2" t="s">
         <v>219</v>
       </c>
@@ -5705,7 +5689,7 @@
       </c>
       <c r="J78" s="2"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12">
       <c r="A79" s="5">
         <v>251104</v>
       </c>
@@ -5730,7 +5714,7 @@
       <c r="J79" s="8"/>
       <c r="K79" s="9"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12">
       <c r="A80" s="2" t="s">
         <v>224</v>
       </c>
@@ -5754,7 +5738,7 @@
       </c>
       <c r="J80" s="2"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13">
       <c r="A81" s="2" t="s">
         <v>228</v>
       </c>
@@ -5778,7 +5762,7 @@
       </c>
       <c r="J81" s="2"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13">
       <c r="A82" s="2" t="s">
         <v>231</v>
       </c>
@@ -5802,7 +5786,7 @@
       </c>
       <c r="J82" s="2"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13">
       <c r="A83" s="6" t="s">
         <v>234</v>
       </c>
@@ -5829,7 +5813,7 @@
       <c r="L83" s="9"/>
       <c r="M83" s="9"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13">
       <c r="A84" s="2" t="s">
         <v>237</v>
       </c>
@@ -5853,7 +5837,7 @@
       </c>
       <c r="J84" s="2"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13">
       <c r="A85" s="6" t="s">
         <v>240</v>
       </c>
@@ -5879,7 +5863,7 @@
       <c r="K85" s="9"/>
       <c r="L85" s="9"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13">
       <c r="A86" s="2" t="s">
         <v>243</v>
       </c>
@@ -5903,7 +5887,7 @@
       </c>
       <c r="J86" s="2"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13">
       <c r="A87" s="2" t="s">
         <v>246</v>
       </c>
@@ -5927,7 +5911,7 @@
       </c>
       <c r="J87" s="2"/>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13">
       <c r="A88" s="4" t="s">
         <v>249</v>
       </c>
@@ -5953,7 +5937,7 @@
       <c r="K88" s="9"/>
       <c r="L88" s="9"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13">
       <c r="A89" s="2" t="s">
         <v>252</v>
       </c>
@@ -5977,7 +5961,7 @@
       </c>
       <c r="J89" s="2"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13">
       <c r="A90" s="2" t="s">
         <v>256</v>
       </c>
@@ -6001,7 +5985,7 @@
       </c>
       <c r="J90" s="2"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13">
       <c r="A91" s="2" t="s">
         <v>259</v>
       </c>
@@ -6025,7 +6009,7 @@
       </c>
       <c r="J91" s="2"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13">
       <c r="A92" s="2" t="s">
         <v>262</v>
       </c>
@@ -6049,7 +6033,7 @@
       </c>
       <c r="J92" s="2"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13">
       <c r="A93" s="2" t="s">
         <v>265</v>
       </c>
@@ -6073,7 +6057,7 @@
       </c>
       <c r="J93" s="2"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13">
       <c r="A94" s="2" t="s">
         <v>268</v>
       </c>
@@ -6097,7 +6081,7 @@
       </c>
       <c r="J94" s="2"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13">
       <c r="A95" s="2" t="s">
         <v>271</v>
       </c>
@@ -6121,7 +6105,7 @@
       </c>
       <c r="J95" s="2"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13">
       <c r="A96" s="2" t="s">
         <v>274</v>
       </c>
@@ -6145,7 +6129,7 @@
       </c>
       <c r="J96" s="2"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10">
       <c r="A97" s="2" t="s">
         <v>277</v>
       </c>
@@ -6169,7 +6153,7 @@
       </c>
       <c r="J97" s="2"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10">
       <c r="A98" s="2" t="s">
         <v>280</v>
       </c>
@@ -6193,7 +6177,7 @@
       </c>
       <c r="J98" s="2"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10">
       <c r="A99" s="2" t="s">
         <v>283</v>
       </c>
@@ -6217,7 +6201,7 @@
       </c>
       <c r="J99" s="2"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10">
       <c r="A100" s="2" t="s">
         <v>286</v>
       </c>
@@ -6241,7 +6225,7 @@
       </c>
       <c r="J100" s="2"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10">
       <c r="A101" s="2" t="s">
         <v>289</v>
       </c>
@@ -6265,7 +6249,7 @@
       </c>
       <c r="J101" s="2"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10">
       <c r="A102" s="2" t="s">
         <v>292</v>
       </c>
@@ -6289,7 +6273,7 @@
       </c>
       <c r="J102" s="2"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10">
       <c r="A103" s="2" t="s">
         <v>295</v>
       </c>
@@ -6313,7 +6297,7 @@
       </c>
       <c r="J103" s="2"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10">
       <c r="A104" s="2" t="s">
         <v>298</v>
       </c>
@@ -6337,7 +6321,7 @@
       </c>
       <c r="J104" s="2"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10">
       <c r="A105" s="2" t="s">
         <v>301</v>
       </c>
@@ -6361,7 +6345,7 @@
       </c>
       <c r="J105" s="2"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10">
       <c r="A106" s="2" t="s">
         <v>304</v>
       </c>
@@ -6385,7 +6369,7 @@
       </c>
       <c r="J106" s="2"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10">
       <c r="A107" s="2" t="s">
         <v>307</v>
       </c>
@@ -6409,7 +6393,7 @@
       </c>
       <c r="J107" s="2"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10">
       <c r="A108" s="2" t="s">
         <v>310</v>
       </c>
@@ -6433,7 +6417,7 @@
       </c>
       <c r="J108" s="2"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10">
       <c r="A109" s="2" t="s">
         <v>313</v>
       </c>
@@ -6457,7 +6441,7 @@
       </c>
       <c r="J109" s="2"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10">
       <c r="A110" s="2" t="s">
         <v>316</v>
       </c>
@@ -6481,7 +6465,7 @@
       </c>
       <c r="J110" s="2"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10">
       <c r="A111" s="2" t="s">
         <v>319</v>
       </c>
@@ -6505,7 +6489,7 @@
       </c>
       <c r="J111" s="2"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10">
       <c r="A112" s="2" t="s">
         <v>322</v>
       </c>
@@ -6529,7 +6513,7 @@
       </c>
       <c r="J112" s="2"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10">
       <c r="A113" s="2" t="s">
         <v>325</v>
       </c>
@@ -6553,7 +6537,7 @@
       </c>
       <c r="J113" s="2"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10">
       <c r="A114" s="2" t="s">
         <v>328</v>
       </c>
@@ -6577,7 +6561,7 @@
       </c>
       <c r="J114" s="2"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10">
       <c r="A115" s="2" t="s">
         <v>331</v>
       </c>
@@ -6601,7 +6585,7 @@
       </c>
       <c r="J115" s="2"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10">
       <c r="A116" s="2" t="s">
         <v>334</v>
       </c>
@@ -6625,7 +6609,7 @@
       </c>
       <c r="J116" s="2"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10">
       <c r="A117" s="2" t="s">
         <v>337</v>
       </c>
@@ -6633,7 +6617,7 @@
         <v>253</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>1109</v>
+        <v>1100</v>
       </c>
       <c r="D117" s="2">
         <v>37</v>
@@ -6645,11 +6629,11 @@
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
       <c r="I117" s="3" t="s">
-        <v>1110</v>
+        <v>1101</v>
       </c>
       <c r="J117" s="2"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10">
       <c r="A118" s="2" t="s">
         <v>338</v>
       </c>
@@ -6673,7 +6657,7 @@
       </c>
       <c r="J118" s="2"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10">
       <c r="A119" s="2" t="s">
         <v>341</v>
       </c>
@@ -6697,7 +6681,7 @@
       </c>
       <c r="J119" s="2"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10">
       <c r="A120" s="2" t="s">
         <v>344</v>
       </c>
@@ -6721,7 +6705,7 @@
       </c>
       <c r="J120" s="2"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10">
       <c r="A121" s="2" t="s">
         <v>347</v>
       </c>
@@ -6745,7 +6729,7 @@
       </c>
       <c r="J121" s="2"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10">
       <c r="A122" s="2" t="s">
         <v>350</v>
       </c>
@@ -6769,7 +6753,7 @@
       </c>
       <c r="J122" s="2"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10">
       <c r="A123" s="2" t="s">
         <v>353</v>
       </c>
@@ -6793,7 +6777,7 @@
       </c>
       <c r="J123" s="2"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10">
       <c r="A124" s="2" t="s">
         <v>356</v>
       </c>
@@ -6817,7 +6801,7 @@
       </c>
       <c r="J124" s="2"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10">
       <c r="A125" s="2" t="s">
         <v>359</v>
       </c>
@@ -6841,7 +6825,7 @@
       </c>
       <c r="J125" s="2"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10">
       <c r="A126" s="2" t="s">
         <v>362</v>
       </c>
@@ -6865,7 +6849,7 @@
       </c>
       <c r="J126" s="2"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10">
       <c r="A127" s="2" t="s">
         <v>365</v>
       </c>
@@ -6889,7 +6873,7 @@
       </c>
       <c r="J127" s="2"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10">
       <c r="A128" s="2" t="s">
         <v>368</v>
       </c>
@@ -6913,7 +6897,7 @@
       </c>
       <c r="J128" s="2"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10">
       <c r="A129" s="2" t="s">
         <v>371</v>
       </c>
@@ -6937,7 +6921,7 @@
       </c>
       <c r="J129" s="2"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10">
       <c r="A130" s="2" t="s">
         <v>374</v>
       </c>
@@ -6961,7 +6945,7 @@
       </c>
       <c r="J130" s="2"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10">
       <c r="A131" s="2" t="s">
         <v>377</v>
       </c>
@@ -6985,7 +6969,7 @@
       </c>
       <c r="J131" s="2"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10">
       <c r="A132" s="2" t="s">
         <v>380</v>
       </c>
@@ -7009,7 +6993,7 @@
       </c>
       <c r="J132" s="2"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10">
       <c r="A133" s="2" t="s">
         <v>383</v>
       </c>
@@ -7033,7 +7017,7 @@
       </c>
       <c r="J133" s="2"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10">
       <c r="A134" s="2" t="s">
         <v>386</v>
       </c>
@@ -7057,7 +7041,7 @@
       </c>
       <c r="J134" s="2"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10">
       <c r="A135" s="2" t="s">
         <v>389</v>
       </c>
@@ -7081,7 +7065,7 @@
       </c>
       <c r="J135" s="2"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10">
       <c r="A136" s="2" t="s">
         <v>392</v>
       </c>
@@ -7105,7 +7089,7 @@
       </c>
       <c r="J136" s="2"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10">
       <c r="A137" s="2" t="s">
         <v>395</v>
       </c>
@@ -7129,7 +7113,7 @@
       </c>
       <c r="J137" s="2"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10">
       <c r="A138" s="2" t="s">
         <v>398</v>
       </c>
@@ -7153,7 +7137,7 @@
       </c>
       <c r="J138" s="2"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10">
       <c r="A139" s="2" t="s">
         <v>401</v>
       </c>
@@ -7177,7 +7161,7 @@
       </c>
       <c r="J139" s="2"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10">
       <c r="A140" s="2" t="s">
         <v>404</v>
       </c>
@@ -7201,7 +7185,7 @@
       </c>
       <c r="J140" s="2"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10">
       <c r="A141" s="2" t="s">
         <v>407</v>
       </c>
@@ -7225,7 +7209,7 @@
       </c>
       <c r="J141" s="2"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10">
       <c r="A142" s="2" t="s">
         <v>410</v>
       </c>
@@ -7249,7 +7233,7 @@
       </c>
       <c r="J142" s="2"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10">
       <c r="A143" s="2" t="s">
         <v>413</v>
       </c>
@@ -7273,7 +7257,7 @@
       </c>
       <c r="J143" s="2"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10">
       <c r="A144" s="2" t="s">
         <v>416</v>
       </c>
@@ -7297,7 +7281,7 @@
       </c>
       <c r="J144" s="2"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10">
       <c r="A145" s="2" t="s">
         <v>419</v>
       </c>
@@ -7321,7 +7305,7 @@
       </c>
       <c r="J145" s="2"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10">
       <c r="A146" s="2" t="s">
         <v>422</v>
       </c>
@@ -7345,7 +7329,7 @@
       </c>
       <c r="J146" s="2"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10">
       <c r="A147" s="2" t="s">
         <v>425</v>
       </c>
@@ -7369,7 +7353,7 @@
       </c>
       <c r="J147" s="2"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10">
       <c r="A148" s="2" t="s">
         <v>429</v>
       </c>
@@ -7393,7 +7377,7 @@
       </c>
       <c r="J148" s="2"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10">
       <c r="A149" s="2" t="s">
         <v>433</v>
       </c>
@@ -7417,7 +7401,7 @@
       </c>
       <c r="J149" s="2"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10">
       <c r="A150" s="2" t="s">
         <v>436</v>
       </c>
@@ -7441,7 +7425,7 @@
       </c>
       <c r="J150" s="2"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10">
       <c r="A151" s="2" t="s">
         <v>439</v>
       </c>
@@ -7465,7 +7449,7 @@
       </c>
       <c r="J151" s="2"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10">
       <c r="A152" s="2" t="s">
         <v>442</v>
       </c>
@@ -7489,7 +7473,7 @@
       </c>
       <c r="J152" s="2"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10">
       <c r="A153" s="2" t="s">
         <v>445</v>
       </c>
@@ -7513,7 +7497,7 @@
       </c>
       <c r="J153" s="2"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10">
       <c r="A154" s="2" t="s">
         <v>448</v>
       </c>
@@ -7537,7 +7521,7 @@
       </c>
       <c r="J154" s="2"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10">
       <c r="A155" s="2" t="s">
         <v>451</v>
       </c>
@@ -7561,7 +7545,7 @@
       </c>
       <c r="J155" s="2"/>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10">
       <c r="A156" s="2" t="s">
         <v>454</v>
       </c>
@@ -7585,7 +7569,7 @@
       </c>
       <c r="J156" s="2"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10">
       <c r="A157" s="2" t="s">
         <v>457</v>
       </c>
@@ -7609,7 +7593,7 @@
       </c>
       <c r="J157" s="2"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10">
       <c r="A158" s="2" t="s">
         <v>460</v>
       </c>
@@ -7633,7 +7617,7 @@
       </c>
       <c r="J158" s="2"/>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10">
       <c r="A159" s="2" t="s">
         <v>463</v>
       </c>
@@ -7657,7 +7641,7 @@
       </c>
       <c r="J159" s="2"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10">
       <c r="A160" s="2" t="s">
         <v>466</v>
       </c>
@@ -7665,7 +7649,7 @@
         <v>9</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>1111</v>
+        <v>1102</v>
       </c>
       <c r="D160" s="2">
         <v>12.5</v>
@@ -7677,11 +7661,11 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
       <c r="I160" s="3" t="s">
-        <v>1112</v>
+        <v>1103</v>
       </c>
       <c r="J160" s="2"/>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10">
       <c r="A161" s="2" t="s">
         <v>467</v>
       </c>
@@ -7705,7 +7689,7 @@
       </c>
       <c r="J161" s="2"/>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10">
       <c r="A162" s="2" t="s">
         <v>470</v>
       </c>
@@ -7729,7 +7713,7 @@
       </c>
       <c r="J162" s="2"/>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10">
       <c r="A163" s="2" t="s">
         <v>473</v>
       </c>
@@ -7753,7 +7737,7 @@
       </c>
       <c r="J163" s="2"/>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10">
       <c r="A164" s="2" t="s">
         <v>476</v>
       </c>
@@ -7777,7 +7761,7 @@
       </c>
       <c r="J164" s="2"/>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10">
       <c r="A165" s="2" t="s">
         <v>479</v>
       </c>
@@ -7801,7 +7785,7 @@
       </c>
       <c r="J165" s="2"/>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10">
       <c r="A166" s="2" t="s">
         <v>482</v>
       </c>
@@ -7825,7 +7809,7 @@
       </c>
       <c r="J166" s="2"/>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10">
       <c r="A167" s="2" t="s">
         <v>485</v>
       </c>
@@ -7849,7 +7833,7 @@
       </c>
       <c r="J167" s="2"/>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10">
       <c r="A168" s="2" t="s">
         <v>488</v>
       </c>
@@ -7873,7 +7857,7 @@
       </c>
       <c r="J168" s="2"/>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10">
       <c r="A169" s="2" t="s">
         <v>491</v>
       </c>
@@ -7897,7 +7881,7 @@
       </c>
       <c r="J169" s="2"/>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10">
       <c r="A170" s="2" t="s">
         <v>494</v>
       </c>
@@ -7921,7 +7905,7 @@
       </c>
       <c r="J170" s="2"/>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10">
       <c r="A171" s="2" t="s">
         <v>497</v>
       </c>
@@ -7945,7 +7929,7 @@
       </c>
       <c r="J171" s="2"/>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10">
       <c r="A172" s="2" t="s">
         <v>500</v>
       </c>
@@ -7969,7 +7953,7 @@
       </c>
       <c r="J172" s="2"/>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10">
       <c r="A173" s="2" t="s">
         <v>503</v>
       </c>
@@ -7993,7 +7977,7 @@
       </c>
       <c r="J173" s="2"/>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10">
       <c r="A174" s="2" t="s">
         <v>506</v>
       </c>
@@ -8017,7 +8001,7 @@
       </c>
       <c r="J174" s="2"/>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10">
       <c r="A175" s="2" t="s">
         <v>509</v>
       </c>
@@ -8041,7 +8025,7 @@
       </c>
       <c r="J175" s="2"/>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10">
       <c r="A176" s="2" t="s">
         <v>512</v>
       </c>
@@ -8065,7 +8049,7 @@
       </c>
       <c r="J176" s="2"/>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10">
       <c r="A177" s="2" t="s">
         <v>515</v>
       </c>
@@ -8089,7 +8073,7 @@
       </c>
       <c r="J177" s="2"/>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10">
       <c r="A178" s="2" t="s">
         <v>518</v>
       </c>
@@ -8113,7 +8097,7 @@
       </c>
       <c r="J178" s="2"/>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10">
       <c r="A179" s="2" t="s">
         <v>521</v>
       </c>
@@ -8130,7 +8114,7 @@
         <v>4.13</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>1128</v>
+        <v>1110</v>
       </c>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
@@ -8139,7 +8123,7 @@
       </c>
       <c r="J179" s="2"/>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10">
       <c r="A180" s="2" t="s">
         <v>524</v>
       </c>
@@ -8163,7 +8147,7 @@
       </c>
       <c r="J180" s="2"/>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10">
       <c r="A181" s="2" t="s">
         <v>527</v>
       </c>
@@ -8187,7 +8171,7 @@
       </c>
       <c r="J181" s="2"/>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10">
       <c r="A182" s="2" t="s">
         <v>530</v>
       </c>
@@ -8211,7 +8195,7 @@
       </c>
       <c r="J182" s="2"/>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10">
       <c r="A183" s="2" t="s">
         <v>533</v>
       </c>
@@ -8235,7 +8219,7 @@
       </c>
       <c r="J183" s="2"/>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10">
       <c r="A184" s="2" t="s">
         <v>536</v>
       </c>
@@ -8259,7 +8243,7 @@
       </c>
       <c r="J184" s="2"/>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10">
       <c r="A185" s="2" t="s">
         <v>539</v>
       </c>
@@ -8283,7 +8267,7 @@
       </c>
       <c r="J185" s="2"/>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10">
       <c r="A186" s="2" t="s">
         <v>542</v>
       </c>
@@ -8307,7 +8291,7 @@
       </c>
       <c r="J186" s="2"/>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10">
       <c r="A187" s="2" t="s">
         <v>545</v>
       </c>
@@ -8331,7 +8315,7 @@
       </c>
       <c r="J187" s="2"/>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10">
       <c r="A188" s="2" t="s">
         <v>548</v>
       </c>
@@ -8355,7 +8339,7 @@
       </c>
       <c r="J188" s="2"/>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10">
       <c r="A189" s="2" t="s">
         <v>551</v>
       </c>
@@ -8379,7 +8363,7 @@
       </c>
       <c r="J189" s="2"/>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10">
       <c r="A190" s="2" t="s">
         <v>554</v>
       </c>
@@ -8403,7 +8387,7 @@
       </c>
       <c r="J190" s="2"/>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10">
       <c r="A191" s="2" t="s">
         <v>557</v>
       </c>
@@ -8427,7 +8411,7 @@
       </c>
       <c r="J191" s="2"/>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10">
       <c r="A192" s="2" t="s">
         <v>560</v>
       </c>
@@ -8451,7 +8435,7 @@
       </c>
       <c r="J192" s="2"/>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11">
       <c r="A193" s="2" t="s">
         <v>563</v>
       </c>
@@ -8475,7 +8459,7 @@
       </c>
       <c r="J193" s="2"/>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11">
       <c r="A194" s="2" t="s">
         <v>566</v>
       </c>
@@ -8499,7 +8483,7 @@
       </c>
       <c r="J194" s="2"/>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11">
       <c r="A195" s="2" t="s">
         <v>569</v>
       </c>
@@ -8523,7 +8507,7 @@
       </c>
       <c r="J195" s="2"/>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11">
       <c r="A196" s="2" t="s">
         <v>572</v>
       </c>
@@ -8547,7 +8531,7 @@
       </c>
       <c r="J196" s="2"/>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11">
       <c r="A197" s="2" t="s">
         <v>575</v>
       </c>
@@ -8571,7 +8555,7 @@
       </c>
       <c r="J197" s="2"/>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11">
       <c r="A198" s="2" t="s">
         <v>578</v>
       </c>
@@ -8595,7 +8579,7 @@
       </c>
       <c r="J198" s="2"/>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11">
       <c r="A199" s="2" t="s">
         <v>581</v>
       </c>
@@ -8619,7 +8603,7 @@
       </c>
       <c r="J199" s="2"/>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11">
       <c r="A200" s="2" t="s">
         <v>584</v>
       </c>
@@ -8643,7 +8627,7 @@
       </c>
       <c r="J200" s="2"/>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11">
       <c r="A201" s="2" t="s">
         <v>587</v>
       </c>
@@ -8667,7 +8651,7 @@
       </c>
       <c r="J201" s="2"/>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11">
       <c r="A202" s="2" t="s">
         <v>590</v>
       </c>
@@ -8691,7 +8675,7 @@
       </c>
       <c r="J202" s="2"/>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11">
       <c r="A203" s="2" t="s">
         <v>593</v>
       </c>
@@ -8715,7 +8699,7 @@
       </c>
       <c r="J203" s="2"/>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11">
       <c r="A204" s="2" t="s">
         <v>596</v>
       </c>
@@ -8739,7 +8723,7 @@
       </c>
       <c r="J204" s="2"/>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11">
       <c r="A205" s="6" t="s">
         <v>599</v>
       </c>
@@ -8764,7 +8748,7 @@
       <c r="J205" s="8"/>
       <c r="K205" s="9"/>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11">
       <c r="A206" s="5">
         <v>70109</v>
       </c>
@@ -8789,7 +8773,7 @@
       <c r="J206" s="8"/>
       <c r="K206" s="9"/>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11">
       <c r="A207" s="2" t="s">
         <v>604</v>
       </c>
@@ -8813,7 +8797,7 @@
       </c>
       <c r="J207" s="2"/>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11">
       <c r="A208" s="2" t="s">
         <v>607</v>
       </c>
@@ -8837,7 +8821,7 @@
       </c>
       <c r="J208" s="2"/>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10">
       <c r="A209" s="2" t="s">
         <v>610</v>
       </c>
@@ -8861,7 +8845,7 @@
       </c>
       <c r="J209" s="2"/>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10">
       <c r="A210" s="2" t="s">
         <v>613</v>
       </c>
@@ -8885,7 +8869,7 @@
       </c>
       <c r="J210" s="2"/>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10">
       <c r="A211" s="2" t="s">
         <v>616</v>
       </c>
@@ -8909,7 +8893,7 @@
       </c>
       <c r="J211" s="2"/>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10">
       <c r="A212" s="2" t="s">
         <v>619</v>
       </c>
@@ -8933,7 +8917,7 @@
       </c>
       <c r="J212" s="2"/>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10">
       <c r="A213" s="2" t="s">
         <v>622</v>
       </c>
@@ -8957,7 +8941,7 @@
       </c>
       <c r="J213" s="2"/>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10">
       <c r="A214" s="2" t="s">
         <v>625</v>
       </c>
@@ -8981,7 +8965,7 @@
       </c>
       <c r="J214" s="2"/>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10">
       <c r="A215" s="2" t="s">
         <v>628</v>
       </c>
@@ -9005,7 +8989,7 @@
       </c>
       <c r="J215" s="2"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10">
       <c r="A216" s="2" t="s">
         <v>631</v>
       </c>
@@ -9029,7 +9013,7 @@
       </c>
       <c r="J216" s="2"/>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10">
       <c r="A217" s="2" t="s">
         <v>635</v>
       </c>
@@ -9053,7 +9037,7 @@
       </c>
       <c r="J217" s="2"/>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10">
       <c r="A218" s="2" t="s">
         <v>638</v>
       </c>
@@ -9077,7 +9061,7 @@
       </c>
       <c r="J218" s="2"/>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10">
       <c r="A219" s="2" t="s">
         <v>641</v>
       </c>
@@ -9101,7 +9085,7 @@
       </c>
       <c r="J219" s="2"/>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10">
       <c r="A220" s="2" t="s">
         <v>644</v>
       </c>
@@ -9125,7 +9109,7 @@
       </c>
       <c r="J220" s="2"/>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10">
       <c r="A221" s="2" t="s">
         <v>647</v>
       </c>
@@ -9149,7 +9133,7 @@
       </c>
       <c r="J221" s="2"/>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10">
       <c r="A222" s="2" t="s">
         <v>650</v>
       </c>
@@ -9173,7 +9157,7 @@
       </c>
       <c r="J222" s="2"/>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10">
       <c r="A223" s="2" t="s">
         <v>653</v>
       </c>
@@ -9197,7 +9181,7 @@
       </c>
       <c r="J223" s="2"/>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10">
       <c r="A224" s="2" t="s">
         <v>656</v>
       </c>
@@ -9221,7 +9205,7 @@
       </c>
       <c r="J224" s="2"/>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13">
       <c r="A225" s="2" t="s">
         <v>659</v>
       </c>
@@ -9245,7 +9229,7 @@
       </c>
       <c r="J225" s="2"/>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13">
       <c r="A226" s="2" t="s">
         <v>662</v>
       </c>
@@ -9269,7 +9253,7 @@
       </c>
       <c r="J226" s="2"/>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13">
       <c r="A227" s="2" t="s">
         <v>665</v>
       </c>
@@ -9293,7 +9277,7 @@
       </c>
       <c r="J227" s="2"/>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13">
       <c r="A228" s="2" t="s">
         <v>668</v>
       </c>
@@ -9317,7 +9301,7 @@
       </c>
       <c r="J228" s="2"/>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13">
       <c r="A229" s="2" t="s">
         <v>671</v>
       </c>
@@ -9341,7 +9325,7 @@
       </c>
       <c r="J229" s="2"/>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13">
       <c r="A230" s="2" t="s">
         <v>674</v>
       </c>
@@ -9365,7 +9349,7 @@
       </c>
       <c r="J230" s="2"/>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13">
       <c r="A231" s="2" t="s">
         <v>677</v>
       </c>
@@ -9389,7 +9373,7 @@
       </c>
       <c r="J231" s="2"/>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13">
       <c r="A232" s="5">
         <v>30802</v>
       </c>
@@ -9416,7 +9400,7 @@
       <c r="L232" s="9"/>
       <c r="M232" s="9"/>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13">
       <c r="A233" s="2" t="s">
         <v>682</v>
       </c>
@@ -9440,7 +9424,7 @@
       </c>
       <c r="J233" s="2"/>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13">
       <c r="A234" s="2" t="s">
         <v>685</v>
       </c>
@@ -9464,7 +9448,7 @@
       </c>
       <c r="J234" s="2"/>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13">
       <c r="A235" s="2" t="s">
         <v>688</v>
       </c>
@@ -9488,7 +9472,7 @@
       </c>
       <c r="J235" s="2"/>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13">
       <c r="A236" s="2" t="s">
         <v>691</v>
       </c>
@@ -9512,7 +9496,7 @@
       </c>
       <c r="J236" s="2"/>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13">
       <c r="A237" s="2" t="s">
         <v>694</v>
       </c>
@@ -9536,7 +9520,7 @@
       </c>
       <c r="J237" s="2"/>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13">
       <c r="A238" s="2" t="s">
         <v>697</v>
       </c>
@@ -9560,7 +9544,7 @@
       </c>
       <c r="J238" s="2"/>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13">
       <c r="A239" s="2" t="s">
         <v>700</v>
       </c>
@@ -9584,7 +9568,7 @@
       </c>
       <c r="J239" s="2"/>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13">
       <c r="A240" s="2" t="s">
         <v>703</v>
       </c>
@@ -9608,7 +9592,7 @@
       </c>
       <c r="J240" s="2"/>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10">
       <c r="A241" s="2" t="s">
         <v>706</v>
       </c>
@@ -9632,7 +9616,7 @@
       </c>
       <c r="J241" s="2"/>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10">
       <c r="A242" s="2" t="s">
         <v>709</v>
       </c>
@@ -9656,7 +9640,7 @@
       </c>
       <c r="J242" s="2"/>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10">
       <c r="A243" s="2" t="s">
         <v>712</v>
       </c>
@@ -9680,7 +9664,7 @@
       </c>
       <c r="J243" s="2"/>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10">
       <c r="A244" s="2" t="s">
         <v>715</v>
       </c>
@@ -9704,7 +9688,7 @@
       </c>
       <c r="J244" s="2"/>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10">
       <c r="A245" s="2" t="s">
         <v>718</v>
       </c>
@@ -9728,7 +9712,7 @@
       </c>
       <c r="J245" s="2"/>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10">
       <c r="A246" s="2" t="s">
         <v>721</v>
       </c>
@@ -9752,7 +9736,7 @@
       </c>
       <c r="J246" s="2"/>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10">
       <c r="A247" s="2" t="s">
         <v>724</v>
       </c>
@@ -9776,7 +9760,7 @@
       </c>
       <c r="J247" s="2"/>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10">
       <c r="A248" s="2" t="s">
         <v>727</v>
       </c>
@@ -9800,7 +9784,7 @@
       </c>
       <c r="J248" s="2"/>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10">
       <c r="A249" s="2" t="s">
         <v>730</v>
       </c>
@@ -9824,7 +9808,7 @@
       </c>
       <c r="J249" s="2"/>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10">
       <c r="A250" s="2" t="s">
         <v>733</v>
       </c>
@@ -9848,7 +9832,7 @@
       </c>
       <c r="J250" s="2"/>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10">
       <c r="A251" s="2" t="s">
         <v>736</v>
       </c>
@@ -9872,7 +9856,7 @@
       </c>
       <c r="J251" s="2"/>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10">
       <c r="A252" s="2" t="s">
         <v>739</v>
       </c>
@@ -9896,7 +9880,7 @@
       </c>
       <c r="J252" s="2"/>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10">
       <c r="A253" s="2" t="s">
         <v>742</v>
       </c>
@@ -9920,7 +9904,7 @@
       </c>
       <c r="J253" s="2"/>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10">
       <c r="A254" s="2" t="s">
         <v>745</v>
       </c>
@@ -9944,7 +9928,7 @@
       </c>
       <c r="J254" s="2"/>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10">
       <c r="A255" s="2" t="s">
         <v>748</v>
       </c>
@@ -9961,7 +9945,7 @@
         <v>6.23</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>1128</v>
+        <v>1110</v>
       </c>
       <c r="G255" s="2"/>
       <c r="H255" s="2"/>
@@ -9970,7 +9954,7 @@
       </c>
       <c r="J255" s="2"/>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10">
       <c r="A256" s="2" t="s">
         <v>751</v>
       </c>
@@ -9994,7 +9978,7 @@
       </c>
       <c r="J256" s="2"/>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11">
       <c r="A257" s="2" t="s">
         <v>754</v>
       </c>
@@ -10018,7 +10002,7 @@
       </c>
       <c r="J257" s="2"/>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11">
       <c r="A258" s="2" t="s">
         <v>755</v>
       </c>
@@ -10042,7 +10026,7 @@
       </c>
       <c r="J258" s="2"/>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11">
       <c r="A259" s="2" t="s">
         <v>759</v>
       </c>
@@ -10066,7 +10050,7 @@
       </c>
       <c r="J259" s="2"/>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11">
       <c r="A260" s="2" t="s">
         <v>762</v>
       </c>
@@ -10090,7 +10074,7 @@
       </c>
       <c r="J260" s="2"/>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11">
       <c r="A261" s="2" t="s">
         <v>765</v>
       </c>
@@ -10114,7 +10098,7 @@
       </c>
       <c r="J261" s="2"/>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11">
       <c r="A262" s="2" t="s">
         <v>768</v>
       </c>
@@ -10138,7 +10122,7 @@
       </c>
       <c r="J262" s="2"/>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11">
       <c r="A263" s="2" t="s">
         <v>771</v>
       </c>
@@ -10162,7 +10146,7 @@
       </c>
       <c r="J263" s="2"/>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11">
       <c r="A264" s="2" t="s">
         <v>774</v>
       </c>
@@ -10186,7 +10170,7 @@
       </c>
       <c r="J264" s="2"/>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:11">
       <c r="A265" s="2" t="s">
         <v>777</v>
       </c>
@@ -10210,7 +10194,7 @@
       </c>
       <c r="J265" s="2"/>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11">
       <c r="A266" s="5">
         <v>80305</v>
       </c>
@@ -10235,7 +10219,7 @@
       <c r="J266" s="8"/>
       <c r="K266" s="9"/>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:11">
       <c r="A267" s="2" t="s">
         <v>782</v>
       </c>
@@ -10254,20 +10238,20 @@
       <c r="F267" s="2"/>
       <c r="G267" s="2"/>
       <c r="H267" s="2"/>
-      <c r="I267" s="3" t="s">
+      <c r="I267" s="11" t="s">
+        <v>1120</v>
+      </c>
+      <c r="J267" s="2"/>
+    </row>
+    <row r="268" spans="1:11">
+      <c r="A268" s="2" t="s">
         <v>785</v>
-      </c>
-      <c r="J267" s="2"/>
-    </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A268" s="2" t="s">
-        <v>786</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D268" s="2">
         <v>5.9</v>
@@ -10279,19 +10263,19 @@
       <c r="G268" s="2"/>
       <c r="H268" s="2"/>
       <c r="I268" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="J268" s="2"/>
+    </row>
+    <row r="269" spans="1:11">
+      <c r="A269" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="J268" s="2"/>
-    </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A269" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D269" s="2">
         <v>15.9</v>
@@ -10303,19 +10287,19 @@
       <c r="G269" s="2"/>
       <c r="H269" s="2"/>
       <c r="I269" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="J269" s="2"/>
+    </row>
+    <row r="270" spans="1:11">
+      <c r="A270" s="2" t="s">
         <v>791</v>
-      </c>
-      <c r="J269" s="2"/>
-    </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A270" s="2" t="s">
-        <v>792</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D270" s="2">
         <v>15.9</v>
@@ -10327,19 +10311,19 @@
       <c r="G270" s="2"/>
       <c r="H270" s="2"/>
       <c r="I270" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="J270" s="2"/>
+    </row>
+    <row r="271" spans="1:11">
+      <c r="A271" s="2" t="s">
         <v>794</v>
-      </c>
-      <c r="J270" s="2"/>
-    </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A271" s="2" t="s">
-        <v>795</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D271" s="2">
         <v>4.9000000000000004</v>
@@ -10351,19 +10335,19 @@
       <c r="G271" s="2"/>
       <c r="H271" s="2"/>
       <c r="I271" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="J271" s="2"/>
+    </row>
+    <row r="272" spans="1:11">
+      <c r="A272" s="2" t="s">
         <v>797</v>
-      </c>
-      <c r="J271" s="2"/>
-    </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A272" s="2" t="s">
-        <v>798</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D272" s="2">
         <v>6.5</v>
@@ -10375,19 +10359,19 @@
       <c r="G272" s="2"/>
       <c r="H272" s="2"/>
       <c r="I272" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="J272" s="2"/>
+    </row>
+    <row r="273" spans="1:10">
+      <c r="A273" s="2" t="s">
         <v>800</v>
-      </c>
-      <c r="J272" s="2"/>
-    </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A273" s="2" t="s">
-        <v>801</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D273" s="2">
         <v>5.9</v>
@@ -10399,19 +10383,19 @@
       <c r="G273" s="2"/>
       <c r="H273" s="2"/>
       <c r="I273" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="J273" s="2"/>
+    </row>
+    <row r="274" spans="1:10">
+      <c r="A274" s="2" t="s">
         <v>803</v>
-      </c>
-      <c r="J273" s="2"/>
-    </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A274" s="2" t="s">
-        <v>804</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D274" s="2">
         <v>6.5</v>
@@ -10423,19 +10407,19 @@
       <c r="G274" s="2"/>
       <c r="H274" s="2"/>
       <c r="I274" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="J274" s="2"/>
+    </row>
+    <row r="275" spans="1:10">
+      <c r="A275" s="2" t="s">
         <v>806</v>
-      </c>
-      <c r="J274" s="2"/>
-    </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A275" s="2" t="s">
-        <v>807</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D275" s="2">
         <v>6.5</v>
@@ -10447,19 +10431,19 @@
       <c r="G275" s="2"/>
       <c r="H275" s="2"/>
       <c r="I275" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="J275" s="2"/>
+    </row>
+    <row r="276" spans="1:10">
+      <c r="A276" s="2" t="s">
         <v>809</v>
-      </c>
-      <c r="J275" s="2"/>
-    </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A276" s="2" t="s">
-        <v>810</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D276" s="2">
         <v>6.9</v>
@@ -10471,19 +10455,19 @@
       <c r="G276" s="2"/>
       <c r="H276" s="2"/>
       <c r="I276" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="J276" s="2"/>
+    </row>
+    <row r="277" spans="1:10">
+      <c r="A277" s="2" t="s">
         <v>812</v>
-      </c>
-      <c r="J276" s="2"/>
-    </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A277" s="2" t="s">
-        <v>813</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D277" s="2">
         <v>6.9</v>
@@ -10495,19 +10479,19 @@
       <c r="G277" s="2"/>
       <c r="H277" s="2"/>
       <c r="I277" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="J277" s="2"/>
+    </row>
+    <row r="278" spans="1:10">
+      <c r="A278" s="2" t="s">
         <v>815</v>
-      </c>
-      <c r="J277" s="2"/>
-    </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A278" s="2" t="s">
-        <v>816</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D278" s="2">
         <v>7.9</v>
@@ -10519,19 +10503,19 @@
       <c r="G278" s="2"/>
       <c r="H278" s="2"/>
       <c r="I278" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="J278" s="2"/>
+    </row>
+    <row r="279" spans="1:10">
+      <c r="A279" s="2" t="s">
         <v>818</v>
-      </c>
-      <c r="J278" s="2"/>
-    </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A279" s="2" t="s">
-        <v>819</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D279" s="2">
         <v>7.5</v>
@@ -10543,19 +10527,19 @@
       <c r="G279" s="2"/>
       <c r="H279" s="2"/>
       <c r="I279" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="J279" s="2"/>
+    </row>
+    <row r="280" spans="1:10">
+      <c r="A280" s="2" t="s">
         <v>821</v>
-      </c>
-      <c r="J279" s="2"/>
-    </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A280" s="2" t="s">
-        <v>822</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D280" s="2">
         <v>4.9000000000000004</v>
@@ -10567,19 +10551,19 @@
       <c r="G280" s="2"/>
       <c r="H280" s="2"/>
       <c r="I280" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="J280" s="2"/>
+    </row>
+    <row r="281" spans="1:10">
+      <c r="A281" s="2" t="s">
         <v>824</v>
-      </c>
-      <c r="J280" s="2"/>
-    </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A281" s="2" t="s">
-        <v>825</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D281" s="2">
         <v>6.9</v>
@@ -10591,19 +10575,19 @@
       <c r="G281" s="2"/>
       <c r="H281" s="2"/>
       <c r="I281" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="J281" s="2"/>
+    </row>
+    <row r="282" spans="1:10">
+      <c r="A282" s="2" t="s">
         <v>827</v>
-      </c>
-      <c r="J281" s="2"/>
-    </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A282" s="2" t="s">
-        <v>828</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D282" s="2">
         <v>7.9</v>
@@ -10615,19 +10599,19 @@
       <c r="G282" s="2"/>
       <c r="H282" s="2"/>
       <c r="I282" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="J282" s="2"/>
+    </row>
+    <row r="283" spans="1:10">
+      <c r="A283" s="2" t="s">
         <v>830</v>
-      </c>
-      <c r="J282" s="2"/>
-    </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A283" s="2" t="s">
-        <v>831</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D283" s="2">
         <v>6.9</v>
@@ -10639,19 +10623,19 @@
       <c r="G283" s="2"/>
       <c r="H283" s="2"/>
       <c r="I283" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="J283" s="2"/>
+    </row>
+    <row r="284" spans="1:10">
+      <c r="A284" s="2" t="s">
         <v>833</v>
-      </c>
-      <c r="J283" s="2"/>
-    </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A284" s="2" t="s">
-        <v>834</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D284" s="2">
         <v>7.5</v>
@@ -10663,19 +10647,19 @@
       <c r="G284" s="2"/>
       <c r="H284" s="2"/>
       <c r="I284" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="J284" s="2"/>
+    </row>
+    <row r="285" spans="1:10">
+      <c r="A285" s="2" t="s">
         <v>836</v>
-      </c>
-      <c r="J284" s="2"/>
-    </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A285" s="2" t="s">
-        <v>837</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D285" s="2">
         <v>5.9</v>
@@ -10687,19 +10671,19 @@
       <c r="G285" s="2"/>
       <c r="H285" s="2"/>
       <c r="I285" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="J285" s="2"/>
+    </row>
+    <row r="286" spans="1:10">
+      <c r="A286" s="2" t="s">
         <v>839</v>
-      </c>
-      <c r="J285" s="2"/>
-    </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A286" s="2" t="s">
-        <v>840</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D286" s="2">
         <v>4.9000000000000004</v>
@@ -10711,19 +10695,19 @@
       <c r="G286" s="2"/>
       <c r="H286" s="2"/>
       <c r="I286" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="J286" s="2"/>
+    </row>
+    <row r="287" spans="1:10">
+      <c r="A287" s="2" t="s">
         <v>842</v>
-      </c>
-      <c r="J286" s="2"/>
-    </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A287" s="2" t="s">
-        <v>843</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D287" s="2">
         <v>8.5</v>
@@ -10735,19 +10719,19 @@
       <c r="G287" s="2"/>
       <c r="H287" s="2"/>
       <c r="I287" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="J287" s="2"/>
+    </row>
+    <row r="288" spans="1:10">
+      <c r="A288" s="2" t="s">
         <v>845</v>
-      </c>
-      <c r="J287" s="2"/>
-    </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A288" s="2" t="s">
-        <v>846</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D288" s="2">
         <v>6.9</v>
@@ -10759,19 +10743,19 @@
       <c r="G288" s="2"/>
       <c r="H288" s="2"/>
       <c r="I288" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="J288" s="2"/>
+    </row>
+    <row r="289" spans="1:10">
+      <c r="A289" s="2" t="s">
         <v>848</v>
-      </c>
-      <c r="J288" s="2"/>
-    </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A289" s="2" t="s">
-        <v>849</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="D289" s="2">
         <v>6.5</v>
@@ -10783,19 +10767,19 @@
       <c r="G289" s="2"/>
       <c r="H289" s="2"/>
       <c r="I289" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="J289" s="2"/>
+    </row>
+    <row r="290" spans="1:10">
+      <c r="A290" s="2" t="s">
         <v>851</v>
-      </c>
-      <c r="J289" s="2"/>
-    </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A290" s="2" t="s">
-        <v>852</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D290" s="2">
         <v>10.9</v>
@@ -10807,19 +10791,19 @@
       <c r="G290" s="2"/>
       <c r="H290" s="2"/>
       <c r="I290" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="J290" s="2"/>
+    </row>
+    <row r="291" spans="1:10">
+      <c r="A291" s="2" t="s">
         <v>854</v>
-      </c>
-      <c r="J290" s="2"/>
-    </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A291" s="2" t="s">
-        <v>855</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D291" s="2">
         <v>6.9</v>
@@ -10831,19 +10815,19 @@
       <c r="G291" s="2"/>
       <c r="H291" s="2"/>
       <c r="I291" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="J291" s="2"/>
+    </row>
+    <row r="292" spans="1:10">
+      <c r="A292" s="2" t="s">
         <v>857</v>
-      </c>
-      <c r="J291" s="2"/>
-    </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A292" s="2" t="s">
-        <v>858</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="D292" s="2">
         <v>11.9</v>
@@ -10855,19 +10839,19 @@
       <c r="G292" s="2"/>
       <c r="H292" s="2"/>
       <c r="I292" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="J292" s="2"/>
+    </row>
+    <row r="293" spans="1:10">
+      <c r="A293" s="2" t="s">
         <v>860</v>
-      </c>
-      <c r="J292" s="2"/>
-    </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A293" s="2" t="s">
-        <v>861</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="D293" s="2">
         <v>6.9</v>
@@ -10879,19 +10863,19 @@
       <c r="G293" s="2"/>
       <c r="H293" s="2"/>
       <c r="I293" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="J293" s="2"/>
+    </row>
+    <row r="294" spans="1:10">
+      <c r="A294" s="2" t="s">
         <v>863</v>
-      </c>
-      <c r="J293" s="2"/>
-    </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A294" s="2" t="s">
-        <v>864</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D294" s="2">
         <v>11.9</v>
@@ -10903,19 +10887,19 @@
       <c r="G294" s="2"/>
       <c r="H294" s="2"/>
       <c r="I294" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="J294" s="2"/>
+    </row>
+    <row r="295" spans="1:10">
+      <c r="A295" s="2" t="s">
         <v>866</v>
-      </c>
-      <c r="J294" s="2"/>
-    </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A295" s="2" t="s">
-        <v>867</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D295" s="2">
         <v>6.9</v>
@@ -10927,19 +10911,19 @@
       <c r="G295" s="2"/>
       <c r="H295" s="2"/>
       <c r="I295" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="J295" s="2"/>
+    </row>
+    <row r="296" spans="1:10">
+      <c r="A296" s="2" t="s">
         <v>869</v>
-      </c>
-      <c r="J295" s="2"/>
-    </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A296" s="2" t="s">
-        <v>870</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D296" s="2">
         <v>6.9</v>
@@ -10951,19 +10935,19 @@
       <c r="G296" s="2"/>
       <c r="H296" s="2"/>
       <c r="I296" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="J296" s="2"/>
+    </row>
+    <row r="297" spans="1:10">
+      <c r="A297" s="2" t="s">
         <v>872</v>
-      </c>
-      <c r="J296" s="2"/>
-    </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A297" s="2" t="s">
-        <v>873</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D297" s="2">
         <v>11.9</v>
@@ -10975,19 +10959,19 @@
       <c r="G297" s="2"/>
       <c r="H297" s="2"/>
       <c r="I297" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="J297" s="2"/>
+    </row>
+    <row r="298" spans="1:10">
+      <c r="A298" s="2" t="s">
         <v>875</v>
-      </c>
-      <c r="J297" s="2"/>
-    </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A298" s="2" t="s">
-        <v>876</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="D298" s="2">
         <v>11.9</v>
@@ -10999,19 +10983,19 @@
       <c r="G298" s="2"/>
       <c r="H298" s="2"/>
       <c r="I298" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="J298" s="2"/>
+    </row>
+    <row r="299" spans="1:10">
+      <c r="A299" s="2" t="s">
         <v>878</v>
-      </c>
-      <c r="J298" s="2"/>
-    </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A299" s="2" t="s">
-        <v>879</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D299" s="2">
         <v>11.9</v>
@@ -11023,19 +11007,19 @@
       <c r="G299" s="2"/>
       <c r="H299" s="2"/>
       <c r="I299" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="J299" s="2"/>
+    </row>
+    <row r="300" spans="1:10">
+      <c r="A300" s="2" t="s">
         <v>881</v>
-      </c>
-      <c r="J299" s="2"/>
-    </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A300" s="2" t="s">
-        <v>882</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D300" s="2">
         <v>11.9</v>
@@ -11047,19 +11031,19 @@
       <c r="G300" s="2"/>
       <c r="H300" s="2"/>
       <c r="I300" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="J300" s="2"/>
+    </row>
+    <row r="301" spans="1:10">
+      <c r="A301" s="2" t="s">
         <v>884</v>
-      </c>
-      <c r="J300" s="2"/>
-    </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A301" s="2" t="s">
-        <v>885</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D301" s="2">
         <v>9.9</v>
@@ -11071,19 +11055,19 @@
       <c r="G301" s="2"/>
       <c r="H301" s="2"/>
       <c r="I301" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="J301" s="2"/>
+    </row>
+    <row r="302" spans="1:10">
+      <c r="A302" s="2" t="s">
         <v>887</v>
-      </c>
-      <c r="J301" s="2"/>
-    </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A302" s="2" t="s">
-        <v>888</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="D302" s="2">
         <v>10.9</v>
@@ -11095,19 +11079,19 @@
       <c r="G302" s="2"/>
       <c r="H302" s="2"/>
       <c r="I302" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="J302" s="2"/>
+    </row>
+    <row r="303" spans="1:10">
+      <c r="A303" s="2" t="s">
         <v>890</v>
-      </c>
-      <c r="J302" s="2"/>
-    </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A303" s="2" t="s">
-        <v>891</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D303" s="2">
         <v>6.9</v>
@@ -11116,24 +11100,24 @@
         <v>4.83</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>1128</v>
+        <v>1110</v>
       </c>
       <c r="G303" s="2"/>
       <c r="H303" s="2"/>
       <c r="I303" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="J303" s="2"/>
+    </row>
+    <row r="304" spans="1:10">
+      <c r="A304" s="2" t="s">
         <v>893</v>
-      </c>
-      <c r="J303" s="2"/>
-    </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A304" s="2" t="s">
-        <v>894</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D304" s="2">
         <v>6.9</v>
@@ -11145,19 +11129,19 @@
       <c r="G304" s="2"/>
       <c r="H304" s="2"/>
       <c r="I304" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="J304" s="2"/>
+    </row>
+    <row r="305" spans="1:10">
+      <c r="A305" s="2" t="s">
         <v>896</v>
-      </c>
-      <c r="J304" s="2"/>
-    </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A305" s="2" t="s">
-        <v>897</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D305" s="2">
         <v>5.5</v>
@@ -11169,19 +11153,19 @@
       <c r="G305" s="2"/>
       <c r="H305" s="2"/>
       <c r="I305" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="J305" s="2"/>
+    </row>
+    <row r="306" spans="1:10">
+      <c r="A306" s="2" t="s">
         <v>899</v>
-      </c>
-      <c r="J305" s="2"/>
-    </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A306" s="2" t="s">
-        <v>900</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D306" s="2">
         <v>5.9</v>
@@ -11193,19 +11177,19 @@
       <c r="G306" s="2"/>
       <c r="H306" s="2"/>
       <c r="I306" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="J306" s="2"/>
+    </row>
+    <row r="307" spans="1:10">
+      <c r="A307" s="2" t="s">
         <v>902</v>
-      </c>
-      <c r="J306" s="2"/>
-    </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A307" s="2" t="s">
-        <v>903</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D307" s="2">
         <v>6.5</v>
@@ -11217,19 +11201,19 @@
       <c r="G307" s="2"/>
       <c r="H307" s="2"/>
       <c r="I307" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="J307" s="2"/>
+    </row>
+    <row r="308" spans="1:10">
+      <c r="A308" s="2" t="s">
         <v>905</v>
-      </c>
-      <c r="J307" s="2"/>
-    </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A308" s="2" t="s">
-        <v>906</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D308" s="2">
         <v>7.9</v>
@@ -11241,19 +11225,19 @@
       <c r="G308" s="2"/>
       <c r="H308" s="2"/>
       <c r="I308" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="J308" s="2"/>
+    </row>
+    <row r="309" spans="1:10">
+      <c r="A309" s="2" t="s">
         <v>908</v>
-      </c>
-      <c r="J308" s="2"/>
-    </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A309" s="2" t="s">
-        <v>909</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D309" s="2">
         <v>2.5</v>
@@ -11265,19 +11249,19 @@
       <c r="G309" s="2"/>
       <c r="H309" s="2"/>
       <c r="I309" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="J309" s="2"/>
+    </row>
+    <row r="310" spans="1:10">
+      <c r="A310" s="2" t="s">
         <v>911</v>
-      </c>
-      <c r="J309" s="2"/>
-    </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A310" s="2" t="s">
-        <v>912</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D310" s="2">
         <v>2.5</v>
@@ -11289,19 +11273,19 @@
       <c r="G310" s="2"/>
       <c r="H310" s="2"/>
       <c r="I310" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="J310" s="2"/>
+    </row>
+    <row r="311" spans="1:10">
+      <c r="A311" s="2" t="s">
         <v>914</v>
-      </c>
-      <c r="J310" s="2"/>
-    </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A311" s="2" t="s">
-        <v>915</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="D311" s="2">
         <v>1.5</v>
@@ -11317,135 +11301,135 @@
       </c>
       <c r="J311" s="2"/>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A312" s="2" t="s">
-        <v>917</v>
-      </c>
-      <c r="B312" s="2" t="s">
+    <row r="312" spans="1:10">
+      <c r="A312" s="2">
+        <v>80146</v>
+      </c>
+      <c r="B312" s="12" t="s">
         <v>783</v>
       </c>
-      <c r="C312" s="2" t="s">
-        <v>918</v>
+      <c r="C312" s="12" t="s">
+        <v>1118</v>
       </c>
       <c r="D312" s="2">
-        <v>1.5</v>
+        <v>7.9</v>
       </c>
       <c r="E312" s="2">
-        <v>1.05</v>
+        <v>5.53</v>
       </c>
       <c r="F312" s="2"/>
       <c r="G312" s="2"/>
       <c r="H312" s="2"/>
       <c r="I312" s="3" t="s">
-        <v>919</v>
+        <v>1119</v>
       </c>
       <c r="J312" s="2"/>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A313" s="13">
-        <v>40505</v>
+    <row r="313" spans="1:10">
+      <c r="A313" s="2" t="s">
+        <v>916</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>756</v>
+        <v>783</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>1113</v>
+        <v>917</v>
       </c>
       <c r="D313" s="2">
-        <v>20.399999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="E313" s="2">
-        <v>14.28</v>
+        <v>1.05</v>
       </c>
       <c r="F313" s="2"/>
       <c r="G313" s="2"/>
       <c r="H313" s="2"/>
       <c r="I313" s="3" t="s">
-        <v>1114</v>
+        <v>918</v>
       </c>
       <c r="J313" s="2"/>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A314" s="2" t="s">
-        <v>920</v>
+    <row r="314" spans="1:10">
+      <c r="A314" s="13">
+        <v>40505</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>921</v>
+        <v>1104</v>
       </c>
       <c r="D314" s="2">
-        <v>18.899999999999999</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="E314" s="2">
-        <v>13.23</v>
+        <v>14.28</v>
       </c>
       <c r="F314" s="2"/>
       <c r="G314" s="2"/>
       <c r="H314" s="2"/>
       <c r="I314" s="3" t="s">
-        <v>922</v>
+        <v>1105</v>
       </c>
       <c r="J314" s="2"/>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10">
       <c r="A315" s="2" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="D315" s="2">
-        <v>20.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="E315" s="2">
-        <v>14.63</v>
+        <v>13.23</v>
       </c>
       <c r="F315" s="2"/>
       <c r="G315" s="2"/>
       <c r="H315" s="2"/>
       <c r="I315" s="3" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="J315" s="2"/>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10">
       <c r="A316" s="2" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D316" s="2">
-        <v>22.5</v>
+        <v>20.9</v>
       </c>
       <c r="E316" s="2">
-        <v>15.75</v>
+        <v>14.63</v>
       </c>
       <c r="F316" s="2"/>
       <c r="G316" s="2"/>
       <c r="H316" s="2"/>
       <c r="I316" s="3" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="J316" s="2"/>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10">
       <c r="A317" s="2" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="D317" s="2">
         <v>22.5</v>
@@ -11457,19 +11441,19 @@
       <c r="G317" s="2"/>
       <c r="H317" s="2"/>
       <c r="I317" s="3" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="J317" s="2"/>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10">
       <c r="A318" s="2" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="D318" s="2">
         <v>22.5</v>
@@ -11481,19 +11465,19 @@
       <c r="G318" s="2"/>
       <c r="H318" s="2"/>
       <c r="I318" s="3" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="J318" s="2"/>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10">
       <c r="A319" s="2" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="D319" s="2">
         <v>22.5</v>
@@ -11505,91 +11489,91 @@
       <c r="G319" s="2"/>
       <c r="H319" s="2"/>
       <c r="I319" s="3" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="J319" s="2"/>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10">
       <c r="A320" s="2" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="D320" s="2">
-        <v>18.5</v>
+        <v>22.5</v>
       </c>
       <c r="E320" s="2">
-        <v>12.95</v>
+        <v>15.75</v>
       </c>
       <c r="F320" s="2"/>
       <c r="G320" s="2"/>
       <c r="H320" s="2"/>
       <c r="I320" s="3" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="J320" s="2"/>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:11">
       <c r="A321" s="2" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="D321" s="2">
-        <v>16.3</v>
+        <v>18.5</v>
       </c>
       <c r="E321" s="2">
-        <v>11.41</v>
+        <v>12.95</v>
       </c>
       <c r="F321" s="2"/>
       <c r="G321" s="2"/>
       <c r="H321" s="2"/>
       <c r="I321" s="3" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="J321" s="2"/>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:11">
       <c r="A322" s="2" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="D322" s="2">
-        <v>18.5</v>
+        <v>16.3</v>
       </c>
       <c r="E322" s="2">
-        <v>12.95</v>
+        <v>11.41</v>
       </c>
       <c r="F322" s="2"/>
       <c r="G322" s="2"/>
       <c r="H322" s="2"/>
       <c r="I322" s="3" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="J322" s="2"/>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:11">
       <c r="A323" s="2" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="D323" s="2">
         <v>18.5</v>
@@ -11601,19 +11585,19 @@
       <c r="G323" s="2"/>
       <c r="H323" s="2"/>
       <c r="I323" s="3" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="J323" s="2"/>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:11">
       <c r="A324" s="2" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="D324" s="2">
         <v>18.5</v>
@@ -11625,19 +11609,19 @@
       <c r="G324" s="2"/>
       <c r="H324" s="2"/>
       <c r="I324" s="3" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="J324" s="2"/>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:11">
       <c r="A325" s="2" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="D325" s="2">
         <v>18.5</v>
@@ -11649,19 +11633,19 @@
       <c r="G325" s="2"/>
       <c r="H325" s="2"/>
       <c r="I325" s="3" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="J325" s="2"/>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:11">
       <c r="A326" s="2" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="D326" s="2">
         <v>18.5</v>
@@ -11673,19 +11657,19 @@
       <c r="G326" s="2"/>
       <c r="H326" s="2"/>
       <c r="I326" s="3" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="J326" s="2"/>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:11">
       <c r="A327" s="2" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="D327" s="2">
         <v>18.5</v>
@@ -11697,310 +11681,310 @@
       <c r="G327" s="2"/>
       <c r="H327" s="2"/>
       <c r="I327" s="3" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="J327" s="2"/>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:11">
       <c r="A328" s="2" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="D328" s="2">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="E328" s="2">
-        <v>13.65</v>
+        <v>12.95</v>
       </c>
       <c r="F328" s="2"/>
       <c r="G328" s="2"/>
       <c r="H328" s="2"/>
       <c r="I328" s="3" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="J328" s="2"/>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:11">
       <c r="A329" s="2" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="D329" s="2">
-        <v>22.5</v>
+        <v>19.5</v>
       </c>
       <c r="E329" s="2">
-        <v>15.75</v>
+        <v>13.65</v>
       </c>
       <c r="F329" s="2"/>
       <c r="G329" s="2"/>
       <c r="H329" s="2"/>
       <c r="I329" s="3" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="J329" s="2"/>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:11">
       <c r="A330" s="2" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="D330" s="2">
-        <v>16.899999999999999</v>
+        <v>22.5</v>
       </c>
       <c r="E330" s="2">
-        <v>11.83</v>
-      </c>
-      <c r="F330" s="2" t="s">
-        <v>1128</v>
-      </c>
+        <v>15.75</v>
+      </c>
+      <c r="F330" s="2"/>
       <c r="G330" s="2"/>
       <c r="H330" s="2"/>
       <c r="I330" s="3" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="J330" s="2"/>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:11">
       <c r="A331" s="2" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>756</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="D331" s="2">
-        <v>23.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E331" s="2">
-        <v>16.73</v>
-      </c>
-      <c r="F331" s="2"/>
+        <v>11.83</v>
+      </c>
+      <c r="F331" s="2" t="s">
+        <v>1110</v>
+      </c>
       <c r="G331" s="2"/>
       <c r="H331" s="2"/>
       <c r="I331" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="J331" s="2"/>
+    </row>
+    <row r="332" spans="1:11">
+      <c r="A332" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="D332" s="2">
+        <v>23.9</v>
+      </c>
+      <c r="E332" s="2">
+        <v>16.73</v>
+      </c>
+      <c r="F332" s="2"/>
+      <c r="G332" s="2"/>
+      <c r="H332" s="2"/>
+      <c r="I332" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="J332" s="2"/>
+    </row>
+    <row r="333" spans="1:11">
+      <c r="A333" s="5">
+        <v>100236</v>
+      </c>
+      <c r="B333" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="C333" s="6" t="s">
         <v>973</v>
       </c>
-      <c r="J331" s="2"/>
-    </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A332" s="5">
-        <v>100236</v>
-      </c>
-      <c r="B332" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="C332" s="6" t="s">
+      <c r="D333" s="6">
+        <v>14.9</v>
+      </c>
+      <c r="E333" s="6">
+        <v>10.43</v>
+      </c>
+      <c r="F333" s="6"/>
+      <c r="G333" s="6"/>
+      <c r="H333" s="6"/>
+      <c r="I333" s="7" t="s">
         <v>974</v>
       </c>
-      <c r="D332" s="6">
-        <v>14.9</v>
-      </c>
-      <c r="E332" s="6">
-        <v>10.43</v>
-      </c>
-      <c r="F332" s="6"/>
-      <c r="G332" s="6"/>
-      <c r="H332" s="6"/>
-      <c r="I332" s="7" t="s">
+      <c r="J333" s="8"/>
+      <c r="K333" s="9"/>
+    </row>
+    <row r="334" spans="1:11">
+      <c r="A334" s="2" t="s">
         <v>975</v>
-      </c>
-      <c r="J332" s="8"/>
-      <c r="K332" s="9"/>
-    </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A333" s="2" t="s">
-        <v>976</v>
-      </c>
-      <c r="B333" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C333" s="2" t="s">
-        <v>977</v>
-      </c>
-      <c r="D333" s="2">
-        <v>11.5</v>
-      </c>
-      <c r="E333" s="2">
-        <v>8.0500000000000007</v>
-      </c>
-      <c r="F333" s="2"/>
-      <c r="G333" s="2"/>
-      <c r="H333" s="2"/>
-      <c r="I333" s="3" t="s">
-        <v>978</v>
-      </c>
-      <c r="J333" s="2"/>
-    </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A334" s="2" t="s">
-        <v>979</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="D334" s="2">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="E334" s="2">
-        <v>7.63</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="F334" s="2"/>
       <c r="G334" s="2"/>
       <c r="H334" s="2"/>
       <c r="I334" s="3" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="J334" s="2"/>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:11">
       <c r="A335" s="2" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="D335" s="2">
-        <v>14.9</v>
+        <v>10.9</v>
       </c>
       <c r="E335" s="2">
-        <v>10.15</v>
+        <v>7.63</v>
       </c>
       <c r="F335" s="2"/>
       <c r="G335" s="2"/>
       <c r="H335" s="2"/>
       <c r="I335" s="3" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="J335" s="2"/>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:11">
       <c r="A336" s="2" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="D336" s="2">
-        <v>9.9</v>
+        <v>14.9</v>
       </c>
       <c r="E336" s="2">
-        <v>6.93</v>
+        <v>10.15</v>
       </c>
       <c r="F336" s="2"/>
       <c r="G336" s="2"/>
       <c r="H336" s="2"/>
       <c r="I336" s="3" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="J336" s="2"/>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:11">
       <c r="A337" s="2" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="D337" s="2">
-        <v>16.899999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="E337" s="2">
-        <v>11.83</v>
+        <v>6.93</v>
       </c>
       <c r="F337" s="2"/>
       <c r="G337" s="2"/>
       <c r="H337" s="2"/>
       <c r="I337" s="3" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="J337" s="2"/>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:11">
       <c r="A338" s="2" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="D338" s="2">
-        <v>14</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E338" s="2">
-        <v>9.8000000000000007</v>
+        <v>11.83</v>
       </c>
       <c r="F338" s="2"/>
       <c r="G338" s="2"/>
       <c r="H338" s="2"/>
       <c r="I338" s="3" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="J338" s="2"/>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:11">
       <c r="A339" s="2" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>1115</v>
+        <v>991</v>
       </c>
       <c r="D339" s="2">
-        <v>15.9</v>
+        <v>14</v>
       </c>
       <c r="E339" s="2">
-        <v>11.13</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="F339" s="2"/>
       <c r="G339" s="2"/>
       <c r="H339" s="2"/>
       <c r="I339" s="3" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="J339" s="2"/>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:11">
       <c r="A340" s="2" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>997</v>
+        <v>1106</v>
       </c>
       <c r="D340" s="2">
         <v>15.9</v>
@@ -12012,478 +11996,480 @@
       <c r="G340" s="2"/>
       <c r="H340" s="2"/>
       <c r="I340" s="3" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="J340" s="2"/>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:11">
       <c r="A341" s="2" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="D341" s="2">
-        <v>11.9</v>
+        <v>15.9</v>
       </c>
       <c r="E341" s="2">
-        <v>8.33</v>
+        <v>11.13</v>
       </c>
       <c r="F341" s="2"/>
       <c r="G341" s="2"/>
       <c r="H341" s="2"/>
       <c r="I341" s="3" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="J341" s="2"/>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:11">
       <c r="A342" s="2" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="D342" s="2">
-        <v>6.9</v>
+        <v>11.9</v>
       </c>
       <c r="E342" s="2">
-        <v>4.83</v>
+        <v>8.33</v>
       </c>
       <c r="F342" s="2"/>
       <c r="G342" s="2"/>
       <c r="H342" s="2"/>
       <c r="I342" s="3" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="J342" s="2"/>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:11">
       <c r="A343" s="2" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="D343" s="2">
-        <v>11.5</v>
+        <v>6.9</v>
       </c>
       <c r="E343" s="2">
-        <v>8.0500000000000007</v>
+        <v>4.83</v>
       </c>
       <c r="F343" s="2"/>
       <c r="G343" s="2"/>
       <c r="H343" s="2"/>
       <c r="I343" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J343" s="2"/>
+    </row>
+    <row r="344" spans="1:11">
+      <c r="A344" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C344" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D344" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="E344" s="2">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="F344" s="2"/>
+      <c r="G344" s="2"/>
+      <c r="H344" s="2"/>
+      <c r="I344" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="J344" s="2"/>
+    </row>
+    <row r="345" spans="1:11">
+      <c r="A345" s="5">
+        <v>100224</v>
+      </c>
+      <c r="B345" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C345" s="6" t="s">
         <v>1007</v>
       </c>
-      <c r="J343" s="2"/>
-    </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A344" s="5">
-        <v>100224</v>
-      </c>
-      <c r="B344" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C344" s="6" t="s">
+      <c r="D345" s="6">
+        <v>12.5</v>
+      </c>
+      <c r="E345" s="6">
+        <v>8.75</v>
+      </c>
+      <c r="F345" s="6"/>
+      <c r="G345" s="6"/>
+      <c r="H345" s="6"/>
+      <c r="I345" s="7" t="s">
         <v>1008</v>
       </c>
-      <c r="D344" s="6">
-        <v>12.5</v>
-      </c>
-      <c r="E344" s="6">
-        <v>8.75</v>
-      </c>
-      <c r="F344" s="6"/>
-      <c r="G344" s="6"/>
-      <c r="H344" s="6"/>
-      <c r="I344" s="7" t="s">
+      <c r="J345" s="8"/>
+      <c r="K345" s="9"/>
+    </row>
+    <row r="346" spans="1:11">
+      <c r="A346" s="2" t="s">
         <v>1009</v>
       </c>
-      <c r="J344" s="8"/>
-      <c r="K344" s="9"/>
-    </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A345" s="2" t="s">
+      <c r="B346" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C346" s="2" t="s">
         <v>1010</v>
       </c>
-      <c r="B345" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C345" s="2" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D345" s="2">
+      <c r="D346" s="2">
         <v>11.3</v>
       </c>
-      <c r="E345" s="2">
+      <c r="E346" s="2">
         <v>7.91</v>
-      </c>
-      <c r="F345" s="2"/>
-      <c r="G345" s="2"/>
-      <c r="H345" s="2"/>
-      <c r="I345" s="3" t="s">
-        <v>1012</v>
-      </c>
-      <c r="J345" s="2"/>
-    </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A346" s="2" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B346" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C346" s="2" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D346" s="2">
-        <v>26.9</v>
-      </c>
-      <c r="E346" s="2">
-        <v>18.829999999999998</v>
       </c>
       <c r="F346" s="2"/>
       <c r="G346" s="2"/>
       <c r="H346" s="2"/>
       <c r="I346" s="3" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="J346" s="2"/>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:11">
       <c r="A347" s="2" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="D347" s="2">
-        <v>19.899999999999999</v>
+        <v>26.9</v>
       </c>
       <c r="E347" s="2">
-        <v>13.93</v>
+        <v>18.829999999999998</v>
       </c>
       <c r="F347" s="2"/>
       <c r="G347" s="2"/>
       <c r="H347" s="2"/>
       <c r="I347" s="3" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="J347" s="2"/>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:11">
       <c r="A348" s="2" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>9</v>
+        <v>225</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="D348" s="2">
-        <v>36</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="E348" s="2">
-        <v>25.2</v>
+        <v>13.93</v>
       </c>
       <c r="F348" s="2"/>
       <c r="G348" s="2"/>
       <c r="H348" s="2"/>
       <c r="I348" s="3" t="s">
-        <v>223</v>
+        <v>1017</v>
       </c>
       <c r="J348" s="2"/>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:11">
       <c r="A349" s="2" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>225</v>
+        <v>9</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="D349" s="2">
-        <v>16.899999999999999</v>
+        <v>36</v>
       </c>
       <c r="E349" s="2">
-        <v>11.83</v>
+        <v>25.2</v>
       </c>
       <c r="F349" s="2"/>
       <c r="G349" s="2"/>
       <c r="H349" s="2"/>
       <c r="I349" s="3" t="s">
-        <v>1023</v>
+        <v>223</v>
       </c>
       <c r="J349" s="2"/>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:11">
       <c r="A350" s="2" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="D350" s="2">
-        <v>18.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E350" s="2">
-        <v>12.95</v>
+        <v>11.83</v>
       </c>
       <c r="F350" s="2"/>
       <c r="G350" s="2"/>
       <c r="H350" s="2"/>
       <c r="I350" s="3" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="J350" s="2"/>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:11">
       <c r="A351" s="2" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="D351" s="2">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="E351" s="2">
-        <v>10.85</v>
+        <v>12.95</v>
       </c>
       <c r="F351" s="2"/>
       <c r="G351" s="2"/>
       <c r="H351" s="2"/>
       <c r="I351" s="3" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="J351" s="2"/>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A352" s="13">
-        <v>100218</v>
-      </c>
-      <c r="B352" s="12" t="s">
-        <v>1116</v>
+    <row r="352" spans="1:11">
+      <c r="A352" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>232</v>
+        <v>1027</v>
       </c>
       <c r="D352" s="2">
-        <v>12.9</v>
+        <v>15.5</v>
       </c>
       <c r="E352" s="2">
-        <v>9.0299999999999994</v>
+        <v>10.85</v>
       </c>
       <c r="F352" s="2"/>
       <c r="G352" s="2"/>
       <c r="H352" s="2"/>
-      <c r="I352" s="3"/>
+      <c r="I352" s="3" t="s">
+        <v>1028</v>
+      </c>
       <c r="J352" s="2"/>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A353" s="2" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B353" s="2" t="s">
-        <v>225</v>
+    <row r="353" spans="1:10">
+      <c r="A353" s="13">
+        <v>100218</v>
+      </c>
+      <c r="B353" s="12" t="s">
+        <v>1107</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>1031</v>
+        <v>232</v>
       </c>
       <c r="D353" s="2">
-        <v>19.899999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="E353" s="2">
-        <v>13.93</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="F353" s="2"/>
       <c r="G353" s="2"/>
       <c r="H353" s="2"/>
-      <c r="I353" s="3" t="s">
-        <v>1032</v>
-      </c>
+      <c r="I353" s="3"/>
       <c r="J353" s="2"/>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:10">
       <c r="A354" s="2" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>9</v>
+        <v>225</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="D354" s="2">
-        <v>50.5</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="E354" s="2">
-        <v>35.35</v>
+        <v>13.93</v>
       </c>
       <c r="F354" s="2"/>
       <c r="G354" s="2"/>
       <c r="H354" s="2"/>
       <c r="I354" s="3" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="J354" s="2"/>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:10">
       <c r="A355" s="2" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="D355" s="2">
-        <v>32.5</v>
+        <v>50.5</v>
       </c>
       <c r="E355" s="2">
-        <v>22.75</v>
+        <v>35.35</v>
       </c>
       <c r="F355" s="2"/>
       <c r="G355" s="2"/>
       <c r="H355" s="2"/>
       <c r="I355" s="3" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="J355" s="2"/>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:10">
       <c r="A356" s="2" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="D356" s="2">
-        <v>43.5</v>
+        <v>32.5</v>
       </c>
       <c r="E356" s="2">
-        <v>30.45</v>
+        <v>22.75</v>
       </c>
       <c r="F356" s="2"/>
       <c r="G356" s="2"/>
       <c r="H356" s="2"/>
       <c r="I356" s="3" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="J356" s="2"/>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:10">
       <c r="A357" s="2" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>225</v>
+        <v>9</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="D357" s="2">
-        <v>8.9</v>
+        <v>43.5</v>
       </c>
       <c r="E357" s="2">
-        <v>6.23</v>
+        <v>30.45</v>
       </c>
       <c r="F357" s="2"/>
       <c r="G357" s="2"/>
       <c r="H357" s="2"/>
       <c r="I357" s="3" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="J357" s="2"/>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:10">
       <c r="A358" s="2" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="D358" s="2">
-        <v>14.5</v>
+        <v>8.9</v>
       </c>
       <c r="E358" s="2">
-        <v>10.15</v>
+        <v>6.23</v>
       </c>
       <c r="F358" s="2"/>
       <c r="G358" s="2"/>
       <c r="H358" s="2"/>
       <c r="I358" s="3" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="J358" s="2"/>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A359" s="13">
-        <v>100206</v>
-      </c>
-      <c r="B359" s="12" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C359" s="12" t="s">
-        <v>244</v>
+    <row r="359" spans="1:10">
+      <c r="A359" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>1045</v>
       </c>
       <c r="D359" s="2">
-        <v>18.899999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="E359" s="2">
-        <v>13.23</v>
+        <v>10.15</v>
       </c>
       <c r="F359" s="2"/>
       <c r="G359" s="2"/>
       <c r="H359" s="2"/>
-      <c r="I359" s="3"/>
+      <c r="I359" s="3" t="s">
+        <v>1046</v>
+      </c>
       <c r="J359" s="2"/>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:10">
       <c r="A360" s="13">
-        <v>100220</v>
+        <v>100206</v>
       </c>
       <c r="B360" s="12" t="s">
-        <v>1116</v>
+        <v>1107</v>
       </c>
       <c r="C360" s="12" t="s">
-        <v>1117</v>
+        <v>244</v>
       </c>
       <c r="D360" s="2">
-        <v>9.9</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="E360" s="2">
-        <v>6.93</v>
+        <v>13.23</v>
       </c>
       <c r="F360" s="2"/>
       <c r="G360" s="2"/>
@@ -12491,231 +12477,229 @@
       <c r="I360" s="3"/>
       <c r="J360" s="2"/>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A361" s="2" t="s">
-        <v>1048</v>
-      </c>
-      <c r="B361" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C361" s="2" t="s">
-        <v>1049</v>
+    <row r="361" spans="1:10">
+      <c r="A361" s="13">
+        <v>100220</v>
+      </c>
+      <c r="B361" s="12" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C361" s="12" t="s">
+        <v>1108</v>
       </c>
       <c r="D361" s="2">
-        <v>5.2</v>
+        <v>9.9</v>
       </c>
       <c r="E361" s="2">
-        <v>3.64</v>
+        <v>6.93</v>
       </c>
       <c r="F361" s="2"/>
       <c r="G361" s="2"/>
       <c r="H361" s="2"/>
-      <c r="I361" s="3" t="s">
-        <v>1050</v>
-      </c>
+      <c r="I361" s="3"/>
       <c r="J361" s="2"/>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:10">
       <c r="A362" s="2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="D362" s="2">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="E362" s="2">
-        <v>4.2</v>
+        <v>3.64</v>
       </c>
       <c r="F362" s="2"/>
       <c r="G362" s="2"/>
       <c r="H362" s="2"/>
       <c r="I362" s="3" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="J362" s="2"/>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:10">
       <c r="A363" s="2" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="D363" s="2">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="E363" s="2">
-        <v>4.83</v>
+        <v>4.2</v>
       </c>
       <c r="F363" s="2"/>
       <c r="G363" s="2"/>
       <c r="H363" s="2"/>
       <c r="I363" s="3" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="J363" s="2"/>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:10">
       <c r="A364" s="2" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="D364" s="2">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="E364" s="2">
-        <v>5.53</v>
+        <v>4.83</v>
       </c>
       <c r="F364" s="2"/>
       <c r="G364" s="2"/>
       <c r="H364" s="2"/>
       <c r="I364" s="3" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="J364" s="2"/>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:10">
       <c r="A365" s="2" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="D365" s="2">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="E365" s="2">
-        <v>6.23</v>
+        <v>5.53</v>
       </c>
       <c r="F365" s="2"/>
       <c r="G365" s="2"/>
       <c r="H365" s="2"/>
       <c r="I365" s="3" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="J365" s="2"/>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:10">
       <c r="A366" s="2" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="D366" s="2">
-        <v>12.9</v>
+        <v>8.9</v>
       </c>
       <c r="E366" s="2">
-        <v>9.0299999999999994</v>
+        <v>6.23</v>
       </c>
       <c r="F366" s="2"/>
       <c r="G366" s="2"/>
       <c r="H366" s="2"/>
       <c r="I366" s="3" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="J366" s="2"/>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:10">
       <c r="A367" s="2" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="D367" s="2">
-        <v>7.9</v>
+        <v>12.9</v>
       </c>
       <c r="E367" s="2">
-        <v>5.53</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="F367" s="2"/>
       <c r="G367" s="2"/>
       <c r="H367" s="2"/>
       <c r="I367" s="3" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="J367" s="2"/>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:10">
       <c r="A368" s="2" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>9</v>
+        <v>225</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="D368" s="2">
-        <v>2.5</v>
+        <v>7.9</v>
       </c>
       <c r="E368" s="2">
-        <v>2.5</v>
+        <v>5.53</v>
       </c>
       <c r="F368" s="2"/>
       <c r="G368" s="2"/>
       <c r="H368" s="2"/>
       <c r="I368" s="3" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="J368" s="2"/>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:10">
       <c r="A369" s="2" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>783</v>
+        <v>9</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="D369" s="2">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="E369" s="2">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="F369" s="2"/>
       <c r="G369" s="2"/>
       <c r="H369" s="2"/>
       <c r="I369" s="3" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="J369" s="2"/>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:10">
       <c r="A370" s="2" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="D370" s="2">
         <v>0.3</v>
@@ -12727,19 +12711,19 @@
       <c r="G370" s="2"/>
       <c r="H370" s="2"/>
       <c r="I370" s="3" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="J370" s="2"/>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:10">
       <c r="A371" s="2" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>783</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="D371" s="2">
         <v>0.3</v>
@@ -12751,203 +12735,96 @@
       <c r="G371" s="2"/>
       <c r="H371" s="2"/>
       <c r="I371" s="3" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="J371" s="2"/>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:10">
       <c r="A372" s="2" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>9</v>
+        <v>783</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="D372" s="2">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="E372" s="2">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="F372" s="2"/>
       <c r="G372" s="2"/>
       <c r="H372" s="2"/>
       <c r="I372" s="3" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="J372" s="2"/>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A373" s="2" t="s">
-        <v>1084</v>
-      </c>
-      <c r="B373" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C373" s="2" t="s">
-        <v>1085</v>
-      </c>
-      <c r="D373" s="2">
-        <v>1</v>
-      </c>
-      <c r="E373" s="2">
-        <v>1</v>
-      </c>
-      <c r="F373" s="2"/>
-      <c r="G373" s="2"/>
-      <c r="H373" s="2"/>
-      <c r="I373" s="3" t="s">
-        <v>1083</v>
-      </c>
-      <c r="J373" s="2"/>
-    </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A374" s="2" t="s">
-        <v>1086</v>
-      </c>
-      <c r="B374" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C374" s="2" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D374" s="2">
-        <v>3.3</v>
-      </c>
-      <c r="E374" s="2">
-        <v>3.3</v>
-      </c>
-      <c r="F374" s="2"/>
-      <c r="G374" s="2"/>
-      <c r="H374" s="2"/>
-      <c r="I374" s="3" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J374" s="2"/>
-    </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:10">
+      <c r="A373" s="14">
+        <v>120101</v>
+      </c>
+      <c r="B373" s="12" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C373" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D373" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="E373">
+        <v>3.15</v>
+      </c>
+      <c r="I373" s="11" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10">
+      <c r="A374" s="14">
+        <v>120102</v>
+      </c>
+      <c r="B374" s="12" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C374" s="15" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D374" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="E374">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="I374" s="11" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10">
       <c r="A375" s="14">
-        <v>210546</v>
+        <v>120103</v>
       </c>
       <c r="B375" s="12" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C375" s="12" t="s">
-        <v>1119</v>
+        <v>1111</v>
+      </c>
+      <c r="C375" t="s">
+        <v>1116</v>
       </c>
       <c r="D375" s="12">
-        <v>38</v>
+        <v>3.5</v>
       </c>
       <c r="E375">
-        <v>26.6</v>
-      </c>
-    </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A376" s="14">
-        <v>210535</v>
-      </c>
-      <c r="B376" s="12" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C376" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D376" s="12">
-        <v>6.5</v>
-      </c>
-      <c r="E376">
-        <v>4.55</v>
-      </c>
-    </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A377" s="14">
-        <v>260611</v>
-      </c>
-      <c r="B377" s="12" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C377" s="12" t="s">
-        <v>1121</v>
-      </c>
-      <c r="D377" s="12">
-        <v>6.8</v>
-      </c>
-      <c r="E377">
-        <v>4.76</v>
-      </c>
-    </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A378" s="14">
-        <v>210536</v>
-      </c>
-      <c r="B378" s="12" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C378" t="s">
-        <v>1122</v>
-      </c>
-      <c r="D378" s="12">
-        <v>12</v>
-      </c>
-      <c r="E378">
-        <v>8.4</v>
-      </c>
-    </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A379" s="14">
-        <v>210537</v>
-      </c>
-      <c r="B379" s="12" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C379" t="s">
-        <v>1123</v>
-      </c>
-      <c r="D379" s="12">
-        <v>14</v>
-      </c>
-      <c r="E379">
-        <v>9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A380" s="14">
-        <v>210545</v>
-      </c>
-      <c r="B380" s="12" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C380" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D380" s="12">
-        <v>17</v>
-      </c>
-      <c r="E380">
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A381" s="14">
-        <v>210526</v>
-      </c>
-      <c r="B381" s="12" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C381" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D381" s="12">
-        <v>37</v>
-      </c>
-      <c r="E381">
-        <v>25.9</v>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="I375" t="s">
+        <v>1117</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J374" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J372" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -13256,65 +13133,64 @@
     <hyperlink ref="I309" r:id="rId305" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
     <hyperlink ref="I310" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
     <hyperlink ref="I311" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="I312" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="I314" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="I315" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="I316" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="I317" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="I318" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="I319" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="I320" r:id="rId315" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="I321" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="I322" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="I323" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="I324" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="I325" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="I326" r:id="rId321" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="I327" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="I328" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="I329" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="I330" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="I331" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="I332" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="I333" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="I334" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="I335" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="I336" r:id="rId331" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="I337" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="I338" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="I339" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="I340" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="I341" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="I342" r:id="rId337" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="I343" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="I344" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="I345" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="I346" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="I347" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="I348" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="I349" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="I350" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="I351" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="I353" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="I354" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="I355" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="I356" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="I357" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="I358" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="I361" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="I362" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="I363" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="I364" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="I365" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="I366" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="I367" r:id="rId359" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="I368" r:id="rId360" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="I369" r:id="rId361" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="I370" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="I371" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="I372" r:id="rId364" xr:uid="{00000000-0004-0000-0000-00007F010000}"/>
-    <hyperlink ref="I373" r:id="rId365" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="I374" r:id="rId366" xr:uid="{00000000-0004-0000-0000-000081010000}"/>
+    <hyperlink ref="I313" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="I315" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="I316" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="I317" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="I318" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="I319" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="I320" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="I321" r:id="rId315" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="I322" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="I323" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="I324" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="I325" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="I326" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="I327" r:id="rId321" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="I328" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="I329" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="I330" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="I331" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="I332" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="I333" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="I334" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="I335" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="I336" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="I337" r:id="rId331" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="I338" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="I339" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="I340" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="I341" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="I342" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="I343" r:id="rId337" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="I344" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="I345" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="I346" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="I347" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="I348" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="I349" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="I350" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="I351" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="I352" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="I354" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="I355" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="I356" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="I357" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="I358" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="I359" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="I362" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="I363" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="I364" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="I365" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="I366" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="I367" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="I368" r:id="rId359" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="I369" r:id="rId360" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="I370" r:id="rId361" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="I371" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="I372" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="I373" r:id="rId364" xr:uid="{F9160EA0-F07B-4BB5-B702-F5073AA95056}"/>
+    <hyperlink ref="I374" r:id="rId365" xr:uid="{1AC55159-5C0D-4F25-94CA-0E2E9DEE3542}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/TTABLEAU DES PRIX AVEC REF.xlsx
+++ b/TTABLEAU DES PRIX AVEC REF.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melou\blazing-dynasty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2009645-D2C3-4308-BAEF-3446A65BE841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC32455-E2E2-4706-AC24-3656A79C89EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15135" yWindow="255" windowWidth="13665" windowHeight="14925" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13935" yWindow="75" windowWidth="13665" windowHeight="14925" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$372</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$375</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="1121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="1126">
   <si>
     <t>Art</t>
   </si>
@@ -1788,9 +1788,6 @@
     <t>Just Fruity. Gel douche crémeux Mangue *Distributeur à pompe 090104 vendu séparément</t>
   </si>
   <si>
-    <t>https://www.mihi.care/storage/mini/26/02/mpYrTS2T5OFJJI17usAKwwqT51ALonxhGe1bECRG.png</t>
-  </si>
-  <si>
     <t>20205</t>
   </si>
   <si>
@@ -1806,9 +1803,6 @@
     <t>Hand Help. Baume pour les mains Help Hand</t>
   </si>
   <si>
-    <t>https://www.mihi.care/storage/mini/23/12/ICTYeXdilqgJ1iqr51jMCAxbab0HyLRw9inksyLD.png</t>
-  </si>
-  <si>
     <t>20207</t>
   </si>
   <si>
@@ -3360,9 +3354,6 @@
     <t>Rupture</t>
   </si>
   <si>
-    <t>Oui</t>
-  </si>
-  <si>
     <t>nutrition</t>
   </si>
   <si>
@@ -3391,13 +3382,37 @@
   </si>
   <si>
     <t>https://www.mihi.care/storage/26/08/7GUlemeYM4xjOMEdN8AQJLiLAIlAdVnFzYHc262U.png</t>
+  </si>
+  <si>
+    <t>Spa Mood. Soothing Hand Cream Soft Lavender</t>
+  </si>
+  <si>
+    <t>Spa Mood. Crème pour les mains Balance au bois de santal</t>
+  </si>
+  <si>
+    <t>Spa Mood. Crème réparatrice pour les mains « Biscuit aux épices 3,5</t>
+  </si>
+  <si>
+    <t>https://www.mihi.care/storage/mini/26/09/RITOL4gaYpWr7wLtbTVeLwdKf1s9XHbpuTfPZUKe.png</t>
+  </si>
+  <si>
+    <t>https://www.mihi.care/storage/mini/26/09/zJmNlYkyjhxNOFGvQYQVAVjUW46DWXt3KWKU3CvO.png</t>
+  </si>
+  <si>
+    <t>https://www.mihi.care/storage/mini/26/09/WKbl1LZjui0aNbQDwt9OJ3szc1soQWXB6wVLGeqk.png</t>
+  </si>
+  <si>
+    <t>https://www.mihi.care/storage/mini/26/09/d7zBia1BHtG5Akjh7zisvBMXdc9DI22n4vlPURMM.png</t>
+  </si>
+  <si>
+    <t>https://www.mihi.care/storage/mini/26/07/tM0TGy6Er6F7Q4ionXoL02WiWeH7CcLEp8q3VJfB.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3445,6 +3460,11 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF212529"/>
+      <name val="Jost"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF212529"/>
       <name val="Jost"/>
     </font>
@@ -3497,7 +3517,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3525,6 +3545,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3792,7 +3815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M375"/>
+  <dimension ref="A1:M378"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -3819,10 +3842,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -3857,7 +3880,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="11" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="J2" s="2"/>
     </row>
@@ -3881,7 +3904,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="11" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="J3" s="2"/>
     </row>
@@ -3905,7 +3928,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="11" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J4" s="2"/>
     </row>
@@ -3929,7 +3952,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="11" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="J5" s="2"/>
     </row>
@@ -3953,7 +3976,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="11" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="J6" s="2"/>
     </row>
@@ -3977,7 +4000,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="11" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J7" s="2"/>
     </row>
@@ -4001,7 +4024,7 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="11" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="J8" s="2"/>
     </row>
@@ -4025,7 +4048,7 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="11" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="J9" s="2"/>
     </row>
@@ -4049,7 +4072,7 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="11" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="J10" s="2"/>
     </row>
@@ -4097,7 +4120,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="11" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="J12" s="2"/>
     </row>
@@ -4121,7 +4144,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="11" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="J13" s="2"/>
     </row>
@@ -4169,7 +4192,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="11" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="J15" s="2"/>
     </row>
@@ -4265,7 +4288,7 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="3" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J19" s="2"/>
     </row>
@@ -4313,7 +4336,7 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="11" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="J21" s="2"/>
     </row>
@@ -4457,7 +4480,7 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="11" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="J27" s="2"/>
     </row>
@@ -4529,7 +4552,7 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="11" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="J30" s="2"/>
     </row>
@@ -4721,7 +4744,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="11" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="J38" s="2"/>
     </row>
@@ -4745,7 +4768,7 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="11" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="J39" s="2"/>
     </row>
@@ -4769,7 +4792,7 @@
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="11" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="J40" s="2"/>
     </row>
@@ -4981,9 +5004,7 @@
       <c r="E49" s="2">
         <v>5.25</v>
       </c>
-      <c r="F49" s="2" t="s">
-        <v>1110</v>
-      </c>
+      <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="3" t="s">
@@ -6617,7 +6638,7 @@
         <v>253</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="D117" s="2">
         <v>37</v>
@@ -6629,7 +6650,7 @@
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
       <c r="I117" s="3" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="J117" s="2"/>
     </row>
@@ -7649,7 +7670,7 @@
         <v>9</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="D160" s="2">
         <v>12.5</v>
@@ -7661,7 +7682,7 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
       <c r="I160" s="3" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="J160" s="2"/>
     </row>
@@ -8113,9 +8134,7 @@
       <c r="E179" s="2">
         <v>4.13</v>
       </c>
-      <c r="F179" s="2" t="s">
-        <v>1110</v>
-      </c>
+      <c r="F179" s="2"/>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
       <c r="I179" s="3" t="s">
@@ -8622,20 +8641,20 @@
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
-      <c r="I200" s="3" t="s">
-        <v>586</v>
+      <c r="I200" s="11" t="s">
+        <v>1125</v>
       </c>
       <c r="J200" s="2"/>
     </row>
     <row r="201" spans="1:11">
       <c r="A201" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D201" s="2">
         <v>5.9</v>
@@ -8647,19 +8666,19 @@
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
       <c r="I201" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J201" s="2"/>
     </row>
     <row r="202" spans="1:11">
       <c r="A202" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D202" s="2">
         <v>5.5</v>
@@ -8670,20 +8689,20 @@
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
-      <c r="I202" s="3" t="s">
-        <v>592</v>
+      <c r="I202" s="11" t="s">
+        <v>1124</v>
       </c>
       <c r="J202" s="2"/>
     </row>
     <row r="203" spans="1:11">
       <c r="A203" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D203" s="2">
         <v>4.8</v>
@@ -8695,19 +8714,19 @@
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
       <c r="I203" s="3" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="J203" s="2"/>
     </row>
     <row r="204" spans="1:11">
       <c r="A204" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D204" s="2">
         <v>6.9</v>
@@ -8719,19 +8738,19 @@
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
       <c r="I204" s="3" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="J204" s="2"/>
     </row>
     <row r="205" spans="1:11">
       <c r="A205" s="6" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>207</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D205" s="6">
         <v>6.9</v>
@@ -8743,7 +8762,7 @@
       <c r="G205" s="6"/>
       <c r="H205" s="6"/>
       <c r="I205" s="7" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="J205" s="8"/>
       <c r="K205" s="9"/>
@@ -8756,7 +8775,7 @@
         <v>207</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D206" s="6">
         <v>10.9</v>
@@ -8768,20 +8787,20 @@
       <c r="G206" s="6"/>
       <c r="H206" s="6"/>
       <c r="I206" s="7" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="J206" s="8"/>
       <c r="K206" s="9"/>
     </row>
     <row r="207" spans="1:11">
       <c r="A207" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>430</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D207" s="2">
         <v>5</v>
@@ -8793,19 +8812,19 @@
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
       <c r="I207" s="3" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="J207" s="2"/>
     </row>
     <row r="208" spans="1:11">
       <c r="A208" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>426</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D208" s="2">
         <v>9.5</v>
@@ -8817,19 +8836,19 @@
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
       <c r="I208" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="J208" s="2"/>
     </row>
     <row r="209" spans="1:10">
       <c r="A209" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>426</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D209" s="2">
         <v>9.5</v>
@@ -8841,19 +8860,19 @@
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
       <c r="I209" s="3" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="J209" s="2"/>
     </row>
     <row r="210" spans="1:10">
       <c r="A210" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D210" s="2">
         <v>1.2</v>
@@ -8865,19 +8884,19 @@
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
       <c r="I210" s="3" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="J210" s="2"/>
     </row>
     <row r="211" spans="1:10">
       <c r="A211" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D211" s="2">
         <v>1.2</v>
@@ -8889,19 +8908,19 @@
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
       <c r="I211" s="3" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="J211" s="2"/>
     </row>
     <row r="212" spans="1:10">
       <c r="A212" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D212" s="2">
         <v>1.2</v>
@@ -8913,19 +8932,19 @@
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
       <c r="I212" s="3" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="J212" s="2"/>
     </row>
     <row r="213" spans="1:10">
       <c r="A213" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D213" s="2">
         <v>1.2</v>
@@ -8937,19 +8956,19 @@
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
       <c r="I213" s="3" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="J213" s="2"/>
     </row>
     <row r="214" spans="1:10">
       <c r="A214" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D214" s="2">
         <v>4.5</v>
@@ -8961,403 +8980,401 @@
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
       <c r="I214" s="3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="J214" s="2"/>
     </row>
     <row r="215" spans="1:10">
-      <c r="A215" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="B215" s="2" t="s">
+      <c r="A215" s="2">
+        <v>21710</v>
+      </c>
+      <c r="B215" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="C215" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="D215" s="2">
-        <v>1.5</v>
-      </c>
+      <c r="C215" s="12" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D215" s="2"/>
       <c r="E215" s="2">
-        <v>1.05</v>
-      </c>
-      <c r="F215" s="2"/>
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="F215" s="11"/>
       <c r="G215" s="2"/>
       <c r="H215" s="2"/>
-      <c r="I215" s="3" t="s">
-        <v>630</v>
+      <c r="I215" s="11" t="s">
+        <v>1122</v>
       </c>
       <c r="J215" s="2"/>
     </row>
     <row r="216" spans="1:10">
-      <c r="A216" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>632</v>
+      <c r="A216" s="2">
+        <v>21709</v>
+      </c>
+      <c r="B216" s="12" t="s">
+        <v>207</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>633</v>
+        <v>1118</v>
       </c>
       <c r="D216" s="2">
-        <v>7.9</v>
+        <v>3.5</v>
       </c>
       <c r="E216" s="2">
-        <v>5.53</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
       <c r="I216" s="3" t="s">
-        <v>634</v>
+        <v>1121</v>
       </c>
       <c r="J216" s="2"/>
     </row>
-    <row r="217" spans="1:10">
-      <c r="A217" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>636</v>
+    <row r="217" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A217" s="2">
+        <v>21708</v>
+      </c>
+      <c r="B217" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C217" s="16" t="s">
+        <v>1119</v>
       </c>
       <c r="D217" s="2">
-        <v>7.9</v>
+        <v>3.5</v>
       </c>
       <c r="E217" s="2">
-        <v>5.53</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
       <c r="I217" s="3" t="s">
-        <v>637</v>
+        <v>1123</v>
       </c>
       <c r="J217" s="2"/>
     </row>
     <row r="218" spans="1:10">
       <c r="A218" s="2" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>632</v>
+        <v>207</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="D218" s="2">
-        <v>7.9</v>
+        <v>1.5</v>
       </c>
       <c r="E218" s="2">
-        <v>5.53</v>
+        <v>1.05</v>
       </c>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
       <c r="I218" s="3" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="J218" s="2"/>
     </row>
     <row r="219" spans="1:10">
       <c r="A219" s="2" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="D219" s="2">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="E219" s="2">
-        <v>4.83</v>
+        <v>5.53</v>
       </c>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
       <c r="I219" s="3" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="J219" s="2"/>
     </row>
     <row r="220" spans="1:10">
       <c r="A220" s="2" t="s">
-        <v>644</v>
+        <v>633</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="D220" s="2">
-        <v>11.9</v>
+        <v>7.9</v>
       </c>
       <c r="E220" s="2">
-        <v>8.33</v>
+        <v>5.53</v>
       </c>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
       <c r="I220" s="3" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="J220" s="2"/>
     </row>
     <row r="221" spans="1:10">
       <c r="A221" s="2" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="D221" s="2">
-        <v>0.9</v>
+        <v>7.9</v>
       </c>
       <c r="E221" s="2">
-        <v>0.9</v>
+        <v>5.53</v>
       </c>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
       <c r="I221" s="3" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="J221" s="2"/>
     </row>
     <row r="222" spans="1:10">
       <c r="A222" s="2" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="D222" s="2">
-        <v>0.9</v>
+        <v>6.9</v>
       </c>
       <c r="E222" s="2">
-        <v>0.9</v>
+        <v>4.83</v>
       </c>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
       <c r="I222" s="3" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="J222" s="2"/>
     </row>
     <row r="223" spans="1:10">
       <c r="A223" s="2" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="D223" s="2">
-        <v>6.9</v>
+        <v>11.9</v>
       </c>
       <c r="E223" s="2">
-        <v>4.83</v>
+        <v>8.33</v>
       </c>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
       <c r="I223" s="3" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="J223" s="2"/>
     </row>
     <row r="224" spans="1:10">
       <c r="A224" s="2" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="D224" s="2">
-        <v>6.9</v>
+        <v>0.9</v>
       </c>
       <c r="E224" s="2">
-        <v>4.83</v>
+        <v>0.9</v>
       </c>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
       <c r="I224" s="3" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="J224" s="2"/>
     </row>
     <row r="225" spans="1:13">
       <c r="A225" s="2" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="D225" s="2">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="E225" s="2">
-        <v>7.63</v>
+        <v>0.9</v>
       </c>
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
       <c r="I225" s="3" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="J225" s="2"/>
     </row>
     <row r="226" spans="1:13">
       <c r="A226" s="2" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="D226" s="2">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="E226" s="2">
-        <v>5.53</v>
+        <v>4.83</v>
       </c>
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
       <c r="I226" s="3" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="J226" s="2"/>
     </row>
     <row r="227" spans="1:13">
       <c r="A227" s="2" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
       <c r="D227" s="2">
-        <v>10.9</v>
+        <v>6.9</v>
       </c>
       <c r="E227" s="2">
-        <v>7.63</v>
+        <v>4.83</v>
       </c>
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
       <c r="I227" s="3" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="J227" s="2"/>
     </row>
     <row r="228" spans="1:13">
       <c r="A228" s="2" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="D228" s="2">
-        <v>1</v>
+        <v>10.9</v>
       </c>
       <c r="E228" s="2">
-        <v>1</v>
+        <v>7.63</v>
       </c>
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
       <c r="I228" s="3" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="J228" s="2"/>
     </row>
     <row r="229" spans="1:13">
       <c r="A229" s="2" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="D229" s="2">
-        <v>16.899999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="E229" s="2">
-        <v>11.83</v>
+        <v>5.53</v>
       </c>
       <c r="F229" s="2"/>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
       <c r="I229" s="3" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="J229" s="2"/>
     </row>
     <row r="230" spans="1:13">
       <c r="A230" s="2" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="D230" s="2">
-        <v>16.899999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="E230" s="2">
-        <v>11.83</v>
+        <v>7.63</v>
       </c>
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
       <c r="I230" s="3" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="J230" s="2"/>
     </row>
     <row r="231" spans="1:13">
       <c r="A231" s="2" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="D231" s="2">
         <v>1</v>
@@ -9369,526 +9386,526 @@
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
       <c r="I231" s="3" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="J231" s="2"/>
     </row>
     <row r="232" spans="1:13">
-      <c r="A232" s="5">
-        <v>30802</v>
-      </c>
-      <c r="B232" s="6" t="s">
-        <v>632</v>
-      </c>
-      <c r="C232" s="6" t="s">
-        <v>680</v>
-      </c>
-      <c r="D232" s="6">
-        <v>7.9</v>
-      </c>
-      <c r="E232" s="6">
-        <v>5.53</v>
-      </c>
-      <c r="F232" s="6"/>
-      <c r="G232" s="6"/>
-      <c r="H232" s="6"/>
-      <c r="I232" s="7" t="s">
-        <v>681</v>
-      </c>
-      <c r="J232" s="8"/>
-      <c r="K232" s="9"/>
-      <c r="L232" s="9"/>
-      <c r="M232" s="9"/>
+      <c r="A232" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="D232" s="2">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="E232" s="2">
+        <v>11.83</v>
+      </c>
+      <c r="F232" s="2"/>
+      <c r="G232" s="2"/>
+      <c r="H232" s="2"/>
+      <c r="I232" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="J232" s="2"/>
     </row>
     <row r="233" spans="1:13">
       <c r="A233" s="2" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="D233" s="2">
-        <v>7.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E233" s="2">
-        <v>5.53</v>
+        <v>11.83</v>
       </c>
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
       <c r="I233" s="3" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="J233" s="2"/>
     </row>
     <row r="234" spans="1:13">
       <c r="A234" s="2" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D234" s="2">
-        <v>9.5</v>
+        <v>1</v>
       </c>
       <c r="E234" s="2">
-        <v>6.65</v>
+        <v>1</v>
       </c>
       <c r="F234" s="2"/>
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
       <c r="I234" s="3" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="J234" s="2"/>
     </row>
     <row r="235" spans="1:13">
-      <c r="A235" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="D235" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="E235" s="2">
-        <v>6.65</v>
-      </c>
-      <c r="F235" s="2"/>
-      <c r="G235" s="2"/>
-      <c r="H235" s="2"/>
-      <c r="I235" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="J235" s="2"/>
+      <c r="A235" s="5">
+        <v>30802</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="D235" s="6">
+        <v>7.9</v>
+      </c>
+      <c r="E235" s="6">
+        <v>5.53</v>
+      </c>
+      <c r="F235" s="6"/>
+      <c r="G235" s="6"/>
+      <c r="H235" s="6"/>
+      <c r="I235" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="J235" s="8"/>
+      <c r="K235" s="9"/>
+      <c r="L235" s="9"/>
+      <c r="M235" s="9"/>
     </row>
     <row r="236" spans="1:13">
       <c r="A236" s="2" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="D236" s="2">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
       <c r="E236" s="2">
-        <v>6.65</v>
+        <v>5.53</v>
       </c>
       <c r="F236" s="2"/>
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
       <c r="I236" s="3" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="J236" s="2"/>
     </row>
     <row r="237" spans="1:13">
       <c r="A237" s="2" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="D237" s="2">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="E237" s="2">
-        <v>6.23</v>
+        <v>6.65</v>
       </c>
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
       <c r="I237" s="3" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="J237" s="2"/>
     </row>
     <row r="238" spans="1:13">
       <c r="A238" s="2" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="D238" s="2">
-        <v>0.9</v>
+        <v>9.5</v>
       </c>
       <c r="E238" s="2">
-        <v>0.9</v>
+        <v>6.65</v>
       </c>
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
       <c r="I238" s="3" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="J238" s="2"/>
     </row>
     <row r="239" spans="1:13">
       <c r="A239" s="2" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D239" s="2">
-        <v>0.9</v>
+        <v>9.5</v>
       </c>
       <c r="E239" s="2">
-        <v>0.9</v>
+        <v>6.65</v>
       </c>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
       <c r="H239" s="2"/>
       <c r="I239" s="3" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="J239" s="2"/>
     </row>
     <row r="240" spans="1:13">
       <c r="A240" s="2" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="D240" s="2">
-        <v>5.9</v>
+        <v>8.9</v>
       </c>
       <c r="E240" s="2">
-        <v>4.13</v>
+        <v>6.23</v>
       </c>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
       <c r="H240" s="2"/>
       <c r="I240" s="3" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="J240" s="2"/>
     </row>
     <row r="241" spans="1:10">
       <c r="A241" s="2" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="D241" s="2">
-        <v>7.9</v>
+        <v>0.9</v>
       </c>
       <c r="E241" s="2">
-        <v>5.53</v>
+        <v>0.9</v>
       </c>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
       <c r="I241" s="3" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="J241" s="2"/>
     </row>
     <row r="242" spans="1:10">
       <c r="A242" s="2" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D242" s="2">
-        <v>9.9</v>
+        <v>0.9</v>
       </c>
       <c r="E242" s="2">
-        <v>6.93</v>
+        <v>0.9</v>
       </c>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
       <c r="I242" s="3" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="J242" s="2"/>
     </row>
     <row r="243" spans="1:10">
       <c r="A243" s="2" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="D243" s="2">
-        <v>8.6999999999999993</v>
+        <v>5.9</v>
       </c>
       <c r="E243" s="2">
-        <v>6.09</v>
+        <v>4.13</v>
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
       <c r="I243" s="3" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="J243" s="2"/>
     </row>
     <row r="244" spans="1:10">
       <c r="A244" s="2" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="D244" s="2">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="E244" s="2">
-        <v>4.13</v>
+        <v>5.53</v>
       </c>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
       <c r="H244" s="2"/>
       <c r="I244" s="3" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="J244" s="2"/>
     </row>
     <row r="245" spans="1:10">
       <c r="A245" s="2" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="D245" s="2">
-        <v>10.5</v>
+        <v>9.9</v>
       </c>
       <c r="E245" s="2">
-        <v>7.35</v>
+        <v>6.93</v>
       </c>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
       <c r="I245" s="3" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="J245" s="2"/>
     </row>
     <row r="246" spans="1:10">
       <c r="A246" s="2" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="D246" s="2">
-        <v>5.9</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="E246" s="2">
-        <v>4.13</v>
+        <v>6.09</v>
       </c>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
       <c r="I246" s="3" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="J246" s="2"/>
     </row>
     <row r="247" spans="1:10">
       <c r="A247" s="2" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="D247" s="2">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="E247" s="2">
-        <v>4.55</v>
+        <v>4.13</v>
       </c>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
       <c r="I247" s="3" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="J247" s="2"/>
     </row>
     <row r="248" spans="1:10">
       <c r="A248" s="2" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="D248" s="2">
-        <v>7.9</v>
+        <v>10.5</v>
       </c>
       <c r="E248" s="2">
-        <v>5.53</v>
+        <v>7.35</v>
       </c>
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
       <c r="H248" s="2"/>
       <c r="I248" s="3" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="J248" s="2"/>
     </row>
     <row r="249" spans="1:10">
       <c r="A249" s="2" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="D249" s="2">
-        <v>9.6</v>
+        <v>5.9</v>
       </c>
       <c r="E249" s="2">
-        <v>6.72</v>
+        <v>4.13</v>
       </c>
       <c r="F249" s="2"/>
       <c r="G249" s="2"/>
       <c r="H249" s="2"/>
       <c r="I249" s="3" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="J249" s="2"/>
     </row>
     <row r="250" spans="1:10">
       <c r="A250" s="2" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="D250" s="2">
-        <v>9.6</v>
+        <v>6.5</v>
       </c>
       <c r="E250" s="2">
-        <v>6.72</v>
+        <v>4.55</v>
       </c>
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
       <c r="I250" s="3" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="J250" s="2"/>
     </row>
     <row r="251" spans="1:10">
       <c r="A251" s="2" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="D251" s="2">
-        <v>10.1</v>
+        <v>7.9</v>
       </c>
       <c r="E251" s="2">
-        <v>7.07</v>
+        <v>5.53</v>
       </c>
       <c r="F251" s="2"/>
       <c r="G251" s="2"/>
       <c r="H251" s="2"/>
       <c r="I251" s="3" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="J251" s="2"/>
     </row>
     <row r="252" spans="1:10">
       <c r="A252" s="2" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="D252" s="2">
-        <v>10.9</v>
+        <v>9.6</v>
       </c>
       <c r="E252" s="2">
-        <v>7.63</v>
+        <v>6.72</v>
       </c>
       <c r="F252" s="2"/>
       <c r="G252" s="2"/>
       <c r="H252" s="2"/>
       <c r="I252" s="3" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="J252" s="2"/>
     </row>
     <row r="253" spans="1:10">
       <c r="A253" s="2" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="D253" s="2">
         <v>9.6</v>
@@ -9900,189 +9917,187 @@
       <c r="G253" s="2"/>
       <c r="H253" s="2"/>
       <c r="I253" s="3" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="J253" s="2"/>
     </row>
     <row r="254" spans="1:10">
       <c r="A254" s="2" t="s">
-        <v>745</v>
+        <v>734</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="D254" s="2">
-        <v>5.9</v>
+        <v>10.1</v>
       </c>
       <c r="E254" s="2">
-        <v>4.13</v>
+        <v>7.07</v>
       </c>
       <c r="F254" s="2"/>
       <c r="G254" s="2"/>
       <c r="H254" s="2"/>
       <c r="I254" s="3" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="J254" s="2"/>
     </row>
     <row r="255" spans="1:10">
       <c r="A255" s="2" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>430</v>
+        <v>630</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="D255" s="2">
-        <v>8.9</v>
+        <v>10.9</v>
       </c>
       <c r="E255" s="2">
-        <v>6.23</v>
-      </c>
-      <c r="F255" s="2" t="s">
-        <v>1110</v>
-      </c>
+        <v>7.63</v>
+      </c>
+      <c r="F255" s="2"/>
       <c r="G255" s="2"/>
       <c r="H255" s="2"/>
       <c r="I255" s="3" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="J255" s="2"/>
     </row>
     <row r="256" spans="1:10">
       <c r="A256" s="2" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>426</v>
+        <v>630</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
       <c r="D256" s="2">
-        <v>4.9000000000000004</v>
+        <v>9.6</v>
       </c>
       <c r="E256" s="2">
-        <v>3.43</v>
+        <v>6.72</v>
       </c>
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
       <c r="I256" s="3" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="J256" s="2"/>
     </row>
     <row r="257" spans="1:11">
       <c r="A257" s="2" t="s">
-        <v>754</v>
+        <v>743</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>430</v>
+        <v>630</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>602</v>
+        <v>744</v>
       </c>
       <c r="D257" s="2">
-        <v>10.9</v>
+        <v>5.9</v>
       </c>
       <c r="E257" s="2">
-        <v>7.63</v>
+        <v>4.13</v>
       </c>
       <c r="F257" s="2"/>
       <c r="G257" s="2"/>
       <c r="H257" s="2"/>
       <c r="I257" s="3" t="s">
-        <v>603</v>
+        <v>745</v>
       </c>
       <c r="J257" s="2"/>
     </row>
     <row r="258" spans="1:11">
       <c r="A258" s="2" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>756</v>
+        <v>430</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="D258" s="2">
-        <v>18.5</v>
+        <v>8.9</v>
       </c>
       <c r="E258" s="2">
-        <v>12.95</v>
+        <v>6.23</v>
       </c>
       <c r="F258" s="2"/>
       <c r="G258" s="2"/>
       <c r="H258" s="2"/>
       <c r="I258" s="3" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="J258" s="2"/>
     </row>
     <row r="259" spans="1:11">
       <c r="A259" s="2" t="s">
-        <v>759</v>
+        <v>749</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>756</v>
+        <v>426</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="D259" s="2">
-        <v>18.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E259" s="2">
-        <v>12.95</v>
+        <v>3.43</v>
       </c>
       <c r="F259" s="2"/>
       <c r="G259" s="2"/>
       <c r="H259" s="2"/>
       <c r="I259" s="3" t="s">
-        <v>761</v>
+        <v>751</v>
       </c>
       <c r="J259" s="2"/>
     </row>
     <row r="260" spans="1:11">
       <c r="A260" s="2" t="s">
-        <v>762</v>
+        <v>752</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>756</v>
+        <v>430</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>763</v>
+        <v>600</v>
       </c>
       <c r="D260" s="2">
-        <v>18.5</v>
+        <v>10.9</v>
       </c>
       <c r="E260" s="2">
-        <v>12.95</v>
+        <v>7.63</v>
       </c>
       <c r="F260" s="2"/>
       <c r="G260" s="2"/>
       <c r="H260" s="2"/>
       <c r="I260" s="3" t="s">
-        <v>764</v>
+        <v>601</v>
       </c>
       <c r="J260" s="2"/>
     </row>
     <row r="261" spans="1:11">
       <c r="A261" s="2" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>766</v>
+        <v>755</v>
       </c>
       <c r="D261" s="2">
         <v>18.5</v>
@@ -10094,19 +10109,19 @@
       <c r="G261" s="2"/>
       <c r="H261" s="2"/>
       <c r="I261" s="3" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="J261" s="2"/>
     </row>
     <row r="262" spans="1:11">
       <c r="A262" s="2" t="s">
-        <v>768</v>
+        <v>757</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>769</v>
+        <v>758</v>
       </c>
       <c r="D262" s="2">
         <v>18.5</v>
@@ -10118,19 +10133,19 @@
       <c r="G262" s="2"/>
       <c r="H262" s="2"/>
       <c r="I262" s="3" t="s">
-        <v>770</v>
+        <v>759</v>
       </c>
       <c r="J262" s="2"/>
     </row>
     <row r="263" spans="1:11">
       <c r="A263" s="2" t="s">
-        <v>771</v>
+        <v>760</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>772</v>
+        <v>761</v>
       </c>
       <c r="D263" s="2">
         <v>18.5</v>
@@ -10142,284 +10157,284 @@
       <c r="G263" s="2"/>
       <c r="H263" s="2"/>
       <c r="I263" s="3" t="s">
-        <v>773</v>
+        <v>762</v>
       </c>
       <c r="J263" s="2"/>
     </row>
     <row r="264" spans="1:11">
       <c r="A264" s="2" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>775</v>
+        <v>764</v>
       </c>
       <c r="D264" s="2">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="E264" s="2">
-        <v>13.65</v>
+        <v>12.95</v>
       </c>
       <c r="F264" s="2"/>
       <c r="G264" s="2"/>
       <c r="H264" s="2"/>
       <c r="I264" s="3" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="J264" s="2"/>
     </row>
     <row r="265" spans="1:11">
       <c r="A265" s="2" t="s">
-        <v>777</v>
+        <v>766</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>778</v>
+        <v>767</v>
       </c>
       <c r="D265" s="2">
-        <v>22.5</v>
+        <v>18.5</v>
       </c>
       <c r="E265" s="2">
-        <v>15.75</v>
+        <v>12.95</v>
       </c>
       <c r="F265" s="2"/>
       <c r="G265" s="2"/>
       <c r="H265" s="2"/>
       <c r="I265" s="3" t="s">
-        <v>779</v>
+        <v>768</v>
       </c>
       <c r="J265" s="2"/>
     </row>
     <row r="266" spans="1:11">
-      <c r="A266" s="5">
-        <v>80305</v>
-      </c>
-      <c r="B266" s="6" t="s">
-        <v>783</v>
-      </c>
-      <c r="C266" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="D266" s="6">
-        <v>6.9</v>
-      </c>
-      <c r="E266" s="6">
-        <v>4.83</v>
-      </c>
-      <c r="F266" s="6"/>
-      <c r="G266" s="6"/>
-      <c r="H266" s="6"/>
-      <c r="I266" s="7" t="s">
-        <v>781</v>
-      </c>
-      <c r="J266" s="8"/>
-      <c r="K266" s="9"/>
+      <c r="A266" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="D266" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="E266" s="2">
+        <v>12.95</v>
+      </c>
+      <c r="F266" s="2"/>
+      <c r="G266" s="2"/>
+      <c r="H266" s="2"/>
+      <c r="I266" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="J266" s="2"/>
     </row>
     <row r="267" spans="1:11">
       <c r="A267" s="2" t="s">
-        <v>782</v>
+        <v>772</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>783</v>
+        <v>754</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="D267" s="2">
-        <v>5.9</v>
+        <v>19.5</v>
       </c>
       <c r="E267" s="2">
-        <v>4.13</v>
+        <v>13.65</v>
       </c>
       <c r="F267" s="2"/>
       <c r="G267" s="2"/>
       <c r="H267" s="2"/>
-      <c r="I267" s="11" t="s">
-        <v>1120</v>
+      <c r="I267" s="3" t="s">
+        <v>774</v>
       </c>
       <c r="J267" s="2"/>
     </row>
     <row r="268" spans="1:11">
       <c r="A268" s="2" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>783</v>
+        <v>754</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
       <c r="D268" s="2">
-        <v>5.9</v>
+        <v>22.5</v>
       </c>
       <c r="E268" s="2">
-        <v>4.13</v>
+        <v>15.75</v>
       </c>
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
       <c r="H268" s="2"/>
       <c r="I268" s="3" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
       <c r="J268" s="2"/>
     </row>
     <row r="269" spans="1:11">
-      <c r="A269" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="D269" s="2">
-        <v>15.9</v>
-      </c>
-      <c r="E269" s="2">
-        <v>11.13</v>
-      </c>
-      <c r="F269" s="2"/>
-      <c r="G269" s="2"/>
-      <c r="H269" s="2"/>
-      <c r="I269" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="J269" s="2"/>
+      <c r="A269" s="5">
+        <v>80305</v>
+      </c>
+      <c r="B269" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="C269" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="D269" s="6">
+        <v>6.9</v>
+      </c>
+      <c r="E269" s="6">
+        <v>4.83</v>
+      </c>
+      <c r="F269" s="6"/>
+      <c r="G269" s="6"/>
+      <c r="H269" s="6"/>
+      <c r="I269" s="7" t="s">
+        <v>779</v>
+      </c>
+      <c r="J269" s="8"/>
+      <c r="K269" s="9"/>
     </row>
     <row r="270" spans="1:11">
       <c r="A270" s="2" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="D270" s="2">
-        <v>15.9</v>
+        <v>5.9</v>
       </c>
       <c r="E270" s="2">
-        <v>11.13</v>
+        <v>4.13</v>
       </c>
       <c r="F270" s="2"/>
       <c r="G270" s="2"/>
       <c r="H270" s="2"/>
-      <c r="I270" s="3" t="s">
-        <v>793</v>
+      <c r="I270" s="11" t="s">
+        <v>1117</v>
       </c>
       <c r="J270" s="2"/>
     </row>
     <row r="271" spans="1:11">
       <c r="A271" s="2" t="s">
-        <v>794</v>
+        <v>783</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>795</v>
+        <v>784</v>
       </c>
       <c r="D271" s="2">
-        <v>4.9000000000000004</v>
+        <v>5.9</v>
       </c>
       <c r="E271" s="2">
-        <v>3.43</v>
+        <v>4.13</v>
       </c>
       <c r="F271" s="2"/>
       <c r="G271" s="2"/>
       <c r="H271" s="2"/>
       <c r="I271" s="3" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="J271" s="2"/>
     </row>
     <row r="272" spans="1:11">
       <c r="A272" s="2" t="s">
-        <v>797</v>
+        <v>786</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>798</v>
+        <v>787</v>
       </c>
       <c r="D272" s="2">
-        <v>6.5</v>
+        <v>15.9</v>
       </c>
       <c r="E272" s="2">
-        <v>4.55</v>
+        <v>11.13</v>
       </c>
       <c r="F272" s="2"/>
       <c r="G272" s="2"/>
       <c r="H272" s="2"/>
       <c r="I272" s="3" t="s">
-        <v>799</v>
+        <v>788</v>
       </c>
       <c r="J272" s="2"/>
     </row>
     <row r="273" spans="1:10">
       <c r="A273" s="2" t="s">
-        <v>800</v>
+        <v>789</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>801</v>
+        <v>790</v>
       </c>
       <c r="D273" s="2">
-        <v>5.9</v>
+        <v>15.9</v>
       </c>
       <c r="E273" s="2">
-        <v>4.13</v>
+        <v>11.13</v>
       </c>
       <c r="F273" s="2"/>
       <c r="G273" s="2"/>
       <c r="H273" s="2"/>
       <c r="I273" s="3" t="s">
-        <v>802</v>
+        <v>791</v>
       </c>
       <c r="J273" s="2"/>
     </row>
     <row r="274" spans="1:10">
       <c r="A274" s="2" t="s">
-        <v>803</v>
+        <v>792</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>804</v>
+        <v>793</v>
       </c>
       <c r="D274" s="2">
-        <v>6.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E274" s="2">
-        <v>4.55</v>
+        <v>3.43</v>
       </c>
       <c r="F274" s="2"/>
       <c r="G274" s="2"/>
       <c r="H274" s="2"/>
       <c r="I274" s="3" t="s">
-        <v>805</v>
+        <v>794</v>
       </c>
       <c r="J274" s="2"/>
     </row>
     <row r="275" spans="1:10">
       <c r="A275" s="2" t="s">
-        <v>806</v>
+        <v>795</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>807</v>
+        <v>796</v>
       </c>
       <c r="D275" s="2">
         <v>6.5</v>
@@ -10431,379 +10446,379 @@
       <c r="G275" s="2"/>
       <c r="H275" s="2"/>
       <c r="I275" s="3" t="s">
-        <v>808</v>
+        <v>797</v>
       </c>
       <c r="J275" s="2"/>
     </row>
     <row r="276" spans="1:10">
       <c r="A276" s="2" t="s">
-        <v>809</v>
+        <v>798</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>810</v>
+        <v>799</v>
       </c>
       <c r="D276" s="2">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="E276" s="2">
-        <v>4.83</v>
+        <v>4.13</v>
       </c>
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
       <c r="H276" s="2"/>
       <c r="I276" s="3" t="s">
-        <v>811</v>
+        <v>800</v>
       </c>
       <c r="J276" s="2"/>
     </row>
     <row r="277" spans="1:10">
       <c r="A277" s="2" t="s">
-        <v>812</v>
+        <v>801</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>813</v>
+        <v>802</v>
       </c>
       <c r="D277" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="E277" s="2">
-        <v>4.83</v>
+        <v>4.55</v>
       </c>
       <c r="F277" s="2"/>
       <c r="G277" s="2"/>
       <c r="H277" s="2"/>
       <c r="I277" s="3" t="s">
-        <v>814</v>
+        <v>803</v>
       </c>
       <c r="J277" s="2"/>
     </row>
     <row r="278" spans="1:10">
       <c r="A278" s="2" t="s">
-        <v>815</v>
+        <v>804</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>816</v>
+        <v>805</v>
       </c>
       <c r="D278" s="2">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="E278" s="2">
-        <v>5.53</v>
+        <v>4.55</v>
       </c>
       <c r="F278" s="2"/>
       <c r="G278" s="2"/>
       <c r="H278" s="2"/>
       <c r="I278" s="3" t="s">
-        <v>817</v>
+        <v>806</v>
       </c>
       <c r="J278" s="2"/>
     </row>
     <row r="279" spans="1:10">
       <c r="A279" s="2" t="s">
-        <v>818</v>
+        <v>807</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>819</v>
+        <v>808</v>
       </c>
       <c r="D279" s="2">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="E279" s="2">
-        <v>5.25</v>
+        <v>4.83</v>
       </c>
       <c r="F279" s="2"/>
       <c r="G279" s="2"/>
       <c r="H279" s="2"/>
       <c r="I279" s="3" t="s">
-        <v>820</v>
+        <v>809</v>
       </c>
       <c r="J279" s="2"/>
     </row>
     <row r="280" spans="1:10">
       <c r="A280" s="2" t="s">
-        <v>821</v>
+        <v>810</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>822</v>
+        <v>811</v>
       </c>
       <c r="D280" s="2">
-        <v>4.9000000000000004</v>
+        <v>6.9</v>
       </c>
       <c r="E280" s="2">
-        <v>3.43</v>
+        <v>4.83</v>
       </c>
       <c r="F280" s="2"/>
       <c r="G280" s="2"/>
       <c r="H280" s="2"/>
       <c r="I280" s="3" t="s">
-        <v>823</v>
+        <v>812</v>
       </c>
       <c r="J280" s="2"/>
     </row>
     <row r="281" spans="1:10">
       <c r="A281" s="2" t="s">
-        <v>824</v>
+        <v>813</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>825</v>
+        <v>814</v>
       </c>
       <c r="D281" s="2">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="E281" s="2">
-        <v>4.83</v>
+        <v>5.53</v>
       </c>
       <c r="F281" s="2"/>
       <c r="G281" s="2"/>
       <c r="H281" s="2"/>
       <c r="I281" s="3" t="s">
-        <v>826</v>
+        <v>815</v>
       </c>
       <c r="J281" s="2"/>
     </row>
     <row r="282" spans="1:10">
       <c r="A282" s="2" t="s">
-        <v>827</v>
+        <v>816</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>828</v>
+        <v>817</v>
       </c>
       <c r="D282" s="2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="E282" s="2">
-        <v>5.53</v>
+        <v>5.25</v>
       </c>
       <c r="F282" s="2"/>
       <c r="G282" s="2"/>
       <c r="H282" s="2"/>
       <c r="I282" s="3" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
       <c r="J282" s="2"/>
     </row>
     <row r="283" spans="1:10">
       <c r="A283" s="2" t="s">
-        <v>830</v>
+        <v>819</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>831</v>
+        <v>820</v>
       </c>
       <c r="D283" s="2">
-        <v>6.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E283" s="2">
-        <v>4.83</v>
+        <v>3.43</v>
       </c>
       <c r="F283" s="2"/>
       <c r="G283" s="2"/>
       <c r="H283" s="2"/>
       <c r="I283" s="3" t="s">
-        <v>832</v>
+        <v>821</v>
       </c>
       <c r="J283" s="2"/>
     </row>
     <row r="284" spans="1:10">
       <c r="A284" s="2" t="s">
-        <v>833</v>
+        <v>822</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>834</v>
+        <v>823</v>
       </c>
       <c r="D284" s="2">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="E284" s="2">
-        <v>5.25</v>
+        <v>4.83</v>
       </c>
       <c r="F284" s="2"/>
       <c r="G284" s="2"/>
       <c r="H284" s="2"/>
       <c r="I284" s="3" t="s">
-        <v>835</v>
+        <v>824</v>
       </c>
       <c r="J284" s="2"/>
     </row>
     <row r="285" spans="1:10">
       <c r="A285" s="2" t="s">
-        <v>836</v>
+        <v>825</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>837</v>
+        <v>826</v>
       </c>
       <c r="D285" s="2">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="E285" s="2">
-        <v>4.13</v>
+        <v>5.53</v>
       </c>
       <c r="F285" s="2"/>
       <c r="G285" s="2"/>
       <c r="H285" s="2"/>
       <c r="I285" s="3" t="s">
-        <v>838</v>
+        <v>827</v>
       </c>
       <c r="J285" s="2"/>
     </row>
     <row r="286" spans="1:10">
       <c r="A286" s="2" t="s">
-        <v>839</v>
+        <v>828</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="D286" s="2">
-        <v>4.9000000000000004</v>
+        <v>6.9</v>
       </c>
       <c r="E286" s="2">
-        <v>3.43</v>
+        <v>4.83</v>
       </c>
       <c r="F286" s="2"/>
       <c r="G286" s="2"/>
       <c r="H286" s="2"/>
       <c r="I286" s="3" t="s">
-        <v>841</v>
+        <v>830</v>
       </c>
       <c r="J286" s="2"/>
     </row>
     <row r="287" spans="1:10">
       <c r="A287" s="2" t="s">
-        <v>842</v>
+        <v>831</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>843</v>
+        <v>832</v>
       </c>
       <c r="D287" s="2">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="E287" s="2">
-        <v>5.95</v>
+        <v>5.25</v>
       </c>
       <c r="F287" s="2"/>
       <c r="G287" s="2"/>
       <c r="H287" s="2"/>
       <c r="I287" s="3" t="s">
-        <v>844</v>
+        <v>833</v>
       </c>
       <c r="J287" s="2"/>
     </row>
     <row r="288" spans="1:10">
       <c r="A288" s="2" t="s">
-        <v>845</v>
+        <v>834</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>846</v>
+        <v>835</v>
       </c>
       <c r="D288" s="2">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="E288" s="2">
-        <v>4.83</v>
+        <v>4.13</v>
       </c>
       <c r="F288" s="2"/>
       <c r="G288" s="2"/>
       <c r="H288" s="2"/>
       <c r="I288" s="3" t="s">
-        <v>847</v>
+        <v>836</v>
       </c>
       <c r="J288" s="2"/>
     </row>
     <row r="289" spans="1:10">
       <c r="A289" s="2" t="s">
-        <v>848</v>
+        <v>837</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>849</v>
+        <v>838</v>
       </c>
       <c r="D289" s="2">
-        <v>6.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E289" s="2">
-        <v>4.55</v>
+        <v>3.43</v>
       </c>
       <c r="F289" s="2"/>
       <c r="G289" s="2"/>
       <c r="H289" s="2"/>
       <c r="I289" s="3" t="s">
-        <v>850</v>
+        <v>839</v>
       </c>
       <c r="J289" s="2"/>
     </row>
     <row r="290" spans="1:10">
       <c r="A290" s="2" t="s">
-        <v>851</v>
+        <v>840</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>852</v>
+        <v>841</v>
       </c>
       <c r="D290" s="2">
-        <v>10.9</v>
+        <v>8.5</v>
       </c>
       <c r="E290" s="2">
-        <v>7.63</v>
+        <v>5.95</v>
       </c>
       <c r="F290" s="2"/>
       <c r="G290" s="2"/>
       <c r="H290" s="2"/>
       <c r="I290" s="3" t="s">
-        <v>853</v>
+        <v>842</v>
       </c>
       <c r="J290" s="2"/>
     </row>
     <row r="291" spans="1:10">
       <c r="A291" s="2" t="s">
-        <v>854</v>
+        <v>843</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>855</v>
+        <v>844</v>
       </c>
       <c r="D291" s="2">
         <v>6.9</v>
@@ -10815,115 +10830,115 @@
       <c r="G291" s="2"/>
       <c r="H291" s="2"/>
       <c r="I291" s="3" t="s">
-        <v>856</v>
+        <v>845</v>
       </c>
       <c r="J291" s="2"/>
     </row>
     <row r="292" spans="1:10">
       <c r="A292" s="2" t="s">
-        <v>857</v>
+        <v>846</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>858</v>
+        <v>847</v>
       </c>
       <c r="D292" s="2">
-        <v>11.9</v>
+        <v>6.5</v>
       </c>
       <c r="E292" s="2">
-        <v>8.33</v>
+        <v>4.55</v>
       </c>
       <c r="F292" s="2"/>
       <c r="G292" s="2"/>
       <c r="H292" s="2"/>
       <c r="I292" s="3" t="s">
-        <v>859</v>
+        <v>848</v>
       </c>
       <c r="J292" s="2"/>
     </row>
     <row r="293" spans="1:10">
       <c r="A293" s="2" t="s">
-        <v>860</v>
+        <v>849</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>861</v>
+        <v>850</v>
       </c>
       <c r="D293" s="2">
-        <v>6.9</v>
+        <v>10.9</v>
       </c>
       <c r="E293" s="2">
-        <v>4.83</v>
+        <v>7.63</v>
       </c>
       <c r="F293" s="2"/>
       <c r="G293" s="2"/>
       <c r="H293" s="2"/>
       <c r="I293" s="3" t="s">
-        <v>862</v>
+        <v>851</v>
       </c>
       <c r="J293" s="2"/>
     </row>
     <row r="294" spans="1:10">
       <c r="A294" s="2" t="s">
-        <v>863</v>
+        <v>852</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>864</v>
+        <v>853</v>
       </c>
       <c r="D294" s="2">
-        <v>11.9</v>
+        <v>6.9</v>
       </c>
       <c r="E294" s="2">
-        <v>8.33</v>
+        <v>4.83</v>
       </c>
       <c r="F294" s="2"/>
       <c r="G294" s="2"/>
       <c r="H294" s="2"/>
       <c r="I294" s="3" t="s">
-        <v>865</v>
+        <v>854</v>
       </c>
       <c r="J294" s="2"/>
     </row>
     <row r="295" spans="1:10">
       <c r="A295" s="2" t="s">
-        <v>866</v>
+        <v>855</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>867</v>
+        <v>856</v>
       </c>
       <c r="D295" s="2">
-        <v>6.9</v>
+        <v>11.9</v>
       </c>
       <c r="E295" s="2">
-        <v>4.83</v>
+        <v>8.33</v>
       </c>
       <c r="F295" s="2"/>
       <c r="G295" s="2"/>
       <c r="H295" s="2"/>
       <c r="I295" s="3" t="s">
-        <v>868</v>
+        <v>857</v>
       </c>
       <c r="J295" s="2"/>
     </row>
     <row r="296" spans="1:10">
       <c r="A296" s="2" t="s">
-        <v>869</v>
+        <v>858</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>870</v>
+        <v>859</v>
       </c>
       <c r="D296" s="2">
         <v>6.9</v>
@@ -10935,19 +10950,19 @@
       <c r="G296" s="2"/>
       <c r="H296" s="2"/>
       <c r="I296" s="3" t="s">
-        <v>871</v>
+        <v>860</v>
       </c>
       <c r="J296" s="2"/>
     </row>
     <row r="297" spans="1:10">
       <c r="A297" s="2" t="s">
-        <v>872</v>
+        <v>861</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>873</v>
+        <v>862</v>
       </c>
       <c r="D297" s="2">
         <v>11.9</v>
@@ -10959,67 +10974,67 @@
       <c r="G297" s="2"/>
       <c r="H297" s="2"/>
       <c r="I297" s="3" t="s">
-        <v>874</v>
+        <v>863</v>
       </c>
       <c r="J297" s="2"/>
     </row>
     <row r="298" spans="1:10">
       <c r="A298" s="2" t="s">
-        <v>875</v>
+        <v>864</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>876</v>
+        <v>865</v>
       </c>
       <c r="D298" s="2">
-        <v>11.9</v>
+        <v>6.9</v>
       </c>
       <c r="E298" s="2">
-        <v>8.33</v>
+        <v>4.83</v>
       </c>
       <c r="F298" s="2"/>
       <c r="G298" s="2"/>
       <c r="H298" s="2"/>
       <c r="I298" s="3" t="s">
-        <v>877</v>
+        <v>866</v>
       </c>
       <c r="J298" s="2"/>
     </row>
     <row r="299" spans="1:10">
       <c r="A299" s="2" t="s">
-        <v>878</v>
+        <v>867</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>879</v>
+        <v>868</v>
       </c>
       <c r="D299" s="2">
-        <v>11.9</v>
+        <v>6.9</v>
       </c>
       <c r="E299" s="2">
-        <v>8.33</v>
+        <v>4.83</v>
       </c>
       <c r="F299" s="2"/>
       <c r="G299" s="2"/>
       <c r="H299" s="2"/>
       <c r="I299" s="3" t="s">
-        <v>880</v>
+        <v>869</v>
       </c>
       <c r="J299" s="2"/>
     </row>
     <row r="300" spans="1:10">
       <c r="A300" s="2" t="s">
-        <v>881</v>
+        <v>870</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>882</v>
+        <v>871</v>
       </c>
       <c r="D300" s="2">
         <v>11.9</v>
@@ -11031,477 +11046,473 @@
       <c r="G300" s="2"/>
       <c r="H300" s="2"/>
       <c r="I300" s="3" t="s">
-        <v>883</v>
+        <v>872</v>
       </c>
       <c r="J300" s="2"/>
     </row>
     <row r="301" spans="1:10">
       <c r="A301" s="2" t="s">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>885</v>
+        <v>874</v>
       </c>
       <c r="D301" s="2">
-        <v>9.9</v>
+        <v>11.9</v>
       </c>
       <c r="E301" s="2">
-        <v>6.93</v>
+        <v>8.33</v>
       </c>
       <c r="F301" s="2"/>
       <c r="G301" s="2"/>
       <c r="H301" s="2"/>
       <c r="I301" s="3" t="s">
-        <v>886</v>
+        <v>875</v>
       </c>
       <c r="J301" s="2"/>
     </row>
     <row r="302" spans="1:10">
       <c r="A302" s="2" t="s">
-        <v>887</v>
+        <v>876</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="D302" s="2">
-        <v>10.9</v>
+        <v>11.9</v>
       </c>
       <c r="E302" s="2">
-        <v>7.63</v>
+        <v>8.33</v>
       </c>
       <c r="F302" s="2"/>
       <c r="G302" s="2"/>
       <c r="H302" s="2"/>
       <c r="I302" s="3" t="s">
-        <v>889</v>
+        <v>878</v>
       </c>
       <c r="J302" s="2"/>
     </row>
     <row r="303" spans="1:10">
       <c r="A303" s="2" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="D303" s="2">
-        <v>6.9</v>
+        <v>11.9</v>
       </c>
       <c r="E303" s="2">
-        <v>4.83</v>
-      </c>
-      <c r="F303" s="2" t="s">
-        <v>1110</v>
-      </c>
+        <v>8.33</v>
+      </c>
+      <c r="F303" s="2"/>
       <c r="G303" s="2"/>
       <c r="H303" s="2"/>
       <c r="I303" s="3" t="s">
-        <v>892</v>
+        <v>881</v>
       </c>
       <c r="J303" s="2"/>
     </row>
     <row r="304" spans="1:10">
       <c r="A304" s="2" t="s">
-        <v>893</v>
+        <v>882</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>894</v>
+        <v>883</v>
       </c>
       <c r="D304" s="2">
-        <v>6.9</v>
+        <v>9.9</v>
       </c>
       <c r="E304" s="2">
-        <v>4.83</v>
+        <v>6.93</v>
       </c>
       <c r="F304" s="2"/>
       <c r="G304" s="2"/>
       <c r="H304" s="2"/>
       <c r="I304" s="3" t="s">
-        <v>895</v>
+        <v>884</v>
       </c>
       <c r="J304" s="2"/>
     </row>
     <row r="305" spans="1:10">
       <c r="A305" s="2" t="s">
-        <v>896</v>
+        <v>885</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>897</v>
+        <v>886</v>
       </c>
       <c r="D305" s="2">
-        <v>5.5</v>
+        <v>10.9</v>
       </c>
       <c r="E305" s="2">
-        <v>3.85</v>
+        <v>7.63</v>
       </c>
       <c r="F305" s="2"/>
       <c r="G305" s="2"/>
       <c r="H305" s="2"/>
       <c r="I305" s="3" t="s">
-        <v>898</v>
+        <v>887</v>
       </c>
       <c r="J305" s="2"/>
     </row>
     <row r="306" spans="1:10">
       <c r="A306" s="2" t="s">
-        <v>899</v>
+        <v>888</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>900</v>
+        <v>889</v>
       </c>
       <c r="D306" s="2">
-        <v>5.9</v>
-      </c>
-      <c r="E306" s="2">
-        <v>4.13</v>
-      </c>
+        <v>6.9</v>
+      </c>
+      <c r="E306" s="2"/>
       <c r="F306" s="2"/>
       <c r="G306" s="2"/>
       <c r="H306" s="2"/>
       <c r="I306" s="3" t="s">
-        <v>901</v>
+        <v>890</v>
       </c>
       <c r="J306" s="2"/>
     </row>
     <row r="307" spans="1:10">
       <c r="A307" s="2" t="s">
-        <v>902</v>
+        <v>891</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>903</v>
+        <v>892</v>
       </c>
       <c r="D307" s="2">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="E307" s="2">
-        <v>4.55</v>
+        <v>4.83</v>
       </c>
       <c r="F307" s="2"/>
       <c r="G307" s="2"/>
       <c r="H307" s="2"/>
       <c r="I307" s="3" t="s">
-        <v>904</v>
+        <v>893</v>
       </c>
       <c r="J307" s="2"/>
     </row>
     <row r="308" spans="1:10">
       <c r="A308" s="2" t="s">
-        <v>905</v>
+        <v>894</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>906</v>
+        <v>895</v>
       </c>
       <c r="D308" s="2">
-        <v>7.9</v>
+        <v>5.5</v>
       </c>
       <c r="E308" s="2">
-        <v>5.53</v>
+        <v>3.85</v>
       </c>
       <c r="F308" s="2"/>
       <c r="G308" s="2"/>
       <c r="H308" s="2"/>
       <c r="I308" s="3" t="s">
-        <v>907</v>
+        <v>896</v>
       </c>
       <c r="J308" s="2"/>
     </row>
     <row r="309" spans="1:10">
       <c r="A309" s="2" t="s">
-        <v>908</v>
+        <v>897</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>909</v>
+        <v>898</v>
       </c>
       <c r="D309" s="2">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="E309" s="2">
-        <v>1.75</v>
+        <v>4.13</v>
       </c>
       <c r="F309" s="2"/>
       <c r="G309" s="2"/>
       <c r="H309" s="2"/>
       <c r="I309" s="3" t="s">
-        <v>910</v>
+        <v>899</v>
       </c>
       <c r="J309" s="2"/>
     </row>
     <row r="310" spans="1:10">
       <c r="A310" s="2" t="s">
-        <v>911</v>
+        <v>900</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>912</v>
+        <v>901</v>
       </c>
       <c r="D310" s="2">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="E310" s="2">
-        <v>1.75</v>
+        <v>4.55</v>
       </c>
       <c r="F310" s="2"/>
       <c r="G310" s="2"/>
       <c r="H310" s="2"/>
       <c r="I310" s="3" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="J310" s="2"/>
     </row>
     <row r="311" spans="1:10">
       <c r="A311" s="2" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>915</v>
+        <v>904</v>
       </c>
       <c r="D311" s="2">
-        <v>1.5</v>
+        <v>7.9</v>
       </c>
       <c r="E311" s="2">
-        <v>1.05</v>
+        <v>5.53</v>
       </c>
       <c r="F311" s="2"/>
       <c r="G311" s="2"/>
       <c r="H311" s="2"/>
       <c r="I311" s="3" t="s">
-        <v>630</v>
+        <v>905</v>
       </c>
       <c r="J311" s="2"/>
     </row>
     <row r="312" spans="1:10">
-      <c r="A312" s="2">
-        <v>80146</v>
-      </c>
-      <c r="B312" s="12" t="s">
-        <v>783</v>
-      </c>
-      <c r="C312" s="12" t="s">
-        <v>1118</v>
+      <c r="A312" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>907</v>
       </c>
       <c r="D312" s="2">
-        <v>7.9</v>
+        <v>2.5</v>
       </c>
       <c r="E312" s="2">
-        <v>5.53</v>
+        <v>1.75</v>
       </c>
       <c r="F312" s="2"/>
       <c r="G312" s="2"/>
       <c r="H312" s="2"/>
       <c r="I312" s="3" t="s">
-        <v>1119</v>
+        <v>908</v>
       </c>
       <c r="J312" s="2"/>
     </row>
     <row r="313" spans="1:10">
       <c r="A313" s="2" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="D313" s="2">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E313" s="2">
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="F313" s="2"/>
       <c r="G313" s="2"/>
       <c r="H313" s="2"/>
       <c r="I313" s="3" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="J313" s="2"/>
     </row>
     <row r="314" spans="1:10">
-      <c r="A314" s="13">
-        <v>40505</v>
+      <c r="A314" s="2" t="s">
+        <v>912</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>756</v>
+        <v>781</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>1104</v>
+        <v>913</v>
       </c>
       <c r="D314" s="2">
-        <v>20.399999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="E314" s="2">
-        <v>14.28</v>
+        <v>1.05</v>
       </c>
       <c r="F314" s="2"/>
       <c r="G314" s="2"/>
       <c r="H314" s="2"/>
       <c r="I314" s="3" t="s">
-        <v>1105</v>
+        <v>628</v>
       </c>
       <c r="J314" s="2"/>
     </row>
     <row r="315" spans="1:10">
-      <c r="A315" s="2" t="s">
-        <v>919</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="C315" s="2" t="s">
-        <v>920</v>
+      <c r="A315" s="2">
+        <v>80146</v>
+      </c>
+      <c r="B315" s="12" t="s">
+        <v>781</v>
+      </c>
+      <c r="C315" s="12" t="s">
+        <v>1115</v>
       </c>
       <c r="D315" s="2">
-        <v>18.899999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="E315" s="2">
-        <v>13.23</v>
+        <v>5.53</v>
       </c>
       <c r="F315" s="2"/>
       <c r="G315" s="2"/>
       <c r="H315" s="2"/>
       <c r="I315" s="3" t="s">
-        <v>921</v>
+        <v>1116</v>
       </c>
       <c r="J315" s="2"/>
     </row>
     <row r="316" spans="1:10">
       <c r="A316" s="2" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>756</v>
+        <v>781</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="D316" s="2">
-        <v>20.9</v>
+        <v>1.5</v>
       </c>
       <c r="E316" s="2">
-        <v>14.63</v>
+        <v>1.05</v>
       </c>
       <c r="F316" s="2"/>
       <c r="G316" s="2"/>
       <c r="H316" s="2"/>
       <c r="I316" s="3" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
       <c r="J316" s="2"/>
     </row>
     <row r="317" spans="1:10">
-      <c r="A317" s="2" t="s">
-        <v>925</v>
+      <c r="A317" s="13">
+        <v>40505</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>926</v>
+        <v>1102</v>
       </c>
       <c r="D317" s="2">
-        <v>22.5</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="E317" s="2">
-        <v>15.75</v>
+        <v>14.28</v>
       </c>
       <c r="F317" s="2"/>
       <c r="G317" s="2"/>
       <c r="H317" s="2"/>
       <c r="I317" s="3" t="s">
-        <v>927</v>
+        <v>1103</v>
       </c>
       <c r="J317" s="2"/>
     </row>
     <row r="318" spans="1:10">
       <c r="A318" s="2" t="s">
-        <v>928</v>
+        <v>917</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>929</v>
+        <v>918</v>
       </c>
       <c r="D318" s="2">
-        <v>22.5</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="E318" s="2">
-        <v>15.75</v>
+        <v>13.23</v>
       </c>
       <c r="F318" s="2"/>
       <c r="G318" s="2"/>
       <c r="H318" s="2"/>
       <c r="I318" s="3" t="s">
-        <v>930</v>
+        <v>919</v>
       </c>
       <c r="J318" s="2"/>
     </row>
     <row r="319" spans="1:10">
       <c r="A319" s="2" t="s">
-        <v>931</v>
+        <v>920</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>932</v>
+        <v>921</v>
       </c>
       <c r="D319" s="2">
-        <v>22.5</v>
+        <v>20.9</v>
       </c>
       <c r="E319" s="2">
-        <v>15.75</v>
+        <v>14.63</v>
       </c>
       <c r="F319" s="2"/>
       <c r="G319" s="2"/>
       <c r="H319" s="2"/>
       <c r="I319" s="3" t="s">
-        <v>933</v>
+        <v>922</v>
       </c>
       <c r="J319" s="2"/>
     </row>
     <row r="320" spans="1:10">
       <c r="A320" s="2" t="s">
-        <v>934</v>
+        <v>923</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>935</v>
+        <v>924</v>
       </c>
       <c r="D320" s="2">
         <v>22.5</v>
@@ -11513,91 +11524,91 @@
       <c r="G320" s="2"/>
       <c r="H320" s="2"/>
       <c r="I320" s="3" t="s">
-        <v>936</v>
+        <v>925</v>
       </c>
       <c r="J320" s="2"/>
     </row>
     <row r="321" spans="1:11">
       <c r="A321" s="2" t="s">
-        <v>937</v>
+        <v>926</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>938</v>
+        <v>927</v>
       </c>
       <c r="D321" s="2">
-        <v>18.5</v>
+        <v>22.5</v>
       </c>
       <c r="E321" s="2">
-        <v>12.95</v>
+        <v>15.75</v>
       </c>
       <c r="F321" s="2"/>
       <c r="G321" s="2"/>
       <c r="H321" s="2"/>
       <c r="I321" s="3" t="s">
-        <v>939</v>
+        <v>928</v>
       </c>
       <c r="J321" s="2"/>
     </row>
     <row r="322" spans="1:11">
       <c r="A322" s="2" t="s">
-        <v>940</v>
+        <v>929</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>941</v>
+        <v>930</v>
       </c>
       <c r="D322" s="2">
-        <v>16.3</v>
+        <v>22.5</v>
       </c>
       <c r="E322" s="2">
-        <v>11.41</v>
+        <v>15.75</v>
       </c>
       <c r="F322" s="2"/>
       <c r="G322" s="2"/>
       <c r="H322" s="2"/>
       <c r="I322" s="3" t="s">
-        <v>942</v>
+        <v>931</v>
       </c>
       <c r="J322" s="2"/>
     </row>
     <row r="323" spans="1:11">
       <c r="A323" s="2" t="s">
-        <v>943</v>
+        <v>932</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>944</v>
+        <v>933</v>
       </c>
       <c r="D323" s="2">
-        <v>18.5</v>
+        <v>22.5</v>
       </c>
       <c r="E323" s="2">
-        <v>12.95</v>
+        <v>15.75</v>
       </c>
       <c r="F323" s="2"/>
       <c r="G323" s="2"/>
       <c r="H323" s="2"/>
       <c r="I323" s="3" t="s">
-        <v>945</v>
+        <v>934</v>
       </c>
       <c r="J323" s="2"/>
     </row>
     <row r="324" spans="1:11">
       <c r="A324" s="2" t="s">
-        <v>946</v>
+        <v>935</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>947</v>
+        <v>936</v>
       </c>
       <c r="D324" s="2">
         <v>18.5</v>
@@ -11609,43 +11620,43 @@
       <c r="G324" s="2"/>
       <c r="H324" s="2"/>
       <c r="I324" s="3" t="s">
-        <v>948</v>
+        <v>937</v>
       </c>
       <c r="J324" s="2"/>
     </row>
     <row r="325" spans="1:11">
       <c r="A325" s="2" t="s">
-        <v>949</v>
+        <v>938</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>950</v>
+        <v>939</v>
       </c>
       <c r="D325" s="2">
-        <v>18.5</v>
+        <v>16.3</v>
       </c>
       <c r="E325" s="2">
-        <v>12.95</v>
+        <v>11.41</v>
       </c>
       <c r="F325" s="2"/>
       <c r="G325" s="2"/>
       <c r="H325" s="2"/>
       <c r="I325" s="3" t="s">
-        <v>951</v>
+        <v>940</v>
       </c>
       <c r="J325" s="2"/>
     </row>
     <row r="326" spans="1:11">
       <c r="A326" s="2" t="s">
-        <v>952</v>
+        <v>941</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>953</v>
+        <v>942</v>
       </c>
       <c r="D326" s="2">
         <v>18.5</v>
@@ -11657,19 +11668,19 @@
       <c r="G326" s="2"/>
       <c r="H326" s="2"/>
       <c r="I326" s="3" t="s">
-        <v>954</v>
+        <v>943</v>
       </c>
       <c r="J326" s="2"/>
     </row>
     <row r="327" spans="1:11">
       <c r="A327" s="2" t="s">
-        <v>955</v>
+        <v>944</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>956</v>
+        <v>945</v>
       </c>
       <c r="D327" s="2">
         <v>18.5</v>
@@ -11681,19 +11692,19 @@
       <c r="G327" s="2"/>
       <c r="H327" s="2"/>
       <c r="I327" s="3" t="s">
-        <v>957</v>
+        <v>946</v>
       </c>
       <c r="J327" s="2"/>
     </row>
     <row r="328" spans="1:11">
       <c r="A328" s="2" t="s">
-        <v>958</v>
+        <v>947</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>959</v>
+        <v>948</v>
       </c>
       <c r="D328" s="2">
         <v>18.5</v>
@@ -11705,953 +11716,951 @@
       <c r="G328" s="2"/>
       <c r="H328" s="2"/>
       <c r="I328" s="3" t="s">
-        <v>960</v>
+        <v>949</v>
       </c>
       <c r="J328" s="2"/>
     </row>
     <row r="329" spans="1:11">
       <c r="A329" s="2" t="s">
-        <v>961</v>
+        <v>950</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>962</v>
+        <v>951</v>
       </c>
       <c r="D329" s="2">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="E329" s="2">
-        <v>13.65</v>
+        <v>12.95</v>
       </c>
       <c r="F329" s="2"/>
       <c r="G329" s="2"/>
       <c r="H329" s="2"/>
       <c r="I329" s="3" t="s">
-        <v>963</v>
+        <v>952</v>
       </c>
       <c r="J329" s="2"/>
     </row>
     <row r="330" spans="1:11">
       <c r="A330" s="2" t="s">
-        <v>964</v>
+        <v>953</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>965</v>
+        <v>954</v>
       </c>
       <c r="D330" s="2">
-        <v>22.5</v>
+        <v>18.5</v>
       </c>
       <c r="E330" s="2">
-        <v>15.75</v>
+        <v>12.95</v>
       </c>
       <c r="F330" s="2"/>
       <c r="G330" s="2"/>
       <c r="H330" s="2"/>
       <c r="I330" s="3" t="s">
-        <v>966</v>
+        <v>955</v>
       </c>
       <c r="J330" s="2"/>
     </row>
     <row r="331" spans="1:11">
       <c r="A331" s="2" t="s">
-        <v>967</v>
+        <v>956</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>968</v>
+        <v>957</v>
       </c>
       <c r="D331" s="2">
-        <v>16.899999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="E331" s="2">
-        <v>11.83</v>
-      </c>
-      <c r="F331" s="2" t="s">
-        <v>1110</v>
-      </c>
+        <v>12.95</v>
+      </c>
+      <c r="F331" s="2"/>
       <c r="G331" s="2"/>
       <c r="H331" s="2"/>
       <c r="I331" s="3" t="s">
-        <v>969</v>
+        <v>958</v>
       </c>
       <c r="J331" s="2"/>
     </row>
     <row r="332" spans="1:11">
       <c r="A332" s="2" t="s">
-        <v>970</v>
+        <v>959</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>971</v>
+        <v>960</v>
       </c>
       <c r="D332" s="2">
-        <v>23.9</v>
+        <v>19.5</v>
       </c>
       <c r="E332" s="2">
-        <v>16.73</v>
+        <v>13.65</v>
       </c>
       <c r="F332" s="2"/>
       <c r="G332" s="2"/>
       <c r="H332" s="2"/>
       <c r="I332" s="3" t="s">
-        <v>972</v>
+        <v>961</v>
       </c>
       <c r="J332" s="2"/>
     </row>
     <row r="333" spans="1:11">
-      <c r="A333" s="5">
-        <v>100236</v>
-      </c>
-      <c r="B333" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="C333" s="6" t="s">
-        <v>973</v>
-      </c>
-      <c r="D333" s="6">
-        <v>14.9</v>
-      </c>
-      <c r="E333" s="6">
-        <v>10.43</v>
-      </c>
-      <c r="F333" s="6"/>
-      <c r="G333" s="6"/>
-      <c r="H333" s="6"/>
-      <c r="I333" s="7" t="s">
-        <v>974</v>
-      </c>
-      <c r="J333" s="8"/>
-      <c r="K333" s="9"/>
+      <c r="A333" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="D333" s="2">
+        <v>22.5</v>
+      </c>
+      <c r="E333" s="2">
+        <v>15.75</v>
+      </c>
+      <c r="F333" s="2"/>
+      <c r="G333" s="2"/>
+      <c r="H333" s="2"/>
+      <c r="I333" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="J333" s="2"/>
     </row>
     <row r="334" spans="1:11">
       <c r="A334" s="2" t="s">
-        <v>975</v>
+        <v>965</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>225</v>
+        <v>754</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>976</v>
+        <v>966</v>
       </c>
       <c r="D334" s="2">
-        <v>11.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E334" s="2">
-        <v>8.0500000000000007</v>
+        <v>11.83</v>
       </c>
       <c r="F334" s="2"/>
       <c r="G334" s="2"/>
       <c r="H334" s="2"/>
       <c r="I334" s="3" t="s">
-        <v>977</v>
+        <v>967</v>
       </c>
       <c r="J334" s="2"/>
     </row>
     <row r="335" spans="1:11">
       <c r="A335" s="2" t="s">
-        <v>978</v>
+        <v>968</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>225</v>
+        <v>754</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>979</v>
+        <v>969</v>
       </c>
       <c r="D335" s="2">
-        <v>10.9</v>
+        <v>23.9</v>
       </c>
       <c r="E335" s="2">
-        <v>7.63</v>
+        <v>16.73</v>
       </c>
       <c r="F335" s="2"/>
       <c r="G335" s="2"/>
       <c r="H335" s="2"/>
       <c r="I335" s="3" t="s">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="J335" s="2"/>
     </row>
     <row r="336" spans="1:11">
-      <c r="A336" s="2" t="s">
-        <v>981</v>
-      </c>
-      <c r="B336" s="2" t="s">
+      <c r="A336" s="5">
+        <v>100236</v>
+      </c>
+      <c r="B336" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="C336" s="2" t="s">
-        <v>982</v>
-      </c>
-      <c r="D336" s="2">
+      <c r="C336" s="6" t="s">
+        <v>971</v>
+      </c>
+      <c r="D336" s="6">
         <v>14.9</v>
       </c>
-      <c r="E336" s="2">
-        <v>10.15</v>
-      </c>
-      <c r="F336" s="2"/>
-      <c r="G336" s="2"/>
-      <c r="H336" s="2"/>
-      <c r="I336" s="3" t="s">
-        <v>983</v>
-      </c>
-      <c r="J336" s="2"/>
+      <c r="E336" s="6">
+        <v>10.43</v>
+      </c>
+      <c r="F336" s="6"/>
+      <c r="G336" s="6"/>
+      <c r="H336" s="6"/>
+      <c r="I336" s="7" t="s">
+        <v>972</v>
+      </c>
+      <c r="J336" s="8"/>
+      <c r="K336" s="9"/>
     </row>
     <row r="337" spans="1:11">
       <c r="A337" s="2" t="s">
-        <v>984</v>
+        <v>973</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>985</v>
+        <v>974</v>
       </c>
       <c r="D337" s="2">
-        <v>9.9</v>
+        <v>11.5</v>
       </c>
       <c r="E337" s="2">
-        <v>6.93</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="F337" s="2"/>
       <c r="G337" s="2"/>
       <c r="H337" s="2"/>
       <c r="I337" s="3" t="s">
-        <v>986</v>
+        <v>975</v>
       </c>
       <c r="J337" s="2"/>
     </row>
     <row r="338" spans="1:11">
       <c r="A338" s="2" t="s">
-        <v>987</v>
+        <v>976</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>988</v>
+        <v>977</v>
       </c>
       <c r="D338" s="2">
-        <v>16.899999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="E338" s="2">
-        <v>11.83</v>
+        <v>7.63</v>
       </c>
       <c r="F338" s="2"/>
       <c r="G338" s="2"/>
       <c r="H338" s="2"/>
       <c r="I338" s="3" t="s">
-        <v>989</v>
+        <v>978</v>
       </c>
       <c r="J338" s="2"/>
     </row>
     <row r="339" spans="1:11">
       <c r="A339" s="2" t="s">
-        <v>990</v>
+        <v>979</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>991</v>
+        <v>980</v>
       </c>
       <c r="D339" s="2">
-        <v>14</v>
+        <v>14.9</v>
       </c>
       <c r="E339" s="2">
-        <v>9.8000000000000007</v>
+        <v>10.15</v>
       </c>
       <c r="F339" s="2"/>
       <c r="G339" s="2"/>
       <c r="H339" s="2"/>
       <c r="I339" s="3" t="s">
-        <v>992</v>
+        <v>981</v>
       </c>
       <c r="J339" s="2"/>
     </row>
     <row r="340" spans="1:11">
       <c r="A340" s="2" t="s">
-        <v>993</v>
+        <v>982</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>1106</v>
+        <v>983</v>
       </c>
       <c r="D340" s="2">
-        <v>15.9</v>
+        <v>9.9</v>
       </c>
       <c r="E340" s="2">
-        <v>11.13</v>
+        <v>6.93</v>
       </c>
       <c r="F340" s="2"/>
       <c r="G340" s="2"/>
       <c r="H340" s="2"/>
       <c r="I340" s="3" t="s">
-        <v>994</v>
+        <v>984</v>
       </c>
       <c r="J340" s="2"/>
     </row>
     <row r="341" spans="1:11">
       <c r="A341" s="2" t="s">
-        <v>995</v>
+        <v>985</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>996</v>
+        <v>986</v>
       </c>
       <c r="D341" s="2">
-        <v>15.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E341" s="2">
-        <v>11.13</v>
+        <v>11.83</v>
       </c>
       <c r="F341" s="2"/>
       <c r="G341" s="2"/>
       <c r="H341" s="2"/>
       <c r="I341" s="3" t="s">
-        <v>997</v>
+        <v>987</v>
       </c>
       <c r="J341" s="2"/>
     </row>
     <row r="342" spans="1:11">
       <c r="A342" s="2" t="s">
-        <v>998</v>
+        <v>988</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>999</v>
+        <v>989</v>
       </c>
       <c r="D342" s="2">
-        <v>11.9</v>
+        <v>14</v>
       </c>
       <c r="E342" s="2">
-        <v>8.33</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="F342" s="2"/>
       <c r="G342" s="2"/>
       <c r="H342" s="2"/>
       <c r="I342" s="3" t="s">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J342" s="2"/>
     </row>
     <row r="343" spans="1:11">
       <c r="A343" s="2" t="s">
-        <v>1001</v>
+        <v>991</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>1002</v>
+        <v>1104</v>
       </c>
       <c r="D343" s="2">
-        <v>6.9</v>
+        <v>15.9</v>
       </c>
       <c r="E343" s="2">
-        <v>4.83</v>
+        <v>11.13</v>
       </c>
       <c r="F343" s="2"/>
       <c r="G343" s="2"/>
       <c r="H343" s="2"/>
       <c r="I343" s="3" t="s">
-        <v>1003</v>
+        <v>992</v>
       </c>
       <c r="J343" s="2"/>
     </row>
     <row r="344" spans="1:11">
       <c r="A344" s="2" t="s">
-        <v>1004</v>
+        <v>993</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>1005</v>
+        <v>994</v>
       </c>
       <c r="D344" s="2">
-        <v>11.5</v>
+        <v>15.9</v>
       </c>
       <c r="E344" s="2">
-        <v>8.0500000000000007</v>
+        <v>11.13</v>
       </c>
       <c r="F344" s="2"/>
       <c r="G344" s="2"/>
       <c r="H344" s="2"/>
       <c r="I344" s="3" t="s">
-        <v>1006</v>
+        <v>995</v>
       </c>
       <c r="J344" s="2"/>
     </row>
     <row r="345" spans="1:11">
-      <c r="A345" s="5">
-        <v>100224</v>
-      </c>
-      <c r="B345" s="6" t="s">
+      <c r="A345" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="B345" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C345" s="6" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D345" s="6">
-        <v>12.5</v>
-      </c>
-      <c r="E345" s="6">
-        <v>8.75</v>
-      </c>
-      <c r="F345" s="6"/>
-      <c r="G345" s="6"/>
-      <c r="H345" s="6"/>
-      <c r="I345" s="7" t="s">
-        <v>1008</v>
-      </c>
-      <c r="J345" s="8"/>
-      <c r="K345" s="9"/>
+      <c r="C345" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="D345" s="2">
+        <v>11.9</v>
+      </c>
+      <c r="E345" s="2">
+        <v>8.33</v>
+      </c>
+      <c r="F345" s="2"/>
+      <c r="G345" s="2"/>
+      <c r="H345" s="2"/>
+      <c r="I345" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="J345" s="2"/>
     </row>
     <row r="346" spans="1:11">
       <c r="A346" s="2" t="s">
-        <v>1009</v>
+        <v>999</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="D346" s="2">
-        <v>11.3</v>
+        <v>6.9</v>
       </c>
       <c r="E346" s="2">
-        <v>7.91</v>
+        <v>4.83</v>
       </c>
       <c r="F346" s="2"/>
       <c r="G346" s="2"/>
       <c r="H346" s="2"/>
       <c r="I346" s="3" t="s">
-        <v>1011</v>
+        <v>1001</v>
       </c>
       <c r="J346" s="2"/>
     </row>
     <row r="347" spans="1:11">
       <c r="A347" s="2" t="s">
-        <v>1012</v>
+        <v>1002</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>1013</v>
+        <v>1003</v>
       </c>
       <c r="D347" s="2">
-        <v>26.9</v>
+        <v>11.5</v>
       </c>
       <c r="E347" s="2">
-        <v>18.829999999999998</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="F347" s="2"/>
       <c r="G347" s="2"/>
       <c r="H347" s="2"/>
       <c r="I347" s="3" t="s">
-        <v>1014</v>
+        <v>1004</v>
       </c>
       <c r="J347" s="2"/>
     </row>
     <row r="348" spans="1:11">
-      <c r="A348" s="2" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B348" s="2" t="s">
+      <c r="A348" s="5">
+        <v>100224</v>
+      </c>
+      <c r="B348" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C348" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D348" s="2">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="E348" s="2">
-        <v>13.93</v>
-      </c>
-      <c r="F348" s="2"/>
-      <c r="G348" s="2"/>
-      <c r="H348" s="2"/>
-      <c r="I348" s="3" t="s">
-        <v>1017</v>
-      </c>
-      <c r="J348" s="2"/>
+      <c r="C348" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D348" s="6">
+        <v>12.5</v>
+      </c>
+      <c r="E348" s="6">
+        <v>8.75</v>
+      </c>
+      <c r="F348" s="6"/>
+      <c r="G348" s="6"/>
+      <c r="H348" s="6"/>
+      <c r="I348" s="7" t="s">
+        <v>1006</v>
+      </c>
+      <c r="J348" s="8"/>
+      <c r="K348" s="9"/>
     </row>
     <row r="349" spans="1:11">
       <c r="A349" s="2" t="s">
-        <v>1018</v>
+        <v>1007</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>9</v>
+        <v>253</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>1019</v>
+        <v>1008</v>
       </c>
       <c r="D349" s="2">
-        <v>36</v>
+        <v>11.3</v>
       </c>
       <c r="E349" s="2">
-        <v>25.2</v>
+        <v>7.91</v>
       </c>
       <c r="F349" s="2"/>
       <c r="G349" s="2"/>
       <c r="H349" s="2"/>
       <c r="I349" s="3" t="s">
-        <v>223</v>
+        <v>1009</v>
       </c>
       <c r="J349" s="2"/>
     </row>
     <row r="350" spans="1:11">
       <c r="A350" s="2" t="s">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>1021</v>
+        <v>1011</v>
       </c>
       <c r="D350" s="2">
-        <v>16.899999999999999</v>
+        <v>26.9</v>
       </c>
       <c r="E350" s="2">
-        <v>11.83</v>
+        <v>18.829999999999998</v>
       </c>
       <c r="F350" s="2"/>
       <c r="G350" s="2"/>
       <c r="H350" s="2"/>
       <c r="I350" s="3" t="s">
-        <v>1022</v>
+        <v>1012</v>
       </c>
       <c r="J350" s="2"/>
     </row>
     <row r="351" spans="1:11">
       <c r="A351" s="2" t="s">
-        <v>1023</v>
+        <v>1013</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>1024</v>
+        <v>1014</v>
       </c>
       <c r="D351" s="2">
-        <v>18.5</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="E351" s="2">
-        <v>12.95</v>
+        <v>13.93</v>
       </c>
       <c r="F351" s="2"/>
       <c r="G351" s="2"/>
       <c r="H351" s="2"/>
       <c r="I351" s="3" t="s">
-        <v>1025</v>
+        <v>1015</v>
       </c>
       <c r="J351" s="2"/>
     </row>
     <row r="352" spans="1:11">
       <c r="A352" s="2" t="s">
-        <v>1026</v>
+        <v>1016</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>225</v>
+        <v>9</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>1027</v>
+        <v>1017</v>
       </c>
       <c r="D352" s="2">
-        <v>15.5</v>
+        <v>36</v>
       </c>
       <c r="E352" s="2">
-        <v>10.85</v>
+        <v>25.2</v>
       </c>
       <c r="F352" s="2"/>
       <c r="G352" s="2"/>
       <c r="H352" s="2"/>
       <c r="I352" s="3" t="s">
-        <v>1028</v>
+        <v>223</v>
       </c>
       <c r="J352" s="2"/>
     </row>
     <row r="353" spans="1:10">
-      <c r="A353" s="13">
-        <v>100218</v>
-      </c>
-      <c r="B353" s="12" t="s">
-        <v>1107</v>
+      <c r="A353" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>232</v>
+        <v>1019</v>
       </c>
       <c r="D353" s="2">
-        <v>12.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="E353" s="2">
-        <v>9.0299999999999994</v>
+        <v>11.83</v>
       </c>
       <c r="F353" s="2"/>
       <c r="G353" s="2"/>
       <c r="H353" s="2"/>
-      <c r="I353" s="3"/>
+      <c r="I353" s="3" t="s">
+        <v>1020</v>
+      </c>
       <c r="J353" s="2"/>
     </row>
     <row r="354" spans="1:10">
       <c r="A354" s="2" t="s">
-        <v>1029</v>
+        <v>1021</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="D354" s="2">
-        <v>19.899999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="E354" s="2">
-        <v>13.93</v>
+        <v>12.95</v>
       </c>
       <c r="F354" s="2"/>
       <c r="G354" s="2"/>
       <c r="H354" s="2"/>
       <c r="I354" s="3" t="s">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="J354" s="2"/>
     </row>
     <row r="355" spans="1:10">
       <c r="A355" s="2" t="s">
-        <v>1032</v>
+        <v>1024</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>9</v>
+        <v>225</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>1033</v>
+        <v>1025</v>
       </c>
       <c r="D355" s="2">
-        <v>50.5</v>
+        <v>15.5</v>
       </c>
       <c r="E355" s="2">
-        <v>35.35</v>
+        <v>10.85</v>
       </c>
       <c r="F355" s="2"/>
       <c r="G355" s="2"/>
       <c r="H355" s="2"/>
       <c r="I355" s="3" t="s">
-        <v>1034</v>
+        <v>1026</v>
       </c>
       <c r="J355" s="2"/>
     </row>
     <row r="356" spans="1:10">
-      <c r="A356" s="2" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B356" s="2" t="s">
-        <v>9</v>
+      <c r="A356" s="13">
+        <v>100218</v>
+      </c>
+      <c r="B356" s="12" t="s">
+        <v>1105</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>1036</v>
+        <v>232</v>
       </c>
       <c r="D356" s="2">
-        <v>32.5</v>
+        <v>12.9</v>
       </c>
       <c r="E356" s="2">
-        <v>22.75</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="F356" s="2"/>
       <c r="G356" s="2"/>
       <c r="H356" s="2"/>
-      <c r="I356" s="3" t="s">
-        <v>1037</v>
-      </c>
+      <c r="I356" s="3"/>
       <c r="J356" s="2"/>
     </row>
     <row r="357" spans="1:10">
       <c r="A357" s="2" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>9</v>
+        <v>225</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
       <c r="D357" s="2">
-        <v>43.5</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="E357" s="2">
-        <v>30.45</v>
+        <v>13.93</v>
       </c>
       <c r="F357" s="2"/>
       <c r="G357" s="2"/>
       <c r="H357" s="2"/>
       <c r="I357" s="3" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
       <c r="J357" s="2"/>
     </row>
     <row r="358" spans="1:10">
       <c r="A358" s="2" t="s">
-        <v>1041</v>
+        <v>1030</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>225</v>
+        <v>9</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
       <c r="D358" s="2">
-        <v>8.9</v>
+        <v>50.5</v>
       </c>
       <c r="E358" s="2">
-        <v>6.23</v>
+        <v>35.35</v>
       </c>
       <c r="F358" s="2"/>
       <c r="G358" s="2"/>
       <c r="H358" s="2"/>
       <c r="I358" s="3" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
       <c r="J358" s="2"/>
     </row>
     <row r="359" spans="1:10">
       <c r="A359" s="2" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>225</v>
+        <v>9</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
       <c r="D359" s="2">
-        <v>14.5</v>
+        <v>32.5</v>
       </c>
       <c r="E359" s="2">
-        <v>10.15</v>
+        <v>22.75</v>
       </c>
       <c r="F359" s="2"/>
       <c r="G359" s="2"/>
       <c r="H359" s="2"/>
       <c r="I359" s="3" t="s">
-        <v>1046</v>
+        <v>1035</v>
       </c>
       <c r="J359" s="2"/>
     </row>
     <row r="360" spans="1:10">
-      <c r="A360" s="13">
-        <v>100206</v>
-      </c>
-      <c r="B360" s="12" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C360" s="12" t="s">
-        <v>244</v>
+      <c r="A360" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>1037</v>
       </c>
       <c r="D360" s="2">
-        <v>18.899999999999999</v>
+        <v>43.5</v>
       </c>
       <c r="E360" s="2">
-        <v>13.23</v>
+        <v>30.45</v>
       </c>
       <c r="F360" s="2"/>
       <c r="G360" s="2"/>
       <c r="H360" s="2"/>
-      <c r="I360" s="3"/>
+      <c r="I360" s="3" t="s">
+        <v>1038</v>
+      </c>
       <c r="J360" s="2"/>
     </row>
     <row r="361" spans="1:10">
-      <c r="A361" s="13">
-        <v>100220</v>
-      </c>
-      <c r="B361" s="12" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C361" s="12" t="s">
-        <v>1108</v>
+      <c r="A361" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>1040</v>
       </c>
       <c r="D361" s="2">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="E361" s="2">
-        <v>6.93</v>
+        <v>6.23</v>
       </c>
       <c r="F361" s="2"/>
       <c r="G361" s="2"/>
       <c r="H361" s="2"/>
-      <c r="I361" s="3"/>
+      <c r="I361" s="3" t="s">
+        <v>1041</v>
+      </c>
       <c r="J361" s="2"/>
     </row>
     <row r="362" spans="1:10">
       <c r="A362" s="2" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="D362" s="2">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="E362" s="2">
-        <v>3.64</v>
+        <v>10.15</v>
       </c>
       <c r="F362" s="2"/>
       <c r="G362" s="2"/>
       <c r="H362" s="2"/>
       <c r="I362" s="3" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="J362" s="2"/>
     </row>
     <row r="363" spans="1:10">
-      <c r="A363" s="2" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B363" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C363" s="2" t="s">
-        <v>1051</v>
+      <c r="A363" s="13">
+        <v>100206</v>
+      </c>
+      <c r="B363" s="12" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C363" s="12" t="s">
+        <v>244</v>
       </c>
       <c r="D363" s="2">
-        <v>6</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="E363" s="2">
-        <v>4.2</v>
+        <v>13.23</v>
       </c>
       <c r="F363" s="2"/>
       <c r="G363" s="2"/>
       <c r="H363" s="2"/>
-      <c r="I363" s="3" t="s">
-        <v>1052</v>
-      </c>
+      <c r="I363" s="3"/>
       <c r="J363" s="2"/>
     </row>
     <row r="364" spans="1:10">
-      <c r="A364" s="2" t="s">
-        <v>1053</v>
-      </c>
-      <c r="B364" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C364" s="2" t="s">
-        <v>1054</v>
+      <c r="A364" s="13">
+        <v>100220</v>
+      </c>
+      <c r="B364" s="12" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C364" s="12" t="s">
+        <v>1106</v>
       </c>
       <c r="D364" s="2">
-        <v>6.9</v>
+        <v>9.9</v>
       </c>
       <c r="E364" s="2">
-        <v>4.83</v>
+        <v>6.93</v>
       </c>
       <c r="F364" s="2"/>
       <c r="G364" s="2"/>
       <c r="H364" s="2"/>
-      <c r="I364" s="3" t="s">
-        <v>1055</v>
-      </c>
+      <c r="I364" s="3"/>
       <c r="J364" s="2"/>
     </row>
     <row r="365" spans="1:10">
       <c r="A365" s="2" t="s">
-        <v>1056</v>
+        <v>1045</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>1057</v>
+        <v>1046</v>
       </c>
       <c r="D365" s="2">
-        <v>7.9</v>
+        <v>5.2</v>
       </c>
       <c r="E365" s="2">
-        <v>5.53</v>
+        <v>3.64</v>
       </c>
       <c r="F365" s="2"/>
       <c r="G365" s="2"/>
       <c r="H365" s="2"/>
       <c r="I365" s="3" t="s">
-        <v>1058</v>
+        <v>1047</v>
       </c>
       <c r="J365" s="2"/>
     </row>
     <row r="366" spans="1:10">
       <c r="A366" s="2" t="s">
-        <v>1059</v>
+        <v>1048</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>1060</v>
+        <v>1049</v>
       </c>
       <c r="D366" s="2">
-        <v>8.9</v>
+        <v>6</v>
       </c>
       <c r="E366" s="2">
-        <v>6.23</v>
+        <v>4.2</v>
       </c>
       <c r="F366" s="2"/>
       <c r="G366" s="2"/>
       <c r="H366" s="2"/>
       <c r="I366" s="3" t="s">
-        <v>1061</v>
+        <v>1050</v>
       </c>
       <c r="J366" s="2"/>
     </row>
     <row r="367" spans="1:10">
       <c r="A367" s="2" t="s">
-        <v>1062</v>
+        <v>1051</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>1063</v>
+        <v>1052</v>
       </c>
       <c r="D367" s="2">
-        <v>12.9</v>
+        <v>6.9</v>
       </c>
       <c r="E367" s="2">
-        <v>9.0299999999999994</v>
+        <v>4.83</v>
       </c>
       <c r="F367" s="2"/>
       <c r="G367" s="2"/>
       <c r="H367" s="2"/>
       <c r="I367" s="3" t="s">
-        <v>1064</v>
+        <v>1053</v>
       </c>
       <c r="J367" s="2"/>
     </row>
     <row r="368" spans="1:10">
       <c r="A368" s="2" t="s">
-        <v>1065</v>
+        <v>1054</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>1066</v>
+        <v>1055</v>
       </c>
       <c r="D368" s="2">
         <v>7.9</v>
@@ -12663,168 +12672,240 @@
       <c r="G368" s="2"/>
       <c r="H368" s="2"/>
       <c r="I368" s="3" t="s">
-        <v>1067</v>
+        <v>1056</v>
       </c>
       <c r="J368" s="2"/>
     </row>
     <row r="369" spans="1:10">
       <c r="A369" s="2" t="s">
-        <v>1068</v>
+        <v>1057</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>9</v>
+        <v>225</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>1069</v>
+        <v>1058</v>
       </c>
       <c r="D369" s="2">
-        <v>2.5</v>
+        <v>8.9</v>
       </c>
       <c r="E369" s="2">
-        <v>2.5</v>
+        <v>6.23</v>
       </c>
       <c r="F369" s="2"/>
       <c r="G369" s="2"/>
       <c r="H369" s="2"/>
       <c r="I369" s="3" t="s">
-        <v>1070</v>
+        <v>1059</v>
       </c>
       <c r="J369" s="2"/>
     </row>
     <row r="370" spans="1:10">
       <c r="A370" s="2" t="s">
-        <v>1071</v>
+        <v>1060</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>783</v>
+        <v>225</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>1072</v>
+        <v>1061</v>
       </c>
       <c r="D370" s="2">
-        <v>0.3</v>
+        <v>12.9</v>
       </c>
       <c r="E370" s="2">
-        <v>0.3</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="F370" s="2"/>
       <c r="G370" s="2"/>
       <c r="H370" s="2"/>
       <c r="I370" s="3" t="s">
-        <v>1073</v>
+        <v>1062</v>
       </c>
       <c r="J370" s="2"/>
     </row>
     <row r="371" spans="1:10">
       <c r="A371" s="2" t="s">
-        <v>1074</v>
+        <v>1063</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>783</v>
+        <v>225</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>1075</v>
+        <v>1064</v>
       </c>
       <c r="D371" s="2">
-        <v>0.3</v>
+        <v>7.9</v>
       </c>
       <c r="E371" s="2">
-        <v>0.3</v>
+        <v>5.53</v>
       </c>
       <c r="F371" s="2"/>
       <c r="G371" s="2"/>
       <c r="H371" s="2"/>
       <c r="I371" s="3" t="s">
-        <v>1076</v>
+        <v>1065</v>
       </c>
       <c r="J371" s="2"/>
     </row>
     <row r="372" spans="1:10">
       <c r="A372" s="2" t="s">
-        <v>1077</v>
+        <v>1066</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>783</v>
+        <v>9</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>1078</v>
+        <v>1067</v>
       </c>
       <c r="D372" s="2">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="E372" s="2">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="F372" s="2"/>
       <c r="G372" s="2"/>
       <c r="H372" s="2"/>
       <c r="I372" s="3" t="s">
-        <v>1079</v>
+        <v>1068</v>
       </c>
       <c r="J372" s="2"/>
     </row>
     <row r="373" spans="1:10">
-      <c r="A373" s="14">
+      <c r="A373" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D373" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E373" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F373" s="2"/>
+      <c r="G373" s="2"/>
+      <c r="H373" s="2"/>
+      <c r="I373" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="J373" s="2"/>
+    </row>
+    <row r="374" spans="1:10">
+      <c r="A374" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D374" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E374" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F374" s="2"/>
+      <c r="G374" s="2"/>
+      <c r="H374" s="2"/>
+      <c r="I374" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="J374" s="2"/>
+    </row>
+    <row r="375" spans="1:10">
+      <c r="A375" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D375" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E375" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F375" s="2"/>
+      <c r="G375" s="2"/>
+      <c r="H375" s="2"/>
+      <c r="I375" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="J375" s="2"/>
+    </row>
+    <row r="376" spans="1:10">
+      <c r="A376" s="14">
         <v>120101</v>
       </c>
-      <c r="B373" s="12" t="s">
+      <c r="B376" s="12" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C376" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D376" s="12">
+        <v>4.5</v>
+      </c>
+      <c r="E376">
+        <v>3.15</v>
+      </c>
+      <c r="I376" s="11" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10">
+      <c r="A377" s="14">
+        <v>120102</v>
+      </c>
+      <c r="B377" s="12" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C377" s="15" t="s">
         <v>1111</v>
       </c>
-      <c r="C373" t="s">
+      <c r="D377" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="E377">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="I377" s="11" t="s">
         <v>1112</v>
       </c>
-      <c r="D373" s="12">
-        <v>4.5</v>
-      </c>
-      <c r="E373">
-        <v>3.15</v>
-      </c>
-      <c r="I373" s="11" t="s">
+    </row>
+    <row r="378" spans="1:10">
+      <c r="A378" s="14">
+        <v>120103</v>
+      </c>
+      <c r="B378" s="12" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C378" t="s">
         <v>1113</v>
       </c>
-    </row>
-    <row r="374" spans="1:10">
-      <c r="A374" s="14">
-        <v>120102</v>
-      </c>
-      <c r="B374" s="12" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C374" s="15" t="s">
+      <c r="D378" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="E378">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="I378" t="s">
         <v>1114</v>
       </c>
-      <c r="D374" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="E374">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="I374" s="11" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="375" spans="1:10">
-      <c r="A375" s="14">
-        <v>120103</v>
-      </c>
-      <c r="B375" s="12" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C375" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D375" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="E375">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="I375" t="s">
-        <v>1117</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J372" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:J375" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -13036,161 +13117,162 @@
     <hyperlink ref="I212" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
     <hyperlink ref="I213" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
     <hyperlink ref="I214" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="I215" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="I216" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="I217" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="I218" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="I219" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="I220" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="I221" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="I222" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="I223" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="I224" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="I225" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="I226" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
-    <hyperlink ref="I227" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
-    <hyperlink ref="I228" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
-    <hyperlink ref="I229" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
-    <hyperlink ref="I230" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
-    <hyperlink ref="I231" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
-    <hyperlink ref="I232" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
-    <hyperlink ref="I233" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
-    <hyperlink ref="I234" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
-    <hyperlink ref="I235" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
-    <hyperlink ref="I236" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
-    <hyperlink ref="I237" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
-    <hyperlink ref="I238" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
-    <hyperlink ref="I239" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
-    <hyperlink ref="I240" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
-    <hyperlink ref="I241" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
-    <hyperlink ref="I242" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
-    <hyperlink ref="I243" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
-    <hyperlink ref="I244" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
-    <hyperlink ref="I245" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
-    <hyperlink ref="I246" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
-    <hyperlink ref="I247" r:id="rId243" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
-    <hyperlink ref="I248" r:id="rId244" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
-    <hyperlink ref="I249" r:id="rId245" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
-    <hyperlink ref="I250" r:id="rId246" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
-    <hyperlink ref="I251" r:id="rId247" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
-    <hyperlink ref="I252" r:id="rId248" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
-    <hyperlink ref="I253" r:id="rId249" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
-    <hyperlink ref="I254" r:id="rId250" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
-    <hyperlink ref="I255" r:id="rId251" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
-    <hyperlink ref="I256" r:id="rId252" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
-    <hyperlink ref="I257" r:id="rId253" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
-    <hyperlink ref="I258" r:id="rId254" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
-    <hyperlink ref="I259" r:id="rId255" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
-    <hyperlink ref="I260" r:id="rId256" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
-    <hyperlink ref="I261" r:id="rId257" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
-    <hyperlink ref="I262" r:id="rId258" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
-    <hyperlink ref="I263" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
-    <hyperlink ref="I264" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
-    <hyperlink ref="I265" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
-    <hyperlink ref="I266" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
-    <hyperlink ref="I267" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
-    <hyperlink ref="I268" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
-    <hyperlink ref="I269" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
-    <hyperlink ref="I270" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
-    <hyperlink ref="I271" r:id="rId267" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
-    <hyperlink ref="I272" r:id="rId268" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
-    <hyperlink ref="I273" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
-    <hyperlink ref="I274" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
-    <hyperlink ref="I275" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
-    <hyperlink ref="I276" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
-    <hyperlink ref="I277" r:id="rId273" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
-    <hyperlink ref="I278" r:id="rId274" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
-    <hyperlink ref="I279" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
-    <hyperlink ref="I280" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
-    <hyperlink ref="I281" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
-    <hyperlink ref="I282" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
-    <hyperlink ref="I283" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
-    <hyperlink ref="I284" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
-    <hyperlink ref="I285" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
-    <hyperlink ref="I286" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
-    <hyperlink ref="I287" r:id="rId283" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
-    <hyperlink ref="I288" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
-    <hyperlink ref="I289" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
-    <hyperlink ref="I290" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
-    <hyperlink ref="I291" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
-    <hyperlink ref="I292" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
-    <hyperlink ref="I293" r:id="rId289" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
-    <hyperlink ref="I294" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
-    <hyperlink ref="I295" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
-    <hyperlink ref="I296" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
-    <hyperlink ref="I297" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
-    <hyperlink ref="I298" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
-    <hyperlink ref="I299" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
-    <hyperlink ref="I300" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
-    <hyperlink ref="I301" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
-    <hyperlink ref="I302" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
-    <hyperlink ref="I303" r:id="rId299" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
-    <hyperlink ref="I304" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
-    <hyperlink ref="I305" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
-    <hyperlink ref="I306" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
-    <hyperlink ref="I307" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
-    <hyperlink ref="I308" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
-    <hyperlink ref="I309" r:id="rId305" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
-    <hyperlink ref="I310" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
-    <hyperlink ref="I311" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
-    <hyperlink ref="I313" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
-    <hyperlink ref="I315" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
-    <hyperlink ref="I316" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
-    <hyperlink ref="I317" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
-    <hyperlink ref="I318" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
-    <hyperlink ref="I319" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
-    <hyperlink ref="I320" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
-    <hyperlink ref="I321" r:id="rId315" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="I322" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="I323" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="I324" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="I325" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
-    <hyperlink ref="I326" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="I327" r:id="rId321" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
-    <hyperlink ref="I328" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
-    <hyperlink ref="I329" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
-    <hyperlink ref="I330" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
-    <hyperlink ref="I331" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="I332" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="I333" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="I334" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="I335" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
-    <hyperlink ref="I336" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="I337" r:id="rId331" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="I338" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
-    <hyperlink ref="I339" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
-    <hyperlink ref="I340" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
-    <hyperlink ref="I341" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
-    <hyperlink ref="I342" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
-    <hyperlink ref="I343" r:id="rId337" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
-    <hyperlink ref="I344" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
-    <hyperlink ref="I345" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="I346" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="I347" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
-    <hyperlink ref="I348" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
-    <hyperlink ref="I349" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
-    <hyperlink ref="I350" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="I351" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="I352" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="I354" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="I355" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
-    <hyperlink ref="I356" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="I357" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
-    <hyperlink ref="I358" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
-    <hyperlink ref="I359" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="I362" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
-    <hyperlink ref="I363" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="I364" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
-    <hyperlink ref="I365" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
-    <hyperlink ref="I366" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
-    <hyperlink ref="I367" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="I368" r:id="rId359" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
-    <hyperlink ref="I369" r:id="rId360" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="I370" r:id="rId361" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
-    <hyperlink ref="I371" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
-    <hyperlink ref="I372" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="I373" r:id="rId364" xr:uid="{F9160EA0-F07B-4BB5-B702-F5073AA95056}"/>
-    <hyperlink ref="I374" r:id="rId365" xr:uid="{1AC55159-5C0D-4F25-94CA-0E2E9DEE3542}"/>
+    <hyperlink ref="I218" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="I219" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="I220" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="I221" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="I222" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="I223" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="I224" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="I225" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="I226" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="I227" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="I228" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="I229" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="I230" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000EB000000}"/>
+    <hyperlink ref="I231" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000EC000000}"/>
+    <hyperlink ref="I232" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000ED000000}"/>
+    <hyperlink ref="I233" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000EE000000}"/>
+    <hyperlink ref="I234" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000EF000000}"/>
+    <hyperlink ref="I235" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000F0000000}"/>
+    <hyperlink ref="I236" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000F1000000}"/>
+    <hyperlink ref="I237" r:id="rId230" xr:uid="{00000000-0004-0000-0000-0000F3000000}"/>
+    <hyperlink ref="I238" r:id="rId231" xr:uid="{00000000-0004-0000-0000-0000F4000000}"/>
+    <hyperlink ref="I239" r:id="rId232" xr:uid="{00000000-0004-0000-0000-0000F5000000}"/>
+    <hyperlink ref="I240" r:id="rId233" xr:uid="{00000000-0004-0000-0000-0000F6000000}"/>
+    <hyperlink ref="I241" r:id="rId234" xr:uid="{00000000-0004-0000-0000-0000F7000000}"/>
+    <hyperlink ref="I242" r:id="rId235" xr:uid="{00000000-0004-0000-0000-0000F8000000}"/>
+    <hyperlink ref="I243" r:id="rId236" xr:uid="{00000000-0004-0000-0000-0000F9000000}"/>
+    <hyperlink ref="I244" r:id="rId237" xr:uid="{00000000-0004-0000-0000-0000FA000000}"/>
+    <hyperlink ref="I245" r:id="rId238" xr:uid="{00000000-0004-0000-0000-0000FB000000}"/>
+    <hyperlink ref="I246" r:id="rId239" xr:uid="{00000000-0004-0000-0000-0000FC000000}"/>
+    <hyperlink ref="I247" r:id="rId240" xr:uid="{00000000-0004-0000-0000-0000FD000000}"/>
+    <hyperlink ref="I248" r:id="rId241" xr:uid="{00000000-0004-0000-0000-0000FE000000}"/>
+    <hyperlink ref="I249" r:id="rId242" xr:uid="{00000000-0004-0000-0000-0000FF000000}"/>
+    <hyperlink ref="I250" r:id="rId243" xr:uid="{00000000-0004-0000-0000-000000010000}"/>
+    <hyperlink ref="I251" r:id="rId244" xr:uid="{00000000-0004-0000-0000-000001010000}"/>
+    <hyperlink ref="I252" r:id="rId245" xr:uid="{00000000-0004-0000-0000-000002010000}"/>
+    <hyperlink ref="I253" r:id="rId246" xr:uid="{00000000-0004-0000-0000-000003010000}"/>
+    <hyperlink ref="I254" r:id="rId247" xr:uid="{00000000-0004-0000-0000-000004010000}"/>
+    <hyperlink ref="I255" r:id="rId248" xr:uid="{00000000-0004-0000-0000-000005010000}"/>
+    <hyperlink ref="I256" r:id="rId249" xr:uid="{00000000-0004-0000-0000-000006010000}"/>
+    <hyperlink ref="I257" r:id="rId250" xr:uid="{00000000-0004-0000-0000-000007010000}"/>
+    <hyperlink ref="I258" r:id="rId251" xr:uid="{00000000-0004-0000-0000-000008010000}"/>
+    <hyperlink ref="I259" r:id="rId252" xr:uid="{00000000-0004-0000-0000-000009010000}"/>
+    <hyperlink ref="I260" r:id="rId253" xr:uid="{00000000-0004-0000-0000-00000A010000}"/>
+    <hyperlink ref="I261" r:id="rId254" xr:uid="{00000000-0004-0000-0000-00000B010000}"/>
+    <hyperlink ref="I262" r:id="rId255" xr:uid="{00000000-0004-0000-0000-00000C010000}"/>
+    <hyperlink ref="I263" r:id="rId256" xr:uid="{00000000-0004-0000-0000-00000D010000}"/>
+    <hyperlink ref="I264" r:id="rId257" xr:uid="{00000000-0004-0000-0000-00000E010000}"/>
+    <hyperlink ref="I265" r:id="rId258" xr:uid="{00000000-0004-0000-0000-00000F010000}"/>
+    <hyperlink ref="I266" r:id="rId259" xr:uid="{00000000-0004-0000-0000-000010010000}"/>
+    <hyperlink ref="I267" r:id="rId260" xr:uid="{00000000-0004-0000-0000-000011010000}"/>
+    <hyperlink ref="I268" r:id="rId261" xr:uid="{00000000-0004-0000-0000-000012010000}"/>
+    <hyperlink ref="I269" r:id="rId262" xr:uid="{00000000-0004-0000-0000-000013010000}"/>
+    <hyperlink ref="I270" r:id="rId263" xr:uid="{00000000-0004-0000-0000-000014010000}"/>
+    <hyperlink ref="I271" r:id="rId264" xr:uid="{00000000-0004-0000-0000-000015010000}"/>
+    <hyperlink ref="I272" r:id="rId265" xr:uid="{00000000-0004-0000-0000-000016010000}"/>
+    <hyperlink ref="I273" r:id="rId266" xr:uid="{00000000-0004-0000-0000-000017010000}"/>
+    <hyperlink ref="I274" r:id="rId267" xr:uid="{00000000-0004-0000-0000-000018010000}"/>
+    <hyperlink ref="I275" r:id="rId268" xr:uid="{00000000-0004-0000-0000-000019010000}"/>
+    <hyperlink ref="I276" r:id="rId269" xr:uid="{00000000-0004-0000-0000-00001A010000}"/>
+    <hyperlink ref="I277" r:id="rId270" xr:uid="{00000000-0004-0000-0000-00001B010000}"/>
+    <hyperlink ref="I278" r:id="rId271" xr:uid="{00000000-0004-0000-0000-00001C010000}"/>
+    <hyperlink ref="I279" r:id="rId272" xr:uid="{00000000-0004-0000-0000-00001D010000}"/>
+    <hyperlink ref="I280" r:id="rId273" xr:uid="{00000000-0004-0000-0000-00001E010000}"/>
+    <hyperlink ref="I281" r:id="rId274" xr:uid="{00000000-0004-0000-0000-00001F010000}"/>
+    <hyperlink ref="I282" r:id="rId275" xr:uid="{00000000-0004-0000-0000-000020010000}"/>
+    <hyperlink ref="I283" r:id="rId276" xr:uid="{00000000-0004-0000-0000-000021010000}"/>
+    <hyperlink ref="I284" r:id="rId277" xr:uid="{00000000-0004-0000-0000-000022010000}"/>
+    <hyperlink ref="I285" r:id="rId278" xr:uid="{00000000-0004-0000-0000-000023010000}"/>
+    <hyperlink ref="I286" r:id="rId279" xr:uid="{00000000-0004-0000-0000-000024010000}"/>
+    <hyperlink ref="I287" r:id="rId280" xr:uid="{00000000-0004-0000-0000-000025010000}"/>
+    <hyperlink ref="I288" r:id="rId281" xr:uid="{00000000-0004-0000-0000-000026010000}"/>
+    <hyperlink ref="I289" r:id="rId282" xr:uid="{00000000-0004-0000-0000-000027010000}"/>
+    <hyperlink ref="I290" r:id="rId283" xr:uid="{00000000-0004-0000-0000-000029010000}"/>
+    <hyperlink ref="I291" r:id="rId284" xr:uid="{00000000-0004-0000-0000-00002A010000}"/>
+    <hyperlink ref="I292" r:id="rId285" xr:uid="{00000000-0004-0000-0000-00002B010000}"/>
+    <hyperlink ref="I293" r:id="rId286" xr:uid="{00000000-0004-0000-0000-00002C010000}"/>
+    <hyperlink ref="I294" r:id="rId287" xr:uid="{00000000-0004-0000-0000-00002D010000}"/>
+    <hyperlink ref="I295" r:id="rId288" xr:uid="{00000000-0004-0000-0000-00002E010000}"/>
+    <hyperlink ref="I296" r:id="rId289" xr:uid="{00000000-0004-0000-0000-00002F010000}"/>
+    <hyperlink ref="I297" r:id="rId290" xr:uid="{00000000-0004-0000-0000-000030010000}"/>
+    <hyperlink ref="I298" r:id="rId291" xr:uid="{00000000-0004-0000-0000-000031010000}"/>
+    <hyperlink ref="I299" r:id="rId292" xr:uid="{00000000-0004-0000-0000-000032010000}"/>
+    <hyperlink ref="I300" r:id="rId293" xr:uid="{00000000-0004-0000-0000-000033010000}"/>
+    <hyperlink ref="I301" r:id="rId294" xr:uid="{00000000-0004-0000-0000-000034010000}"/>
+    <hyperlink ref="I302" r:id="rId295" xr:uid="{00000000-0004-0000-0000-000035010000}"/>
+    <hyperlink ref="I303" r:id="rId296" xr:uid="{00000000-0004-0000-0000-000036010000}"/>
+    <hyperlink ref="I304" r:id="rId297" xr:uid="{00000000-0004-0000-0000-000037010000}"/>
+    <hyperlink ref="I305" r:id="rId298" xr:uid="{00000000-0004-0000-0000-000038010000}"/>
+    <hyperlink ref="I306" r:id="rId299" xr:uid="{00000000-0004-0000-0000-000039010000}"/>
+    <hyperlink ref="I307" r:id="rId300" xr:uid="{00000000-0004-0000-0000-00003A010000}"/>
+    <hyperlink ref="I308" r:id="rId301" xr:uid="{00000000-0004-0000-0000-00003B010000}"/>
+    <hyperlink ref="I309" r:id="rId302" xr:uid="{00000000-0004-0000-0000-00003C010000}"/>
+    <hyperlink ref="I310" r:id="rId303" xr:uid="{00000000-0004-0000-0000-00003D010000}"/>
+    <hyperlink ref="I311" r:id="rId304" xr:uid="{00000000-0004-0000-0000-00003E010000}"/>
+    <hyperlink ref="I312" r:id="rId305" xr:uid="{00000000-0004-0000-0000-00003F010000}"/>
+    <hyperlink ref="I313" r:id="rId306" xr:uid="{00000000-0004-0000-0000-000040010000}"/>
+    <hyperlink ref="I314" r:id="rId307" xr:uid="{00000000-0004-0000-0000-000041010000}"/>
+    <hyperlink ref="I316" r:id="rId308" xr:uid="{00000000-0004-0000-0000-000042010000}"/>
+    <hyperlink ref="I318" r:id="rId309" xr:uid="{00000000-0004-0000-0000-000043010000}"/>
+    <hyperlink ref="I319" r:id="rId310" xr:uid="{00000000-0004-0000-0000-000044010000}"/>
+    <hyperlink ref="I320" r:id="rId311" xr:uid="{00000000-0004-0000-0000-000045010000}"/>
+    <hyperlink ref="I321" r:id="rId312" xr:uid="{00000000-0004-0000-0000-000046010000}"/>
+    <hyperlink ref="I322" r:id="rId313" xr:uid="{00000000-0004-0000-0000-000047010000}"/>
+    <hyperlink ref="I323" r:id="rId314" xr:uid="{00000000-0004-0000-0000-000048010000}"/>
+    <hyperlink ref="I324" r:id="rId315" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="I325" r:id="rId316" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="I326" r:id="rId317" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="I327" r:id="rId318" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="I328" r:id="rId319" xr:uid="{00000000-0004-0000-0000-00004D010000}"/>
+    <hyperlink ref="I329" r:id="rId320" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="I330" r:id="rId321" xr:uid="{00000000-0004-0000-0000-00004F010000}"/>
+    <hyperlink ref="I331" r:id="rId322" xr:uid="{00000000-0004-0000-0000-000050010000}"/>
+    <hyperlink ref="I332" r:id="rId323" xr:uid="{00000000-0004-0000-0000-000051010000}"/>
+    <hyperlink ref="I333" r:id="rId324" xr:uid="{00000000-0004-0000-0000-000052010000}"/>
+    <hyperlink ref="I334" r:id="rId325" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="I335" r:id="rId326" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="I336" r:id="rId327" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="I337" r:id="rId328" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="I338" r:id="rId329" xr:uid="{00000000-0004-0000-0000-000057010000}"/>
+    <hyperlink ref="I339" r:id="rId330" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="I340" r:id="rId331" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="I341" r:id="rId332" xr:uid="{00000000-0004-0000-0000-00005A010000}"/>
+    <hyperlink ref="I342" r:id="rId333" xr:uid="{00000000-0004-0000-0000-00005B010000}"/>
+    <hyperlink ref="I343" r:id="rId334" xr:uid="{00000000-0004-0000-0000-00005C010000}"/>
+    <hyperlink ref="I344" r:id="rId335" xr:uid="{00000000-0004-0000-0000-00005D010000}"/>
+    <hyperlink ref="I345" r:id="rId336" xr:uid="{00000000-0004-0000-0000-00005E010000}"/>
+    <hyperlink ref="I346" r:id="rId337" xr:uid="{00000000-0004-0000-0000-00005F010000}"/>
+    <hyperlink ref="I347" r:id="rId338" xr:uid="{00000000-0004-0000-0000-000060010000}"/>
+    <hyperlink ref="I348" r:id="rId339" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="I349" r:id="rId340" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="I350" r:id="rId341" xr:uid="{00000000-0004-0000-0000-000063010000}"/>
+    <hyperlink ref="I351" r:id="rId342" xr:uid="{00000000-0004-0000-0000-000064010000}"/>
+    <hyperlink ref="I352" r:id="rId343" xr:uid="{00000000-0004-0000-0000-000065010000}"/>
+    <hyperlink ref="I353" r:id="rId344" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="I354" r:id="rId345" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="I355" r:id="rId346" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="I357" r:id="rId347" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="I358" r:id="rId348" xr:uid="{00000000-0004-0000-0000-00006A010000}"/>
+    <hyperlink ref="I359" r:id="rId349" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="I360" r:id="rId350" xr:uid="{00000000-0004-0000-0000-00006C010000}"/>
+    <hyperlink ref="I361" r:id="rId351" xr:uid="{00000000-0004-0000-0000-00006D010000}"/>
+    <hyperlink ref="I362" r:id="rId352" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="I365" r:id="rId353" xr:uid="{00000000-0004-0000-0000-000074010000}"/>
+    <hyperlink ref="I366" r:id="rId354" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="I367" r:id="rId355" xr:uid="{00000000-0004-0000-0000-000076010000}"/>
+    <hyperlink ref="I368" r:id="rId356" xr:uid="{00000000-0004-0000-0000-000077010000}"/>
+    <hyperlink ref="I369" r:id="rId357" xr:uid="{00000000-0004-0000-0000-000078010000}"/>
+    <hyperlink ref="I370" r:id="rId358" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="I371" r:id="rId359" xr:uid="{00000000-0004-0000-0000-00007A010000}"/>
+    <hyperlink ref="I372" r:id="rId360" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="I373" r:id="rId361" xr:uid="{00000000-0004-0000-0000-00007C010000}"/>
+    <hyperlink ref="I374" r:id="rId362" xr:uid="{00000000-0004-0000-0000-00007D010000}"/>
+    <hyperlink ref="I375" r:id="rId363" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="I376" r:id="rId364" xr:uid="{F9160EA0-F07B-4BB5-B702-F5073AA95056}"/>
+    <hyperlink ref="I377" r:id="rId365" xr:uid="{1AC55159-5C0D-4F25-94CA-0E2E9DEE3542}"/>
+    <hyperlink ref="I215" r:id="rId366" xr:uid="{39463792-79B1-460E-B346-5F21542FF683}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
